--- a/research/traditional_assets/database/data/australia/australia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_investments_asset_management.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04735</v>
+        <v>0.0735</v>
       </c>
       <c r="E2">
-        <v>0.0301</v>
+        <v>0.07475</v>
       </c>
       <c r="F2">
-        <v>0.09895000000000001</v>
+        <v>-0.0462</v>
       </c>
       <c r="G2">
-        <v>0.329011196222702</v>
+        <v>0.2542252969126191</v>
       </c>
       <c r="H2">
-        <v>0.3277199701792269</v>
+        <v>0.253407833992644</v>
       </c>
       <c r="I2">
-        <v>0.4446772003306408</v>
+        <v>0.2654127583090516</v>
       </c>
       <c r="J2">
-        <v>0.378869126150257</v>
+        <v>0.2390411495379623</v>
       </c>
       <c r="K2">
-        <v>1346.089</v>
+        <v>1196.503</v>
       </c>
       <c r="L2">
-        <v>0.2825268487703969</v>
+        <v>0.2423431209462316</v>
       </c>
       <c r="M2">
-        <v>1226.6794</v>
+        <v>1342.5248</v>
       </c>
       <c r="N2">
-        <v>0.0318843618185958</v>
+        <v>0.0485515732950666</v>
       </c>
       <c r="O2">
-        <v>0.911291452496826</v>
+        <v>1.122040479631058</v>
       </c>
       <c r="P2">
-        <v>1181.4294</v>
+        <v>1270.2028</v>
       </c>
       <c r="Q2">
-        <v>0.03070820497411675</v>
+        <v>0.04593609320572612</v>
       </c>
       <c r="R2">
-        <v>0.8776755474563718</v>
+        <v>1.061596001012952</v>
       </c>
       <c r="S2">
-        <v>45.24999999999999</v>
+        <v>72.32199999999999</v>
       </c>
       <c r="T2">
-        <v>0.03688820404092544</v>
+        <v>0.05387014079739905</v>
       </c>
       <c r="U2">
-        <v>2135.807</v>
+        <v>2049.956</v>
       </c>
       <c r="V2">
-        <v>0.05551478500632655</v>
+        <v>0.07413538206941246</v>
       </c>
       <c r="W2">
-        <v>0.1344466600199402</v>
+        <v>0.03374513994090168</v>
       </c>
       <c r="X2">
-        <v>0.04394775155509397</v>
+        <v>0.07262679410017914</v>
       </c>
       <c r="Y2">
-        <v>0.09049890846484621</v>
+        <v>-0.03888165415927745</v>
       </c>
       <c r="Z2">
-        <v>0.3374245633163233</v>
+        <v>0.2572138202624148</v>
       </c>
       <c r="AA2">
-        <v>0.1532688778769695</v>
+        <v>0.01805245524006944</v>
       </c>
       <c r="AB2">
-        <v>0.04386295690739704</v>
+        <v>0.07238689154631267</v>
       </c>
       <c r="AC2">
-        <v>0.109602168683176</v>
+        <v>-0.05440176380063541</v>
       </c>
       <c r="AD2">
-        <v>1570.844</v>
+        <v>2059.593</v>
       </c>
       <c r="AE2">
-        <v>10.09243701936776</v>
+        <v>0.1548176603804269</v>
       </c>
       <c r="AF2">
-        <v>1580.936437019368</v>
+        <v>2059.74781766038</v>
       </c>
       <c r="AG2">
-        <v>-554.870562980632</v>
+        <v>9.791817660380275</v>
       </c>
       <c r="AH2">
-        <v>0.03947042539520017</v>
+        <v>0.06932547713214937</v>
       </c>
       <c r="AI2">
-        <v>0.06578105993785086</v>
+        <v>0.092570323612422</v>
       </c>
       <c r="AJ2">
-        <v>-0.01463347700040789</v>
+        <v>0.00035398963450926</v>
       </c>
       <c r="AK2">
-        <v>-0.02533944751258375</v>
+        <v>0.0004847273273267973</v>
       </c>
       <c r="AL2">
-        <v>42.565</v>
+        <v>45.288</v>
       </c>
       <c r="AM2">
-        <v>28.438</v>
+        <v>-55.79600000000001</v>
       </c>
       <c r="AN2">
-        <v>0.9685531178669246</v>
+        <v>1.658263406810529</v>
       </c>
       <c r="AO2">
-        <v>49.57894984141901</v>
+        <v>28.93196873343932</v>
       </c>
       <c r="AP2">
-        <v>-0.3421228421074701</v>
+        <v>0.007883796901800357</v>
       </c>
       <c r="AQ2">
-        <v>74.20803150713834</v>
+        <v>-23.48324252634597</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qualitas Limited (ASX:QAL)</t>
+          <t>Australian Ethical Investment Ltd. (ASX:AEF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,95 +724,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.201</v>
+      </c>
+      <c r="E3">
+        <v>0.266</v>
+      </c>
       <c r="G3">
-        <v>0.3881188118811881</v>
+        <v>0.2377049180327869</v>
       </c>
       <c r="H3">
-        <v>0.3881188118811881</v>
+        <v>0.2377049180327869</v>
       </c>
       <c r="I3">
-        <v>0.3841584158415841</v>
+        <v>0.2315573770491804</v>
       </c>
       <c r="J3">
-        <v>0.3657961267824895</v>
+        <v>0.1598209504396345</v>
       </c>
       <c r="K3">
-        <v>9.35</v>
+        <v>6.55</v>
       </c>
       <c r="L3">
-        <v>0.1851485148514851</v>
+        <v>0.1342213114754098</v>
       </c>
       <c r="M3">
-        <v>4.2</v>
+        <v>7.27</v>
       </c>
       <c r="N3">
-        <v>0.007921539041870991</v>
+        <v>0.02437961099932931</v>
       </c>
       <c r="O3">
-        <v>0.4491978609625669</v>
+        <v>1.109923664122137</v>
       </c>
       <c r="P3">
-        <v>4.2</v>
+        <v>5.42</v>
       </c>
       <c r="Q3">
-        <v>0.007921539041870991</v>
+        <v>0.0181757209926224</v>
       </c>
       <c r="R3">
-        <v>0.4491978609625669</v>
+        <v>0.8274809160305343</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2544704264099037</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.06338028169014084</v>
+      </c>
+      <c r="W3">
+        <v>0.361878453038674</v>
       </c>
       <c r="X3">
-        <v>0.04387296409148227</v>
+        <v>0.07249964433635839</v>
+      </c>
+      <c r="Y3">
+        <v>0.2893788087023156</v>
       </c>
       <c r="AB3">
-        <v>0.04387296409148227</v>
+        <v>0.07243421116593447</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-18.325</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.001924525144339386</v>
+      </c>
+      <c r="AI3">
+        <v>0.03271692745376956</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.06547565877623938</v>
+      </c>
+      <c r="AK3">
+        <v>13.83018867924529</v>
       </c>
       <c r="AL3">
-        <v>9.9</v>
+        <v>0.028</v>
       </c>
       <c r="AM3">
-        <v>9.9</v>
+        <v>0.028</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.04956896551724137</v>
       </c>
       <c r="AO3">
-        <v>1.959595959595959</v>
+        <v>403.5714285714286</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-1.579741379310345</v>
       </c>
       <c r="AQ3">
-        <v>1.959595959595959</v>
+        <v>403.5714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cadence Opportunities Fund Limited (ASX:CDO)</t>
+          <t>Centrepoint Alliance Limited (ASX:CAF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,41 +849,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.121</v>
+      </c>
+      <c r="E4">
+        <v>-0.00159</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.01532104259376987</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.01532104259376987</v>
       </c>
       <c r="I4">
-        <v>0.8124191461836998</v>
+        <v>0.01176096630642085</v>
       </c>
       <c r="J4">
-        <v>0.5715511581191858</v>
+        <v>0.01176096630642085</v>
       </c>
       <c r="K4">
-        <v>4.19</v>
+        <v>4.47</v>
       </c>
       <c r="L4">
-        <v>0.5420439844760673</v>
+        <v>0.02841703750794659</v>
       </c>
       <c r="M4">
-        <v>0.233</v>
+        <v>2.69</v>
       </c>
       <c r="N4">
-        <v>0.01170854271356784</v>
+        <v>0.09853479853479853</v>
       </c>
       <c r="O4">
-        <v>0.05560859188544152</v>
+        <v>0.6017897091722595</v>
       </c>
       <c r="P4">
-        <v>0.233</v>
+        <v>2.69</v>
       </c>
       <c r="Q4">
-        <v>0.01170854271356784</v>
+        <v>0.09853479853479853</v>
       </c>
       <c r="R4">
-        <v>0.05560859188544152</v>
+        <v>0.6017897091722595</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,46 +898,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.3736263736263736</v>
+      </c>
+      <c r="W4">
+        <v>0.5385542168674698</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07395571496713629</v>
+      </c>
+      <c r="Y4">
+        <v>0.4645985019003336</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07183130229348557</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-8.459999999999999</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.05991735537190083</v>
+      </c>
+      <c r="AI4">
+        <v>0.08192090395480227</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.449044585987261</v>
+      </c>
+      <c r="AK4">
+        <v>-0.7663043478260868</v>
       </c>
       <c r="AL4">
-        <v>0.041</v>
+        <v>0.083</v>
       </c>
       <c r="AM4">
-        <v>0.041</v>
+        <v>0.083</v>
+      </c>
+      <c r="AN4">
+        <v>0.7219917012448133</v>
       </c>
       <c r="AO4">
-        <v>153.1707317073171</v>
+        <v>22.28915662650602</v>
+      </c>
+      <c r="AP4">
+        <v>-3.510373443983402</v>
       </c>
       <c r="AQ4">
-        <v>153.1707317073171</v>
+        <v>22.28915662650602</v>
       </c>
     </row>
     <row r="5">
@@ -924,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Strategic Elements Ltd (ASX:SOR)</t>
+          <t>Eildon Capital Fund (ASX:EDC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -932,113 +974,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.178</v>
+      </c>
+      <c r="E5">
+        <v>-0.09329999999999999</v>
+      </c>
       <c r="G5">
-        <v>-17.05263157894737</v>
+        <v>0.6078665077473182</v>
       </c>
       <c r="H5">
-        <v>-17.05263157894737</v>
+        <v>0.6078665077473182</v>
       </c>
       <c r="I5">
-        <v>-17.14092598769729</v>
+        <v>0.6066746126340882</v>
       </c>
       <c r="J5">
-        <v>-17.14092598769729</v>
+        <v>0.5480593276502027</v>
       </c>
       <c r="K5">
-        <v>-1.77</v>
+        <v>1.54</v>
       </c>
       <c r="L5">
-        <v>-18.63157894736842</v>
+        <v>0.1835518474374255</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>2.68</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.74025974025974</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2.68</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.74025974025974</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>5.86</v>
+        <v>5.64</v>
       </c>
       <c r="V5">
-        <v>0.07690288713910762</v>
+        <v>0.2104477611940298</v>
       </c>
       <c r="W5">
-        <v>-1.149350649350649</v>
+        <v>0.2308845577211394</v>
       </c>
       <c r="X5">
-        <v>0.04387347682831134</v>
+        <v>0.07257640394789369</v>
       </c>
       <c r="Y5">
-        <v>-1.193224126178961</v>
-      </c>
-      <c r="Z5">
-        <v>-3.385583477471716</v>
-      </c>
-      <c r="AA5">
-        <v>58.03203581251351</v>
+        <v>0.1583081537732458</v>
       </c>
       <c r="AB5">
-        <v>0.04387291255636398</v>
-      </c>
-      <c r="AC5">
-        <v>57.98816289995715</v>
+        <v>0.07237276498027213</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AE5">
-        <v>0.001939844156215004</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.001939844156215004</v>
+        <v>0.139</v>
       </c>
       <c r="AG5">
-        <v>-5.858060155843785</v>
+        <v>-5.500999999999999</v>
       </c>
       <c r="AH5">
-        <v>2.545662433505315e-05</v>
+        <v>0.005159805486469432</v>
       </c>
       <c r="AI5">
-        <v>0.0003349213231508631</v>
+        <v>0.0036734586009144</v>
       </c>
       <c r="AJ5">
-        <v>-0.08327976408985051</v>
+        <v>-0.2582750363866848</v>
       </c>
       <c r="AK5">
-        <v>86.0718005008612</v>
+        <v>-0.1708438150253113</v>
       </c>
       <c r="AL5">
-        <v>0.002</v>
+        <v>0.303</v>
       </c>
       <c r="AM5">
-        <v>-0.002</v>
+        <v>0.303</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>0.02725490196078432</v>
       </c>
       <c r="AO5">
-        <v>-814.9999999999999</v>
+        <v>16.7986798679868</v>
       </c>
       <c r="AP5">
-        <v>3.620556338593192</v>
+        <v>-1.078627450980392</v>
       </c>
       <c r="AQ5">
-        <v>814.9999999999999</v>
+        <v>16.7986798679868</v>
       </c>
     </row>
     <row r="6">
@@ -1049,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Australian Ethical Investment Ltd. (ASX:AEF)</t>
+          <t>Netwealth Group Limited (ASX:NWL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1058,121 +1100,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.206</v>
+        <v>0.231</v>
       </c>
       <c r="E6">
-        <v>0.284</v>
+        <v>0.326</v>
+      </c>
+      <c r="F6">
+        <v>0.236</v>
       </c>
       <c r="G6">
-        <v>0.2954545454545455</v>
+        <v>0.4782244556113903</v>
       </c>
       <c r="H6">
-        <v>0.2954545454545455</v>
+        <v>0.4782244556113903</v>
       </c>
       <c r="I6">
-        <v>0.2886363636363636</v>
+        <v>0.4731993299832495</v>
       </c>
       <c r="J6">
-        <v>0.2070219435736677</v>
+        <v>0.3242134944250171</v>
       </c>
       <c r="K6">
-        <v>8.34</v>
+        <v>38.3</v>
       </c>
       <c r="L6">
-        <v>0.1895454545454545</v>
+        <v>0.3207705192629816</v>
       </c>
       <c r="M6">
-        <v>5.859999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="N6">
-        <v>0.005200106486822255</v>
+        <v>0.01635339283043327</v>
       </c>
       <c r="O6">
-        <v>0.7026378896882494</v>
+        <v>0.856396866840731</v>
       </c>
       <c r="P6">
-        <v>4.63</v>
+        <v>32.8</v>
       </c>
       <c r="Q6">
-        <v>0.004108616558700861</v>
+        <v>0.01635339283043327</v>
       </c>
       <c r="R6">
-        <v>0.5551558752997602</v>
+        <v>0.856396866840731</v>
       </c>
       <c r="S6">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.2098976109215016</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>20.9</v>
+        <v>60.9</v>
       </c>
       <c r="V6">
-        <v>0.01854645487620907</v>
+        <v>0.03036346412723737</v>
       </c>
       <c r="W6">
-        <v>0.5791666666666666</v>
+        <v>0.5479256080114449</v>
       </c>
       <c r="X6">
-        <v>0.04389405422222996</v>
+        <v>0.07257637226133423</v>
       </c>
       <c r="Y6">
-        <v>0.5352726124444367</v>
+        <v>0.4753492357501106</v>
       </c>
       <c r="Z6">
-        <v>60.27397260273969</v>
+        <v>5.632075471698113</v>
       </c>
       <c r="AA6">
-        <v>12.47803495512517</v>
+        <v>1.825994869544672</v>
       </c>
       <c r="AB6">
-        <v>0.04386861562478402</v>
+        <v>0.07240059017139927</v>
       </c>
       <c r="AC6">
-        <v>12.43416633950038</v>
+        <v>1.753594279373272</v>
       </c>
       <c r="AD6">
-        <v>1.18</v>
+        <v>10.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.18</v>
+        <v>10.4</v>
       </c>
       <c r="AG6">
-        <v>-19.72</v>
+        <v>-50.5</v>
       </c>
       <c r="AH6">
-        <v>0.00104602510460251</v>
+        <v>0.005158474282029661</v>
       </c>
       <c r="AI6">
-        <v>0.06120331950207468</v>
+        <v>0.1265206812652068</v>
       </c>
       <c r="AJ6">
-        <v>-0.01781101537238751</v>
+        <v>-0.0258285597381342</v>
       </c>
       <c r="AK6">
-        <v>12.17283950617286</v>
+        <v>-2.370892018779343</v>
       </c>
       <c r="AL6">
-        <v>0.043</v>
+        <v>0.342</v>
       </c>
       <c r="AM6">
-        <v>0.043</v>
+        <v>0.342</v>
       </c>
       <c r="AN6">
-        <v>0.09076923076923077</v>
+        <v>0.1821366024518389</v>
       </c>
       <c r="AO6">
-        <v>295.3488372093024</v>
+        <v>165.2046783625731</v>
       </c>
       <c r="AP6">
-        <v>-1.516923076923077</v>
+        <v>-0.8844133099824868</v>
       </c>
       <c r="AQ6">
-        <v>295.3488372093024</v>
+        <v>165.2046783625731</v>
       </c>
     </row>
     <row r="7">
@@ -1192,121 +1237,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.222</v>
+        <v>0.0823</v>
       </c>
       <c r="E7">
-        <v>0.236</v>
+        <v>0.0872</v>
       </c>
       <c r="G7">
-        <v>0.8538011695906432</v>
+        <v>0.7924528301886792</v>
       </c>
       <c r="H7">
-        <v>0.8538011695906432</v>
+        <v>0.7924528301886792</v>
       </c>
       <c r="I7">
-        <v>0.8421052631578947</v>
+        <v>0.7861635220125786</v>
       </c>
       <c r="J7">
-        <v>0.6202540834845734</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="K7">
-        <v>10.5</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L7">
-        <v>0.6140350877192982</v>
+        <v>0.6113207547169811</v>
       </c>
       <c r="M7">
-        <v>7.039399999999999</v>
+        <v>10.106</v>
       </c>
       <c r="N7">
-        <v>0.08390226460071512</v>
+        <v>0.167317880794702</v>
       </c>
       <c r="O7">
-        <v>0.6704190476190475</v>
+        <v>1.039711934156379</v>
       </c>
       <c r="P7">
-        <v>6.744399999999999</v>
+        <v>9.99</v>
       </c>
       <c r="Q7">
-        <v>0.08038617401668652</v>
+        <v>0.1653973509933775</v>
       </c>
       <c r="R7">
-        <v>0.6423238095238094</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="S7">
-        <v>0.2949999999999999</v>
+        <v>0.1159999999999997</v>
       </c>
       <c r="T7">
-        <v>0.04190698070858311</v>
+        <v>0.01147832970512563</v>
       </c>
       <c r="U7">
-        <v>8.859999999999999</v>
+        <v>4.64</v>
       </c>
       <c r="V7">
-        <v>0.1056019070321812</v>
+        <v>0.07682119205298013</v>
       </c>
       <c r="W7">
-        <v>1.581325301204819</v>
+        <v>0.648</v>
       </c>
       <c r="X7">
-        <v>0.04388904814411506</v>
+        <v>0.07264650498426359</v>
       </c>
       <c r="Y7">
-        <v>1.537436253060704</v>
+        <v>0.5753534950157364</v>
       </c>
       <c r="Z7">
-        <v>3.928325292901448</v>
+        <v>2.561623972933784</v>
       </c>
       <c r="AA7">
-        <v>2.436559804177856</v>
+        <v>1.594973417109715</v>
       </c>
       <c r="AB7">
-        <v>0.04386964697893858</v>
+        <v>0.0723700491197596</v>
       </c>
       <c r="AC7">
-        <v>2.392690157198918</v>
+        <v>1.522603367989955</v>
       </c>
       <c r="AD7">
-        <v>0.067</v>
+        <v>0.493</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.067</v>
+        <v>0.493</v>
       </c>
       <c r="AG7">
-        <v>-8.792999999999999</v>
+        <v>-4.146999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.0007979325211094836</v>
+        <v>0.008096168689340318</v>
       </c>
       <c r="AI7">
-        <v>0.004446804274241721</v>
+        <v>0.03653746387015489</v>
       </c>
       <c r="AJ7">
-        <v>-0.1170729758877335</v>
+        <v>-0.07372051268376796</v>
       </c>
       <c r="AK7">
-        <v>-1.416626389560174</v>
+        <v>-0.4684287812041115</v>
       </c>
       <c r="AL7">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AM7">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AN7">
-        <v>0.004589041095890411</v>
+        <v>0.03912698412698413</v>
       </c>
       <c r="AO7">
-        <v>2880</v>
+        <v>2083.333333333333</v>
       </c>
       <c r="AP7">
-        <v>-0.6022602739726027</v>
+        <v>-0.3291269841269841</v>
       </c>
       <c r="AQ7">
-        <v>2880</v>
+        <v>2083.333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -1317,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bentley Capital Limited (ASX:BEL)</t>
+          <t>Advanced Share Registry Limited (ASX:ASW)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1326,115 +1371,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>-0.009220000000000001</v>
       </c>
       <c r="E8">
-        <v>0.8179999999999999</v>
+        <v>-0.0308</v>
       </c>
       <c r="G8">
-        <v>0.8632855567805954</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="H8">
-        <v>0.8632855567805954</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I8">
-        <v>0.8632855567805954</v>
+        <v>0.4110275689223057</v>
       </c>
       <c r="J8">
-        <v>0.8632855567805954</v>
+        <v>0.3056229530882421</v>
       </c>
       <c r="K8">
-        <v>7.82</v>
+        <v>1.21</v>
       </c>
       <c r="L8">
-        <v>0.8621830209481808</v>
+        <v>0.3032581453634085</v>
       </c>
       <c r="M8">
-        <v>0.001</v>
+        <v>1.55</v>
       </c>
       <c r="N8">
-        <v>0.0002288329519450801</v>
+        <v>0.0625</v>
       </c>
       <c r="O8">
-        <v>0.0001278772378516624</v>
+        <v>1.28099173553719</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.55</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.0625</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>1.28099173553719</v>
       </c>
       <c r="S8">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0.717</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>0.1640732265446224</v>
+        <v>0.1161290322580645</v>
       </c>
       <c r="W8">
-        <v>2.172222222222222</v>
+        <v>0.1881804043545879</v>
       </c>
       <c r="X8">
-        <v>0.04387296409148227</v>
+        <v>0.07271164667586702</v>
       </c>
       <c r="Y8">
-        <v>2.12834925813074</v>
+        <v>0.1154687576787209</v>
       </c>
       <c r="Z8">
-        <v>2.559255079006772</v>
+        <v>2.254237288135594</v>
       </c>
       <c r="AA8">
-        <v>2.209367945823928</v>
+        <v>0.6889466569616305</v>
       </c>
       <c r="AB8">
-        <v>0.04387296409148227</v>
+        <v>0.07234184266927933</v>
       </c>
       <c r="AC8">
-        <v>2.165494981732446</v>
+        <v>0.6166048142923511</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="AG8">
-        <v>-0.717</v>
+        <v>-2.609</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.01080930158350285</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.04647573315040303</v>
       </c>
       <c r="AJ8">
-        <v>-0.196277032575965</v>
+        <v>-0.1175701861114866</v>
       </c>
       <c r="AK8">
-        <v>-0.06528270964217428</v>
+        <v>-0.8841070823449679</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>0.1584795321637427</v>
+      </c>
+      <c r="AO8">
+        <v>126.1538461538461</v>
       </c>
       <c r="AP8">
-        <v>-0.09157088122605364</v>
+        <v>-1.525730994152047</v>
+      </c>
+      <c r="AQ8">
+        <v>126.1538461538461</v>
       </c>
     </row>
     <row r="9">
@@ -1445,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Magellan Financial Group Limited (ASX:MFG)</t>
+          <t>Pengana Capital Group Limited (ASX:PCG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,124 +1505,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.166</v>
-      </c>
-      <c r="E9">
-        <v>0.05980000000000001</v>
-      </c>
-      <c r="F9">
-        <v>0.028</v>
+        <v>0.119</v>
       </c>
       <c r="G9">
-        <v>0.8495460440985733</v>
+        <v>0.3929889298892989</v>
       </c>
       <c r="H9">
-        <v>0.8495460440985733</v>
+        <v>0.3929889298892989</v>
       </c>
       <c r="I9">
-        <v>0.8429011375947946</v>
+        <v>0.3597785977859778</v>
       </c>
       <c r="J9">
-        <v>0.6628510528237546</v>
+        <v>0.2404234756633281</v>
       </c>
       <c r="K9">
-        <v>198.8</v>
+        <v>12.9</v>
       </c>
       <c r="L9">
-        <v>0.3683527885862516</v>
+        <v>0.2380073800738007</v>
       </c>
       <c r="M9">
-        <v>257.2</v>
+        <v>12.427</v>
       </c>
       <c r="N9">
-        <v>0.08974180041870201</v>
+        <v>0.1331939978563773</v>
       </c>
       <c r="O9">
-        <v>1.293762575452716</v>
+        <v>0.9633333333333333</v>
       </c>
       <c r="P9">
-        <v>257.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q9">
-        <v>0.08974180041870201</v>
+        <v>0.1232583065380493</v>
       </c>
       <c r="R9">
-        <v>1.293762575452716</v>
+        <v>0.8914728682170543</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>0.9269999999999996</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.07459563852900938</v>
       </c>
       <c r="U9">
-        <v>158.6</v>
+        <v>17.7</v>
       </c>
       <c r="V9">
-        <v>0.05533845080251221</v>
+        <v>0.1897106109324759</v>
       </c>
       <c r="W9">
-        <v>0.2753081290679961</v>
+        <v>0.2208904109589041</v>
       </c>
       <c r="X9">
-        <v>0.04394971437833793</v>
+        <v>0.07272186567016041</v>
       </c>
       <c r="Y9">
-        <v>0.2313584146896582</v>
+        <v>0.1481685452887437</v>
       </c>
       <c r="Z9">
-        <v>1.502416559784114</v>
+        <v>2.640038967364831</v>
       </c>
       <c r="AA9">
-        <v>0.9958783984327436</v>
+        <v>0.6347273444204762</v>
       </c>
       <c r="AB9">
-        <v>0.04384491187967717</v>
+        <v>0.072337431825201</v>
       </c>
       <c r="AC9">
-        <v>0.9520334865530664</v>
+        <v>0.5623899125952752</v>
       </c>
       <c r="AD9">
-        <v>10.9</v>
+        <v>1.06</v>
       </c>
       <c r="AE9">
-        <v>0.021280200446357</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>10.92128020044636</v>
+        <v>1.06</v>
       </c>
       <c r="AG9">
-        <v>-147.6787197995536</v>
+        <v>-16.64</v>
       </c>
       <c r="AH9">
-        <v>0.003796169285412436</v>
+        <v>0.01123357354811361</v>
       </c>
       <c r="AI9">
-        <v>0.01450906263409754</v>
+        <v>0.01730329742082925</v>
       </c>
       <c r="AJ9">
-        <v>-0.05432717643613633</v>
+        <v>-0.2170623532481085</v>
       </c>
       <c r="AK9">
-        <v>-0.2485666222050309</v>
+        <v>-0.3820018365472911</v>
       </c>
       <c r="AL9">
-        <v>0.115</v>
+        <v>0.077</v>
       </c>
       <c r="AM9">
-        <v>0.115</v>
+        <v>0.077</v>
       </c>
       <c r="AN9">
-        <v>0.02377224013015847</v>
+        <v>0.04976525821596244</v>
       </c>
       <c r="AO9">
-        <v>3955.652173913043</v>
+        <v>253.2467532467533</v>
       </c>
       <c r="AP9">
-        <v>-0.322078347632053</v>
+        <v>-0.7812206572769953</v>
       </c>
       <c r="AQ9">
-        <v>3955.652173913043</v>
+        <v>253.2467532467533</v>
       </c>
     </row>
     <row r="10">
@@ -1582,7 +1627,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VGI Partners Limited (ASX:VGI)</t>
+          <t>Fiducian Group Ltd (ASX:FID)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1590,41 +1635,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.113</v>
+      </c>
+      <c r="E10">
+        <v>0.121</v>
+      </c>
       <c r="G10">
-        <v>0.3747706422018349</v>
+        <v>0.3110647181628393</v>
       </c>
       <c r="H10">
-        <v>0.356651376146789</v>
+        <v>0.3110647181628393</v>
       </c>
       <c r="I10">
-        <v>0.8291284403669724</v>
+        <v>0.2734864300626305</v>
       </c>
       <c r="J10">
-        <v>0.5714105988464366</v>
+        <v>0.1908141962421712</v>
       </c>
       <c r="K10">
-        <v>49</v>
+        <v>9.18</v>
       </c>
       <c r="L10">
-        <v>0.5619266055045872</v>
+        <v>0.1916492693110647</v>
       </c>
       <c r="M10">
-        <v>17.3</v>
+        <v>6.38</v>
       </c>
       <c r="N10">
-        <v>0.07012565869477098</v>
+        <v>0.0447719298245614</v>
       </c>
       <c r="O10">
-        <v>0.3530612244897959</v>
+        <v>0.6949891067538126</v>
       </c>
       <c r="P10">
-        <v>17.3</v>
+        <v>6.38</v>
       </c>
       <c r="Q10">
-        <v>0.07012565869477098</v>
+        <v>0.0447719298245614</v>
       </c>
       <c r="R10">
-        <v>0.3530612244897959</v>
+        <v>0.6949891067538126</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1633,73 +1684,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="V10">
-        <v>0.1053911633563032</v>
+        <v>0.08421052631578947</v>
       </c>
       <c r="W10">
-        <v>0.6242038216560509</v>
+        <v>0.2859813084112149</v>
       </c>
       <c r="X10">
-        <v>0.04394578873185001</v>
+        <v>0.0731171481133172</v>
       </c>
       <c r="Y10">
-        <v>0.5802580329242009</v>
+        <v>0.2128641602978977</v>
       </c>
       <c r="Z10">
-        <v>1.705123191239734</v>
+        <v>3.170086035737921</v>
       </c>
       <c r="AA10">
-        <v>0.9743254638132433</v>
+        <v>0.6048974189278623</v>
       </c>
       <c r="AB10">
-        <v>0.04384634153330767</v>
+        <v>0.07202214665311378</v>
       </c>
       <c r="AC10">
-        <v>0.9304791222799356</v>
+        <v>0.5328752722747485</v>
       </c>
       <c r="AD10">
-        <v>0.892</v>
+        <v>4.01</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.892</v>
+        <v>4.01</v>
       </c>
       <c r="AG10">
-        <v>-25.108</v>
+        <v>-7.99</v>
       </c>
       <c r="AH10">
-        <v>0.003602701218133058</v>
+        <v>0.02737014538256774</v>
       </c>
       <c r="AI10">
-        <v>0.007553432916709007</v>
+        <v>0.1098329224869899</v>
       </c>
       <c r="AJ10">
-        <v>-0.1133073396151486</v>
+        <v>-0.05940078804549848</v>
       </c>
       <c r="AK10">
-        <v>-0.2726404030751857</v>
+        <v>-0.3259893920848634</v>
       </c>
       <c r="AL10">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.264</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>0.01226960110041265</v>
-      </c>
-      <c r="AO10">
-        <v>273.8636363636363</v>
+        <v>0.2691275167785235</v>
       </c>
       <c r="AP10">
-        <v>-0.3453645116918844</v>
-      </c>
-      <c r="AQ10">
-        <v>273.8636363636363</v>
+        <v>-0.536241610738255</v>
       </c>
     </row>
     <row r="11">
@@ -1710,7 +1755,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advanced Share Registry Limited (ASX:ASW)</t>
+          <t>Prime Financial Group Limited (ASX:PFG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1719,115 +1764,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0208</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E11">
-        <v>0.067</v>
+        <v>0.0547</v>
       </c>
       <c r="G11">
-        <v>0.5217391304347827</v>
+        <v>0.2911602209944751</v>
       </c>
       <c r="H11">
-        <v>0.5217391304347827</v>
+        <v>0.2823204419889503</v>
       </c>
       <c r="I11">
-        <v>0.5146515575170121</v>
+        <v>0.2569060773480663</v>
       </c>
       <c r="J11">
-        <v>0.3837944173111361</v>
+        <v>0.1951338716532087</v>
       </c>
       <c r="K11">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="L11">
-        <v>0.3794466403162056</v>
+        <v>0.1453038674033149</v>
       </c>
       <c r="M11">
-        <v>1.45</v>
+        <v>1.694</v>
       </c>
       <c r="N11">
-        <v>0.04119318181818182</v>
+        <v>0.05646666666666667</v>
       </c>
       <c r="O11">
-        <v>0.7552083333333334</v>
+        <v>0.644106463878327</v>
       </c>
       <c r="P11">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="Q11">
-        <v>0.04119318181818182</v>
+        <v>0.041</v>
       </c>
       <c r="R11">
-        <v>0.7552083333333334</v>
+        <v>0.467680608365019</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.464</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.2739079102715467</v>
       </c>
       <c r="U11">
-        <v>3.87</v>
+        <v>0.089</v>
       </c>
       <c r="V11">
-        <v>0.1099431818181818</v>
+        <v>0.002966666666666666</v>
       </c>
       <c r="W11">
-        <v>0.3471971066907775</v>
+        <v>0.08193146417445482</v>
       </c>
       <c r="X11">
-        <v>0.04388973817074208</v>
+        <v>0.07631772338657777</v>
       </c>
       <c r="Y11">
-        <v>0.3033073685200354</v>
+        <v>0.005613740787877047</v>
       </c>
       <c r="Z11">
-        <v>2.49099648174039</v>
+        <v>2.746169018358367</v>
       </c>
       <c r="AA11">
-        <v>0.956030543233643</v>
+        <v>0.5358705927663597</v>
       </c>
       <c r="AB11">
-        <v>0.04386681492795315</v>
+        <v>0.07023003727369226</v>
       </c>
       <c r="AC11">
-        <v>0.9121637283056898</v>
+        <v>0.4656405554926675</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="AE11">
-        <v>0.02931559481959467</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.02931559481959467</v>
+        <v>4.92</v>
       </c>
       <c r="AG11">
-        <v>-3.840684405180405</v>
+        <v>4.831</v>
       </c>
       <c r="AH11">
-        <v>0.00083213637065108</v>
+        <v>0.140893470790378</v>
       </c>
       <c r="AI11">
-        <v>0.004538498605503334</v>
+        <v>0.13290113452188</v>
       </c>
       <c r="AJ11">
-        <v>-0.1224734766155058</v>
+        <v>0.1386982860095891</v>
       </c>
       <c r="AK11">
-        <v>-1.48328168758741</v>
+        <v>0.1308115133627576</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.9628180039138943</v>
+      </c>
+      <c r="AO11">
+        <v>17.4812030075188</v>
       </c>
       <c r="AP11">
-        <v>-1.438458578719253</v>
+        <v>0.9454011741682973</v>
+      </c>
+      <c r="AQ11">
+        <v>17.4812030075188</v>
       </c>
     </row>
     <row r="12">
@@ -1838,7 +1889,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NGE Capital Limited (ASX:NGE)</t>
+          <t>Platinum Investment Management Limited (ASX:PTM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1847,118 +1898,124 @@
         </is>
       </c>
       <c r="D12">
-        <v>1.023</v>
+        <v>-0.0693</v>
+      </c>
+      <c r="E12">
+        <v>-0.114</v>
+      </c>
+      <c r="F12">
+        <v>-0.169</v>
       </c>
       <c r="G12">
-        <v>-0.06043577981651376</v>
+        <v>0.7027431421446384</v>
       </c>
       <c r="H12">
-        <v>-0.06043577981651376</v>
+        <v>0.678927680798005</v>
       </c>
       <c r="I12">
-        <v>0.9197247706422017</v>
+        <v>0.6754442685180488</v>
       </c>
       <c r="J12">
-        <v>0.9197247706422017</v>
+        <v>0.4669985595391851</v>
       </c>
       <c r="K12">
-        <v>7.02</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L12">
-        <v>0.8050458715596329</v>
+        <v>0.435785536159601</v>
       </c>
       <c r="M12">
-        <v>0.422</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="N12">
-        <v>0.02099502487562189</v>
+        <v>0.136780949648544</v>
       </c>
       <c r="O12">
-        <v>0.06011396011396011</v>
+        <v>1.364091559370529</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>87.8</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.1259503658011763</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>1.256080114449213</v>
       </c>
       <c r="S12">
-        <v>0.422</v>
+        <v>7.549999999999997</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0.07918196119559515</v>
       </c>
       <c r="U12">
-        <v>12.8</v>
+        <v>60.3</v>
       </c>
       <c r="V12">
-        <v>0.6368159203980099</v>
+        <v>0.08650121933725433</v>
       </c>
       <c r="W12">
-        <v>0.4178571428571428</v>
+        <v>0.2726209048361935</v>
       </c>
       <c r="X12">
-        <v>0.04387697226558458</v>
+        <v>0.0725781997958653</v>
       </c>
       <c r="Y12">
-        <v>0.3739801705915582</v>
+        <v>0.2000427050403282</v>
       </c>
       <c r="Z12">
-        <v>0.9245122985581001</v>
+        <v>1.039003460206585</v>
       </c>
       <c r="AA12">
-        <v>0.8502968617472434</v>
+        <v>0.4852131192727045</v>
       </c>
       <c r="AB12">
-        <v>0.04387149381485269</v>
+        <v>0.0723715740532959</v>
       </c>
       <c r="AC12">
-        <v>0.8064253679323907</v>
+        <v>0.4128415452194086</v>
       </c>
       <c r="AD12">
-        <v>0.004</v>
+        <v>3.62</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.048696648524778</v>
       </c>
       <c r="AF12">
-        <v>0.004</v>
+        <v>3.668696648524778</v>
       </c>
       <c r="AG12">
-        <v>-12.796</v>
+        <v>-56.63130335147522</v>
       </c>
       <c r="AH12">
-        <v>0.0001989653800238758</v>
+        <v>0.005235246189035805</v>
       </c>
       <c r="AI12">
-        <v>0.0001612643122077084</v>
+        <v>0.01619242509134443</v>
       </c>
       <c r="AJ12">
-        <v>-1.751916757940854</v>
+        <v>-0.08842165690191919</v>
       </c>
       <c r="AK12">
-        <v>-1.06597800733089</v>
+        <v>-0.3406011142986708</v>
       </c>
       <c r="AL12">
-        <v>0.004</v>
+        <v>0.105</v>
       </c>
       <c r="AM12">
-        <v>0.004</v>
+        <v>0.105</v>
       </c>
       <c r="AN12">
-        <v>0.0004975124378109454</v>
+        <v>0.03322594560857633</v>
       </c>
       <c r="AO12">
-        <v>2005</v>
+        <v>1031.428571428571</v>
       </c>
       <c r="AP12">
-        <v>-1.591542288557214</v>
+        <v>-0.5197869074306359</v>
       </c>
       <c r="AQ12">
-        <v>2005</v>
+        <v>1031.428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -1969,7 +2026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Platinum Investment Management Limited (ASX:PTM)</t>
+          <t>Diverger Limited (ASX:DVR)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1978,124 +2035,121 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0133</v>
+        <v>0.483</v>
       </c>
       <c r="E13">
-        <v>-0.0406</v>
-      </c>
-      <c r="F13">
-        <v>0.005</v>
+        <v>0.186</v>
       </c>
       <c r="G13">
-        <v>0.7957527333894029</v>
+        <v>0.05205640423031727</v>
       </c>
       <c r="H13">
-        <v>0.7792262405382675</v>
+        <v>0.05205640423031727</v>
       </c>
       <c r="I13">
-        <v>0.7752646278994391</v>
+        <v>0.04477085781433608</v>
       </c>
       <c r="J13">
-        <v>0.5403894672829803</v>
+        <v>0.03088470940133345</v>
       </c>
       <c r="K13">
-        <v>122.4</v>
+        <v>2.45</v>
       </c>
       <c r="L13">
-        <v>0.5147182506307821</v>
+        <v>0.02878965922444184</v>
       </c>
       <c r="M13">
-        <v>105.49</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>0.09283639883833494</v>
+        <v>0.0416</v>
       </c>
       <c r="O13">
-        <v>0.8618464052287581</v>
+        <v>0.4244897959183673</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>1.04</v>
       </c>
       <c r="Q13">
-        <v>0.08800492827598345</v>
+        <v>0.0416</v>
       </c>
       <c r="R13">
-        <v>0.8169934640522876</v>
+        <v>0.4244897959183673</v>
       </c>
       <c r="S13">
-        <v>5.489999999999995</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.05204284766328558</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>107.4</v>
+        <v>1.74</v>
       </c>
       <c r="V13">
-        <v>0.09451729296840623</v>
+        <v>0.0696</v>
       </c>
       <c r="W13">
-        <v>0.5558583106267031</v>
+        <v>0.09245283018867925</v>
       </c>
       <c r="X13">
-        <v>0.04396868617477118</v>
+        <v>0.07336732531171725</v>
       </c>
       <c r="Y13">
-        <v>0.5118896244519319</v>
+        <v>0.01908550487696201</v>
       </c>
       <c r="Z13">
-        <v>1.547468255952276</v>
+        <v>14.7410358565737</v>
       </c>
       <c r="AA13">
-        <v>0.8362355464713731</v>
+        <v>0.4552726087049154</v>
       </c>
       <c r="AB13">
-        <v>0.04383801049194229</v>
+        <v>0.07186517473883981</v>
       </c>
       <c r="AC13">
-        <v>0.7923975359794309</v>
+        <v>0.3834074339660756</v>
       </c>
       <c r="AD13">
-        <v>5.33</v>
+        <v>0.969</v>
       </c>
       <c r="AE13">
-        <v>0.0703574275670272</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>5.400357427567028</v>
+        <v>0.969</v>
       </c>
       <c r="AG13">
-        <v>-101.999642572433</v>
+        <v>-0.771</v>
       </c>
       <c r="AH13">
-        <v>0.004730100496539122</v>
+        <v>0.03731372020485964</v>
       </c>
       <c r="AI13">
-        <v>0.02062776949821835</v>
+        <v>0.035930142014906</v>
       </c>
       <c r="AJ13">
-        <v>-0.09861704275740435</v>
+        <v>-0.0318213710842379</v>
       </c>
       <c r="AK13">
-        <v>-0.6606179174182515</v>
+        <v>-0.03056006976098934</v>
       </c>
       <c r="AL13">
-        <v>0.148</v>
+        <v>0.063</v>
       </c>
       <c r="AM13">
-        <v>0.148</v>
+        <v>0.063</v>
       </c>
       <c r="AN13">
-        <v>0.02875299397967331</v>
+        <v>0.2187358916478555</v>
       </c>
       <c r="AO13">
-        <v>1245.27027027027</v>
+        <v>60.47619047619047</v>
       </c>
       <c r="AP13">
-        <v>-0.550242984768104</v>
+        <v>-0.1740406320541761</v>
       </c>
       <c r="AQ13">
-        <v>1245.27027027027</v>
+        <v>60.47619047619047</v>
       </c>
     </row>
     <row r="14">
@@ -2106,7 +2160,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tribeca Global Natural Resources Limited (ASX:TGF)</t>
+          <t>Magellan Financial Group Limited (ASX:MFG)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2114,110 +2168,125 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.102</v>
+      </c>
+      <c r="E14">
+        <v>0.143</v>
+      </c>
+      <c r="F14">
+        <v>-0.26</v>
+      </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.7598944591029023</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.7598944591029023</v>
       </c>
       <c r="I14">
-        <v>0.9534109816971713</v>
+        <v>0.7509534194500369</v>
       </c>
       <c r="J14">
-        <v>0.6692705455001686</v>
+        <v>0.5799725121242749</v>
       </c>
       <c r="K14">
-        <v>39.2</v>
+        <v>263.9</v>
       </c>
       <c r="L14">
-        <v>0.6522462562396008</v>
+        <v>0.6963060686015831</v>
       </c>
       <c r="M14">
-        <v>0.577</v>
+        <v>253.25</v>
       </c>
       <c r="N14">
-        <v>0.004999999999999999</v>
+        <v>0.2296219058844863</v>
       </c>
       <c r="O14">
-        <v>0.01471938775510204</v>
+        <v>0.9596438044713907</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>248.5</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.2253150784295947</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.9416445623342176</v>
       </c>
       <c r="S14">
-        <v>0.577</v>
+        <v>4.75</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>0.01875616979269496</v>
       </c>
       <c r="U14">
-        <v>38.8</v>
+        <v>289.3</v>
       </c>
       <c r="V14">
-        <v>0.3362218370883882</v>
+        <v>0.2623084595158219</v>
       </c>
       <c r="W14">
-        <v>0.5421853388658369</v>
+        <v>0.3557562685359935</v>
       </c>
       <c r="X14">
-        <v>0.04387296409148227</v>
+        <v>0.07263926656421707</v>
       </c>
       <c r="Y14">
-        <v>0.4983123747743546</v>
+        <v>0.2831170019717765</v>
       </c>
       <c r="Z14">
-        <v>1.234086242299795</v>
+        <v>0.7330566194089642</v>
       </c>
       <c r="AA14">
-        <v>0.825937572578237</v>
+        <v>0.4251526890879455</v>
       </c>
       <c r="AB14">
-        <v>0.04387296409148227</v>
+        <v>0.07237319292122608</v>
       </c>
       <c r="AC14">
-        <v>0.7820646084867547</v>
+        <v>0.3527794961667194</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.01327014218009479</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>8.663270142180096</v>
       </c>
       <c r="AG14">
-        <v>-38.8</v>
+        <v>-280.6367298578199</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.007793771506206727</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.01209847020984603</v>
       </c>
       <c r="AJ14">
-        <v>-0.506527415143603</v>
+        <v>-0.3412979030539623</v>
       </c>
       <c r="AK14">
-        <v>-0.4948979591836734</v>
+        <v>-0.657593446981328</v>
       </c>
       <c r="AL14">
-        <v>0.439</v>
+        <v>0.377</v>
       </c>
       <c r="AM14">
-        <v>0.439</v>
+        <v>0.377</v>
+      </c>
+      <c r="AN14">
+        <v>0.03003326227197289</v>
       </c>
       <c r="AO14">
-        <v>130.5239179954442</v>
+        <v>754.9071618037136</v>
+      </c>
+      <c r="AP14">
+        <v>-0.9743857238114115</v>
       </c>
       <c r="AQ14">
-        <v>130.5239179954442</v>
+        <v>754.9071618037136</v>
       </c>
     </row>
     <row r="15">
@@ -2228,7 +2297,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Centrepoint Alliance Limited (ASX:CAF)</t>
+          <t>Bailador Technology Investments Limited (ASX:BTI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2237,46 +2306,46 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0367</v>
+        <v>0.527</v>
       </c>
       <c r="E15">
-        <v>-0.154</v>
+        <v>0.578</v>
       </c>
       <c r="G15">
-        <v>0.01517771373679155</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.01517771373679155</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.01181556195965418</v>
+        <v>0.7818448023426061</v>
       </c>
       <c r="J15">
-        <v>0.01181556195965418</v>
+        <v>0.54774156018244</v>
       </c>
       <c r="K15">
-        <v>1.38</v>
+        <v>36.5</v>
       </c>
       <c r="L15">
-        <v>0.01325648414985591</v>
+        <v>0.5344070278184481</v>
       </c>
       <c r="M15">
-        <v>1.08</v>
+        <v>0.897</v>
       </c>
       <c r="N15">
-        <v>0.02918918918918919</v>
+        <v>0.007582417582417583</v>
       </c>
       <c r="O15">
-        <v>0.7826086956521741</v>
+        <v>0.02457534246575343</v>
       </c>
       <c r="P15">
-        <v>1.08</v>
+        <v>0.897</v>
       </c>
       <c r="Q15">
-        <v>0.02918918918918919</v>
+        <v>0.007582417582417583</v>
       </c>
       <c r="R15">
-        <v>0.7826086956521741</v>
+        <v>0.02457534246575343</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2285,73 +2354,61 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>8.34</v>
+        <v>12</v>
       </c>
       <c r="V15">
-        <v>0.2254054054054054</v>
+        <v>0.1014370245139476</v>
       </c>
       <c r="W15">
-        <v>0.1352941176470588</v>
+        <v>0.3074978938500421</v>
       </c>
       <c r="X15">
-        <v>0.04407274177999854</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y15">
-        <v>0.09122137586706028</v>
+        <v>0.2350436748093372</v>
       </c>
       <c r="Z15">
-        <v>60.66433566433568</v>
+        <v>0.584510055626872</v>
       </c>
       <c r="AA15">
-        <v>0.716783216783217</v>
+        <v>0.3201604498113877</v>
       </c>
       <c r="AB15">
-        <v>0.04383213479723826</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC15">
-        <v>0.6729510819859787</v>
+        <v>0.2477062307706828</v>
       </c>
       <c r="AD15">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>-7.973</v>
+        <v>-12</v>
       </c>
       <c r="AH15">
-        <v>0.009821500254235021</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.04190932967911384</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-0.2746753023047507</v>
+        <v>-0.1128880526810913</v>
       </c>
       <c r="AK15">
-        <v>-19.11990407673858</v>
+        <v>-0.07863695937090433</v>
       </c>
       <c r="AL15">
-        <v>0.074</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>0.074</v>
-      </c>
-      <c r="AN15">
-        <v>0.2322784810126582</v>
-      </c>
-      <c r="AO15">
-        <v>16.62162162162162</v>
-      </c>
-      <c r="AP15">
-        <v>-5.046202531645569</v>
-      </c>
-      <c r="AQ15">
-        <v>16.62162162162162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2362,7 +2419,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thorney Technologies Ltd (ASX:TEK)</t>
+          <t>EQT Holdings Limited (ASX:EQT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2370,107 +2427,125 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.0689</v>
+      </c>
+      <c r="E16">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="F16">
+        <v>0.0725</v>
+      </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.3776041666666667</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.3776041666666667</v>
       </c>
       <c r="I16">
-        <v>0.7779632721202003</v>
+        <v>0.3567708333333333</v>
       </c>
       <c r="J16">
-        <v>0.6614357262103506</v>
+        <v>0.2174072265625</v>
       </c>
       <c r="K16">
-        <v>39.6</v>
+        <v>16.7</v>
       </c>
       <c r="L16">
-        <v>0.66110183639399</v>
+        <v>0.2174479166666667</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>11.5</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.02556691863050245</v>
       </c>
       <c r="O16">
-        <v>-0</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>11.5</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.02556691863050245</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>4.89</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="V16">
-        <v>0.03811379579111457</v>
+        <v>0.1658514895509115</v>
       </c>
       <c r="W16">
-        <v>0.66</v>
+        <v>0.08048192771084337</v>
       </c>
       <c r="X16">
-        <v>0.04387296409148227</v>
+        <v>0.07427684415371413</v>
       </c>
       <c r="Y16">
-        <v>0.6161270359085178</v>
+        <v>0.006205083557129232</v>
       </c>
       <c r="Z16">
-        <v>1.057743245629525</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AA16">
-        <v>0.699629171817058</v>
+        <v>0.226859714673913</v>
       </c>
       <c r="AB16">
-        <v>0.04387296409148227</v>
+        <v>0.07132057882860217</v>
       </c>
       <c r="AC16">
-        <v>0.6557562077255757</v>
+        <v>0.1555391358453108</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="AG16">
-        <v>-4.89</v>
+        <v>-39.8</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.07181180354931901</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.1522309711286089</v>
       </c>
       <c r="AJ16">
-        <v>-0.03962401750263349</v>
+        <v>-0.09707317073170731</v>
       </c>
       <c r="AK16">
-        <v>-0.03859206061084366</v>
+        <v>-0.2584415584415584</v>
       </c>
       <c r="AL16">
-        <v>0.001</v>
+        <v>1.36</v>
       </c>
       <c r="AM16">
-        <v>0.001</v>
+        <v>1.36</v>
+      </c>
+      <c r="AN16">
+        <v>1.2</v>
       </c>
       <c r="AO16">
-        <v>46600</v>
+        <v>20.14705882352941</v>
+      </c>
+      <c r="AP16">
+        <v>-1.372413793103448</v>
       </c>
       <c r="AQ16">
-        <v>46600</v>
+        <v>20.14705882352941</v>
       </c>
     </row>
     <row r="17">
@@ -2481,7 +2556,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pendal Group Limited (ASX:PDL)</t>
+          <t>Perpetual Limited (ASX:PPT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2490,124 +2565,124 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.04679999999999999</v>
+        <v>0.0755</v>
       </c>
       <c r="E17">
-        <v>0.0301</v>
+        <v>-0.0592</v>
       </c>
       <c r="F17">
-        <v>0.0634</v>
+        <v>0.0476</v>
       </c>
       <c r="G17">
-        <v>0.3687113857016769</v>
+        <v>0.2373668925459826</v>
       </c>
       <c r="H17">
-        <v>0.3687113857016769</v>
+        <v>0.2373668925459826</v>
       </c>
       <c r="I17">
-        <v>0.352603706972639</v>
+        <v>0.1957405614714424</v>
       </c>
       <c r="J17">
-        <v>0.266575552863345</v>
+        <v>0.1442189971940754</v>
       </c>
       <c r="K17">
-        <v>119.3</v>
+        <v>69.7</v>
       </c>
       <c r="L17">
-        <v>0.2632391879964696</v>
+        <v>0.134946757018393</v>
       </c>
       <c r="M17">
-        <v>105.5</v>
+        <v>87.60000000000001</v>
       </c>
       <c r="N17">
-        <v>0.07350379711558559</v>
+        <v>0.09247334529716036</v>
       </c>
       <c r="O17">
-        <v>0.8843252305113161</v>
+        <v>1.256814921090387</v>
       </c>
       <c r="P17">
-        <v>84.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Q17">
-        <v>0.0586636940012541</v>
+        <v>0.08170590098173758</v>
       </c>
       <c r="R17">
-        <v>0.7057837384744342</v>
+        <v>1.110473457675753</v>
       </c>
       <c r="S17">
-        <v>21.3</v>
+        <v>10.2</v>
       </c>
       <c r="T17">
-        <v>0.2018957345971564</v>
+        <v>0.1164383561643836</v>
       </c>
       <c r="U17">
-        <v>215.7</v>
+        <v>120.8</v>
       </c>
       <c r="V17">
-        <v>0.1502821709747091</v>
+        <v>0.1275203209120659</v>
       </c>
       <c r="W17">
-        <v>0.185796604890204</v>
+        <v>0.1024849286869578</v>
       </c>
       <c r="X17">
-        <v>0.04481455548239492</v>
+        <v>0.0781192689385522</v>
       </c>
       <c r="Y17">
-        <v>0.1409820494078091</v>
+        <v>0.0243656597484056</v>
       </c>
       <c r="Z17">
-        <v>2.501103752759382</v>
+        <v>1.515107069521853</v>
       </c>
       <c r="AA17">
-        <v>0.6667331156604192</v>
+        <v>0.218507222208096</v>
       </c>
       <c r="AB17">
-        <v>0.04354293024308268</v>
+        <v>0.07043884219682622</v>
       </c>
       <c r="AC17">
-        <v>0.6231901854173365</v>
+        <v>0.1480683800112698</v>
       </c>
       <c r="AD17">
-        <v>67.09999999999999</v>
+        <v>227.8</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>67.09999999999999</v>
+        <v>227.8</v>
       </c>
       <c r="AG17">
-        <v>-148.6</v>
+        <v>107</v>
       </c>
       <c r="AH17">
-        <v>0.0446618743343983</v>
+        <v>0.1938558420559953</v>
       </c>
       <c r="AI17">
-        <v>0.06272786762643731</v>
+        <v>0.2631396557698972</v>
       </c>
       <c r="AJ17">
-        <v>-0.1154892360301547</v>
+        <v>0.101489139713554</v>
       </c>
       <c r="AK17">
-        <v>-0.1740046838407494</v>
+        <v>0.1436434420727615</v>
       </c>
       <c r="AL17">
-        <v>1.26</v>
+        <v>6.34</v>
       </c>
       <c r="AM17">
-        <v>1.26</v>
+        <v>6.34</v>
       </c>
       <c r="AN17">
-        <v>0.4015559545182525</v>
+        <v>1.858075040783034</v>
       </c>
       <c r="AO17">
-        <v>126.8253968253968</v>
+        <v>15.94637223974763</v>
       </c>
       <c r="AP17">
-        <v>-0.8892878515858768</v>
+        <v>0.8727569331158239</v>
       </c>
       <c r="AQ17">
-        <v>126.8253968253968</v>
+        <v>15.94637223974763</v>
       </c>
     </row>
     <row r="18">
@@ -2618,7 +2693,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fiducian Group Ltd (ASX:FID)</t>
+          <t>Pendal Group Limited (ASX:PDL)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2627,115 +2702,124 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.107</v>
+        <v>0.0413</v>
       </c>
       <c r="E18">
-        <v>0.158</v>
+        <v>-0.0522</v>
+      </c>
+      <c r="F18">
+        <v>-0.14</v>
       </c>
       <c r="G18">
-        <v>0.3219954648526077</v>
+        <v>0.3244002041858091</v>
       </c>
       <c r="H18">
-        <v>0.3219954648526077</v>
+        <v>0.3244002041858091</v>
       </c>
       <c r="I18">
-        <v>0.2879818594104308</v>
+        <v>0.2743746809596733</v>
       </c>
       <c r="J18">
-        <v>0.2072562358276644</v>
+        <v>0.2077816594350859</v>
       </c>
       <c r="K18">
-        <v>9.130000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L18">
-        <v>0.2070294784580499</v>
+        <v>0.1852986217457886</v>
       </c>
       <c r="M18">
-        <v>5.61</v>
+        <v>144.7</v>
       </c>
       <c r="N18">
-        <v>0.02908242612752722</v>
+        <v>0.1185676827269747</v>
       </c>
       <c r="O18">
-        <v>0.6144578313253012</v>
+        <v>1.993112947658402</v>
       </c>
       <c r="P18">
-        <v>5.61</v>
+        <v>107</v>
       </c>
       <c r="Q18">
-        <v>0.02908242612752722</v>
+        <v>0.08767617174696821</v>
       </c>
       <c r="R18">
-        <v>0.6144578313253012</v>
+        <v>1.473829201101928</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>37.69999999999999</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.2605390463026952</v>
       </c>
       <c r="U18">
-        <v>14.5</v>
+        <v>203.8</v>
       </c>
       <c r="V18">
-        <v>0.07516848107827889</v>
+        <v>0.166994428056375</v>
       </c>
       <c r="W18">
-        <v>0.3471482889733841</v>
+        <v>0.07241172950329143</v>
       </c>
       <c r="X18">
-        <v>0.04433446513294959</v>
+        <v>0.07357961127198244</v>
       </c>
       <c r="Y18">
-        <v>0.3028138238404345</v>
+        <v>-0.001167881768691009</v>
       </c>
       <c r="Z18">
-        <v>2.880470280862181</v>
+        <v>0.8449428509812379</v>
       </c>
       <c r="AA18">
-        <v>0.596995427824951</v>
+        <v>0.1755636277046941</v>
       </c>
       <c r="AB18">
-        <v>0.04370743562146291</v>
+        <v>0.07198022022079249</v>
       </c>
       <c r="AC18">
-        <v>0.553287992203488</v>
+        <v>0.1035834074839016</v>
       </c>
       <c r="AD18">
-        <v>4.42</v>
+        <v>58.3</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>4.42</v>
+        <v>58.3</v>
       </c>
       <c r="AG18">
-        <v>-10.08</v>
+        <v>-145.5</v>
       </c>
       <c r="AH18">
-        <v>0.0224001621731198</v>
+        <v>0.04559318057402049</v>
       </c>
       <c r="AI18">
-        <v>0.1210295728368017</v>
+        <v>0.06415052816901408</v>
       </c>
       <c r="AJ18">
-        <v>-0.05513619954053167</v>
+        <v>-0.1353614289701368</v>
       </c>
       <c r="AK18">
-        <v>-0.4577656675749318</v>
+        <v>-0.2063829787234042</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN18">
-        <v>0.3112676056338028</v>
+        <v>0.4586939417781274</v>
+      </c>
+      <c r="AO18">
+        <v>63.23529411764706</v>
       </c>
       <c r="AP18">
-        <v>-0.7098591549295775</v>
+        <v>-1.144767899291896</v>
+      </c>
+      <c r="AQ18">
+        <v>63.23529411764706</v>
       </c>
     </row>
     <row r="19">
@@ -2746,7 +2830,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandon Capital Investments Limited (ASX:SNC)</t>
+          <t>Insignia Financial Ltd. (ASX:IFL)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2755,46 +2839,49 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.648</v>
+        <v>0.188</v>
       </c>
       <c r="E19">
-        <v>0.76</v>
+        <v>-0.205</v>
+      </c>
+      <c r="F19">
+        <v>-0.205</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.1134076325565687</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.1134076325565687</v>
       </c>
       <c r="I19">
-        <v>0.804245283018868</v>
+        <v>0.07666328942924687</v>
       </c>
       <c r="J19">
-        <v>0.6630292730299668</v>
+        <v>0.05343964827247501</v>
       </c>
       <c r="K19">
-        <v>28</v>
+        <v>25.4</v>
       </c>
       <c r="L19">
-        <v>0.6603773584905661</v>
+        <v>0.0171563660925363</v>
       </c>
       <c r="M19">
-        <v>2.73</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N19">
-        <v>0.02834890965732087</v>
+        <v>0.0560154893844305</v>
       </c>
       <c r="O19">
-        <v>0.0975</v>
+        <v>3.303149606299213</v>
       </c>
       <c r="P19">
-        <v>2.73</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>0.02834890965732087</v>
+        <v>0.0560154893844305</v>
       </c>
       <c r="R19">
-        <v>0.0975</v>
+        <v>3.303149606299213</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2803,61 +2890,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>1.64</v>
+        <v>353.9</v>
       </c>
       <c r="V19">
-        <v>0.01703011422637591</v>
+        <v>0.236279877153158</v>
       </c>
       <c r="W19">
-        <v>0.4903677758318739</v>
+        <v>0.01358870104857693</v>
       </c>
       <c r="X19">
-        <v>0.04387296409148227</v>
+        <v>0.08286482747182368</v>
       </c>
       <c r="Y19">
-        <v>0.4464948117403916</v>
+        <v>-0.06927612642324675</v>
       </c>
       <c r="Z19">
-        <v>0.7619047619047619</v>
+        <v>2.634341637010677</v>
       </c>
       <c r="AA19">
-        <v>0.5051651604037842</v>
+        <v>0.1407782905113867</v>
       </c>
       <c r="AB19">
-        <v>0.04387296409148227</v>
+        <v>0.06761607982002014</v>
       </c>
       <c r="AC19">
-        <v>0.4612921963123019</v>
+        <v>0.07316221069136651</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>661.9</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>661.9</v>
       </c>
       <c r="AG19">
-        <v>-1.64</v>
+        <v>308</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.3064777515395657</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>0.2857821337593368</v>
       </c>
       <c r="AJ19">
-        <v>-0.01732516374392563</v>
+        <v>0.1705615239782922</v>
       </c>
       <c r="AK19">
-        <v>-0.01905647222867766</v>
+        <v>0.1569666700642136</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>20.2</v>
+      </c>
+      <c r="AN19">
+        <v>3.942227516378797</v>
+      </c>
+      <c r="AO19">
+        <v>5.618811881188119</v>
+      </c>
+      <c r="AP19">
+        <v>1.834425253126861</v>
+      </c>
+      <c r="AQ19">
+        <v>5.618811881188119</v>
       </c>
     </row>
     <row r="20">
@@ -2868,7 +2967,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Auctus Investment Group Limited (ASX:AVC)</t>
+          <t>BlackWall Limited (ASX:BWF)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2877,109 +2976,121 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.21</v>
+        <v>-0.183</v>
+      </c>
+      <c r="E20">
+        <v>-0.144</v>
       </c>
       <c r="G20">
-        <v>0.2985781990521327</v>
+        <v>0.3013698630136987</v>
       </c>
       <c r="H20">
-        <v>0.2985781990521327</v>
+        <v>0.3013698630136987</v>
       </c>
       <c r="I20">
-        <v>0.282780410742496</v>
+        <v>0.2945205479452055</v>
       </c>
       <c r="J20">
-        <v>0.282780410742496</v>
+        <v>0.2611568921232877</v>
       </c>
       <c r="K20">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="L20">
-        <v>0.2116903633491311</v>
+        <v>0.2579908675799086</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>2.38</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.08122866894197951</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>2.106194690265487</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>2.38</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.08122866894197951</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>2.106194690265487</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>10.9</v>
+        <v>0.803</v>
       </c>
       <c r="V20">
-        <v>0.1526610644257703</v>
+        <v>0.0274061433447099</v>
       </c>
       <c r="W20">
-        <v>0.2552380952380953</v>
+        <v>0.06848484848484848</v>
       </c>
       <c r="X20">
-        <v>0.04388001628856352</v>
+        <v>0.07271231129389416</v>
       </c>
       <c r="Y20">
-        <v>0.2113580789495317</v>
+        <v>-0.004227462809045679</v>
       </c>
       <c r="Z20">
-        <v>1.680382267056013</v>
+        <v>0.3000616565047612</v>
       </c>
       <c r="AA20">
-        <v>0.475179187682506</v>
+        <v>0.07836316965814893</v>
       </c>
       <c r="AB20">
-        <v>0.04387150902177155</v>
+        <v>0.07234155568384251</v>
       </c>
       <c r="AC20">
-        <v>0.4313076786607344</v>
+        <v>0.006021613974306422</v>
       </c>
       <c r="AD20">
-        <v>0.025</v>
+        <v>0.321</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.025</v>
+        <v>0.321</v>
       </c>
       <c r="AG20">
-        <v>-10.875</v>
+        <v>-0.482</v>
       </c>
       <c r="AH20">
-        <v>0.0003500175008750437</v>
+        <v>0.010836906248945</v>
       </c>
       <c r="AI20">
-        <v>0.001314060446780552</v>
+        <v>0.02028948865432021</v>
       </c>
       <c r="AJ20">
-        <v>-0.1796778190830235</v>
+        <v>-0.01672565757512666</v>
       </c>
       <c r="AK20">
-        <v>-1.338461538461538</v>
+        <v>-0.03209481954987348</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AN20">
-        <v>0.01322751322751323</v>
+        <v>0.2431818181818182</v>
+      </c>
+      <c r="AO20">
+        <v>322.5</v>
       </c>
       <c r="AP20">
-        <v>-5.753968253968254</v>
+        <v>-0.3651515151515152</v>
+      </c>
+      <c r="AQ20">
+        <v>322.5</v>
       </c>
     </row>
     <row r="21">
@@ -2990,7 +3101,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prime Financial Group Limited (ASX:PFG)</t>
+          <t>CVC Limited (ASX:CVC)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2999,46 +3110,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.101</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="E21">
-        <v>-0.0312</v>
+        <v>-0.26</v>
       </c>
       <c r="G21">
-        <v>0.2777844311377246</v>
+        <v>0.2793522267206478</v>
       </c>
       <c r="H21">
-        <v>0.2658682634730539</v>
+        <v>0.2793522267206478</v>
       </c>
       <c r="I21">
-        <v>0.2401197604790419</v>
+        <v>0.2773279352226721</v>
       </c>
       <c r="J21">
-        <v>0.1827284990458643</v>
+        <v>0.2359954064154469</v>
       </c>
       <c r="K21">
-        <v>2.3</v>
+        <v>4.21</v>
       </c>
       <c r="L21">
-        <v>0.1377245508982036</v>
+        <v>0.08522267206477734</v>
       </c>
       <c r="M21">
-        <v>0.795</v>
+        <v>10.4</v>
       </c>
       <c r="N21">
-        <v>0.03022813688212928</v>
+        <v>0.06740116655865197</v>
       </c>
       <c r="O21">
-        <v>0.3456521739130435</v>
+        <v>2.470308788598575</v>
       </c>
       <c r="P21">
-        <v>0.795</v>
+        <v>10.4</v>
       </c>
       <c r="Q21">
-        <v>0.03022813688212928</v>
+        <v>0.06740116655865197</v>
       </c>
       <c r="R21">
-        <v>0.3456521739130435</v>
+        <v>2.470308788598575</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3047,73 +3158,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.049</v>
+        <v>18.2</v>
       </c>
       <c r="V21">
-        <v>0.001863117870722433</v>
+        <v>0.1179520414776409</v>
       </c>
       <c r="W21">
-        <v>0.08333333333333333</v>
+        <v>0.03079736649597659</v>
       </c>
       <c r="X21">
-        <v>0.04957066739902751</v>
+        <v>0.0814773884620526</v>
       </c>
       <c r="Y21">
-        <v>0.03376266593430582</v>
+        <v>-0.05068002196607601</v>
       </c>
       <c r="Z21">
-        <v>2.535681749164894</v>
+        <v>0.3008159785653392</v>
       </c>
       <c r="AA21">
-        <v>0.4633413200828929</v>
+        <v>0.07099118911778758</v>
       </c>
       <c r="AB21">
-        <v>0.04295627534884213</v>
+        <v>0.07031170121693869</v>
       </c>
       <c r="AC21">
-        <v>0.4203850447340508</v>
+        <v>0.000679487900848888</v>
       </c>
       <c r="AD21">
-        <v>7.44</v>
+        <v>59.1</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>7.44</v>
+        <v>59.1</v>
       </c>
       <c r="AG21">
-        <v>7.391</v>
+        <v>40.90000000000001</v>
       </c>
       <c r="AH21">
-        <v>0.2205097806757558</v>
+        <v>0.2769447047797563</v>
       </c>
       <c r="AI21">
-        <v>0.1853512705530643</v>
+        <v>0.3276053215077605</v>
       </c>
       <c r="AJ21">
-        <v>0.2193760945059511</v>
+        <v>0.2095286885245902</v>
       </c>
       <c r="AK21">
-        <v>0.1843555910304058</v>
+        <v>0.2521578298397041</v>
       </c>
       <c r="AL21">
-        <v>0.352</v>
+        <v>3.23</v>
       </c>
       <c r="AM21">
-        <v>0.352</v>
+        <v>3.23</v>
       </c>
       <c r="AN21">
-        <v>1.675675675675676</v>
+        <v>4.282608695652174</v>
       </c>
       <c r="AO21">
-        <v>11.39204545454546</v>
+        <v>4.241486068111455</v>
       </c>
       <c r="AP21">
-        <v>1.664639639639639</v>
+        <v>2.963768115942029</v>
       </c>
       <c r="AQ21">
-        <v>11.39204545454546</v>
+        <v>4.241486068111455</v>
       </c>
     </row>
     <row r="22">
@@ -3124,7 +3235,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Perpetual Limited (ASX:PPT)</t>
+          <t>Navigator Global Investments Limited (ASX:NGI)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3133,124 +3244,121 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0513</v>
+        <v>0.0296</v>
       </c>
       <c r="E22">
-        <v>-0.107</v>
-      </c>
-      <c r="F22">
-        <v>0.0849</v>
+        <v>0.17</v>
       </c>
       <c r="G22">
-        <v>0.2164041726324402</v>
+        <v>0.2461355529131986</v>
       </c>
       <c r="H22">
-        <v>0.2164041726324402</v>
+        <v>0.2461355529131986</v>
       </c>
       <c r="I22">
-        <v>0.1795868275721006</v>
+        <v>0.2175980975029727</v>
       </c>
       <c r="J22">
-        <v>0.1261597463694007</v>
+        <v>0.1841727442322754</v>
       </c>
       <c r="K22">
-        <v>56.1</v>
+        <v>38.7</v>
       </c>
       <c r="L22">
-        <v>0.1147473921047249</v>
+        <v>0.4601664684898931</v>
       </c>
       <c r="M22">
-        <v>60</v>
+        <v>31.4</v>
       </c>
       <c r="N22">
-        <v>0.04095004095004095</v>
+        <v>0.1689989235737352</v>
       </c>
       <c r="O22">
-        <v>1.06951871657754</v>
+        <v>0.8113695090439276</v>
       </c>
       <c r="P22">
-        <v>54.3</v>
+        <v>31.4</v>
       </c>
       <c r="Q22">
-        <v>0.03705978705978705</v>
+        <v>0.1689989235737352</v>
       </c>
       <c r="R22">
-        <v>0.9679144385026737</v>
+        <v>0.8113695090439276</v>
       </c>
       <c r="S22">
-        <v>5.700000000000003</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>0.09500000000000004</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>110.3</v>
+        <v>94</v>
       </c>
       <c r="V22">
-        <v>0.07527982527982527</v>
+        <v>0.5059203444564047</v>
       </c>
       <c r="W22">
-        <v>0.1241699867197875</v>
+        <v>0.1044252563410685</v>
       </c>
       <c r="X22">
-        <v>0.04644077243478163</v>
+        <v>0.07576349020256534</v>
       </c>
       <c r="Y22">
-        <v>0.07772921428500588</v>
+        <v>0.0286617661385032</v>
       </c>
       <c r="Z22">
-        <v>3.34633812457221</v>
+        <v>0.3387031816351188</v>
       </c>
       <c r="AA22">
-        <v>0.422173169062286</v>
+        <v>0.06237989444194263</v>
       </c>
       <c r="AB22">
-        <v>0.04303738345493748</v>
+        <v>0.07117369740272129</v>
       </c>
       <c r="AC22">
-        <v>0.3791357856073486</v>
+        <v>-0.008793802960778661</v>
       </c>
       <c r="AD22">
-        <v>186.8</v>
+        <v>26.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>186.8</v>
+        <v>26.1</v>
       </c>
       <c r="AG22">
-        <v>76.50000000000001</v>
+        <v>-67.90000000000001</v>
       </c>
       <c r="AH22">
-        <v>0.1130750605326877</v>
+        <v>0.123171307220387</v>
       </c>
       <c r="AI22">
-        <v>0.2144907566884832</v>
+        <v>0.05937215650591447</v>
       </c>
       <c r="AJ22">
-        <v>0.04962054874489201</v>
+        <v>-0.5759117896522477</v>
       </c>
       <c r="AK22">
-        <v>0.1005784906652643</v>
+        <v>-0.1964699074074074</v>
       </c>
       <c r="AL22">
-        <v>7.58</v>
+        <v>0.949</v>
       </c>
       <c r="AM22">
-        <v>7.58</v>
+        <v>-70.551</v>
       </c>
       <c r="AN22">
-        <v>1.765595463137996</v>
+        <v>1.260869565217391</v>
       </c>
       <c r="AO22">
-        <v>11.58311345646438</v>
+        <v>19.28345626975764</v>
       </c>
       <c r="AP22">
-        <v>0.7230623818525521</v>
+        <v>-3.280193236714976</v>
       </c>
       <c r="AQ22">
-        <v>11.58311345646438</v>
+        <v>-0.2593868265510056</v>
       </c>
     </row>
     <row r="23">
@@ -3261,7 +3369,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Insignia Financial Ltd. (ASX:IFL)</t>
+          <t>Australian United Investment Company Limited (ASX:AUI)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3270,46 +3378,46 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.07980000000000001</v>
-      </c>
-      <c r="F23">
-        <v>0.135</v>
+        <v>0.08779999999999999</v>
+      </c>
+      <c r="E23">
+        <v>0.103</v>
       </c>
       <c r="G23">
-        <v>0.1757757757757758</v>
+        <v>0.9813432835820896</v>
       </c>
       <c r="H23">
-        <v>0.1757757757757758</v>
+        <v>0.9813432835820896</v>
       </c>
       <c r="I23">
-        <v>0.1359903968499006</v>
+        <v>0.9813432835820896</v>
       </c>
       <c r="J23">
-        <v>0.1359903968499006</v>
+        <v>0.9606324884453472</v>
       </c>
       <c r="K23">
-        <v>-107.6</v>
+        <v>49.6</v>
       </c>
       <c r="L23">
-        <v>-0.1077077077077077</v>
+        <v>0.9253731343283582</v>
       </c>
       <c r="M23">
-        <v>69.2</v>
+        <v>28.9</v>
       </c>
       <c r="N23">
-        <v>0.04053895723491506</v>
+        <v>0.0353214373013933</v>
       </c>
       <c r="O23">
-        <v>-0.6431226765799257</v>
+        <v>0.5826612903225806</v>
       </c>
       <c r="P23">
-        <v>69.2</v>
+        <v>28.9</v>
       </c>
       <c r="Q23">
-        <v>0.04053895723491506</v>
+        <v>0.0353214373013933</v>
       </c>
       <c r="R23">
-        <v>-0.6431226765799257</v>
+        <v>0.5826612903225806</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3318,73 +3426,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>499.4</v>
+        <v>4.64</v>
       </c>
       <c r="V23">
-        <v>0.2925600468658465</v>
+        <v>0.005670985089220239</v>
       </c>
       <c r="W23">
-        <v>-0.08968908893890139</v>
+        <v>0.0603479742061078</v>
       </c>
       <c r="X23">
-        <v>0.0508300473018372</v>
+        <v>0.0757797428850473</v>
       </c>
       <c r="Y23">
-        <v>-0.1405191362407386</v>
+        <v>-0.01543176867893949</v>
       </c>
       <c r="Z23">
-        <v>2.96766785814773</v>
+        <v>0.05830586648391694</v>
       </c>
       <c r="AA23">
-        <v>0.4035743297482043</v>
+        <v>0.05601050961140729</v>
       </c>
       <c r="AB23">
-        <v>0.04280567648422485</v>
+        <v>0.07050143582365397</v>
       </c>
       <c r="AC23">
-        <v>0.3607686532639794</v>
+        <v>-0.01449092621224667</v>
       </c>
       <c r="AD23">
-        <v>579.9</v>
+        <v>115.5</v>
       </c>
       <c r="AE23">
-        <v>9.727967734746699</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>589.6279677347467</v>
+        <v>115.5</v>
       </c>
       <c r="AG23">
-        <v>90.2279677347467</v>
+        <v>110.86</v>
       </c>
       <c r="AH23">
-        <v>0.2567363874421157</v>
+        <v>0.123701403020242</v>
       </c>
       <c r="AI23">
-        <v>0.2398784617077128</v>
+        <v>0.1386388188692834</v>
       </c>
       <c r="AJ23">
-        <v>0.0502039637456073</v>
+        <v>0.1193249090478548</v>
       </c>
       <c r="AK23">
-        <v>0.04606692502154962</v>
+        <v>0.1338145474736258</v>
       </c>
       <c r="AL23">
-        <v>8.32</v>
+        <v>1.93</v>
       </c>
       <c r="AM23">
-        <v>8.32</v>
+        <v>1.93</v>
       </c>
       <c r="AN23">
-        <v>3.124461206896552</v>
+        <v>2.195817490494297</v>
       </c>
       <c r="AO23">
-        <v>15.36057692307692</v>
+        <v>27.2538860103627</v>
       </c>
       <c r="AP23">
-        <v>0.4861420675363508</v>
+        <v>2.107604562737643</v>
       </c>
       <c r="AQ23">
-        <v>15.36057692307692</v>
+        <v>27.2538860103627</v>
       </c>
     </row>
     <row r="24">
@@ -3395,7 +3503,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pengana Capital Group Limited (ASX:PCG)</t>
+          <t>Argo Investments Limited (ASX:ARG)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3404,46 +3512,46 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.162</v>
+        <v>0.0764</v>
       </c>
       <c r="E24">
-        <v>0.344</v>
+        <v>0.0815</v>
       </c>
       <c r="G24">
-        <v>0.2520658135283363</v>
+        <v>0.9724650349650349</v>
       </c>
       <c r="H24">
-        <v>0.2449725776965265</v>
+        <v>0.9724650349650349</v>
       </c>
       <c r="I24">
-        <v>0.206581352833638</v>
+        <v>0.971153846153846</v>
       </c>
       <c r="J24">
-        <v>0.1336702871276481</v>
+        <v>0.9264635806671203</v>
       </c>
       <c r="K24">
-        <v>6.54</v>
+        <v>215.6</v>
       </c>
       <c r="L24">
-        <v>0.1195612431444241</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="M24">
-        <v>5.65</v>
+        <v>121.2</v>
       </c>
       <c r="N24">
-        <v>0.03992932862190813</v>
+        <v>0.02649411970445503</v>
       </c>
       <c r="O24">
-        <v>0.863914373088685</v>
+        <v>0.562152133580705</v>
       </c>
       <c r="P24">
-        <v>5.65</v>
+        <v>121.2</v>
       </c>
       <c r="Q24">
-        <v>0.03992932862190813</v>
+        <v>0.02649411970445503</v>
       </c>
       <c r="R24">
-        <v>0.863914373088685</v>
+        <v>0.562152133580705</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3452,73 +3560,67 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>14.9</v>
+        <v>92.8</v>
       </c>
       <c r="V24">
-        <v>0.1053003533568905</v>
+        <v>0.02028592663839461</v>
       </c>
       <c r="W24">
-        <v>0.1272373540856031</v>
+        <v>0.0509475873150905</v>
       </c>
       <c r="X24">
-        <v>0.04416333718492847</v>
+        <v>0.07245687115148267</v>
       </c>
       <c r="Y24">
-        <v>0.08307401690067465</v>
+        <v>-0.02150928383639216</v>
       </c>
       <c r="Z24">
-        <v>2.918890074706511</v>
+        <v>0.05582951111844225</v>
       </c>
       <c r="AA24">
-        <v>0.3901688743800616</v>
+        <v>0.05172400877768681</v>
       </c>
       <c r="AB24">
-        <v>0.04376794245922468</v>
+        <v>0.07245244205218287</v>
       </c>
       <c r="AC24">
-        <v>0.3464009319208369</v>
+        <v>-0.02072843327449606</v>
       </c>
       <c r="AD24">
-        <v>2.04</v>
+        <v>0.515</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>2.04</v>
+        <v>0.515</v>
       </c>
       <c r="AG24">
-        <v>-12.86</v>
+        <v>-92.285</v>
       </c>
       <c r="AH24">
-        <v>0.01421206632297617</v>
+        <v>0.0001125654764962192</v>
       </c>
       <c r="AI24">
-        <v>0.02998236331569665</v>
+        <v>0.0001325913367652606</v>
       </c>
       <c r="AJ24">
-        <v>-0.09996890547263682</v>
+        <v>-0.02058869133472324</v>
       </c>
       <c r="AK24">
-        <v>-0.242002258185924</v>
+        <v>-0.02434115867449684</v>
       </c>
       <c r="AL24">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>0.1522388059701492</v>
-      </c>
-      <c r="AO24">
-        <v>88.97637795275591</v>
+        <v>0.002314606741573034</v>
       </c>
       <c r="AP24">
-        <v>-0.9597014925373134</v>
-      </c>
-      <c r="AQ24">
-        <v>88.97637795275591</v>
+        <v>-0.4147640449438202</v>
       </c>
     </row>
     <row r="25">
@@ -3529,7 +3631,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spheria Emerging Companies Limited (ASX:SEC)</t>
+          <t>BKI Investment Company Limited (ASX:BKI)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3537,6 +3639,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D25">
+        <v>0.0735</v>
+      </c>
+      <c r="E25">
+        <v>0.172</v>
+      </c>
       <c r="G25">
         <v>0</v>
       </c>
@@ -3544,67 +3652,67 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0.9177489177489176</v>
+        <v>0.965675057208238</v>
       </c>
       <c r="J25">
-        <v>0.6530553764596317</v>
+        <v>0.9362732188742442</v>
       </c>
       <c r="K25">
-        <v>30.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L25">
-        <v>0.6515151515151515</v>
+        <v>1.588100686498856</v>
       </c>
       <c r="M25">
-        <v>5.08</v>
+        <v>28.6</v>
       </c>
       <c r="N25">
-        <v>0.0464775846294602</v>
+        <v>0.03143893591293833</v>
       </c>
       <c r="O25">
-        <v>0.1687707641196013</v>
+        <v>0.4121037463976945</v>
       </c>
       <c r="P25">
-        <v>2.73</v>
+        <v>28.6</v>
       </c>
       <c r="Q25">
-        <v>0.02497712717291857</v>
+        <v>0.03143893591293833</v>
       </c>
       <c r="R25">
-        <v>0.09069767441860464</v>
+        <v>0.4121037463976945</v>
       </c>
       <c r="S25">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>0.4625984251968504</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.52</v>
+        <v>49.7</v>
       </c>
       <c r="V25">
-        <v>0.02305580969807868</v>
+        <v>0.0546333956249313</v>
       </c>
       <c r="W25">
-        <v>0.3729863692688972</v>
+        <v>0.0789533560864619</v>
       </c>
       <c r="X25">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y25">
-        <v>0.3291134051774149</v>
+        <v>0.006499137045757039</v>
       </c>
       <c r="Z25">
-        <v>0.582304008066549</v>
+        <v>0.05149658260664625</v>
       </c>
       <c r="AA25">
-        <v>0.3802767632018527</v>
+        <v>0.04821487115814809</v>
       </c>
       <c r="AB25">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC25">
-        <v>0.3364037991103704</v>
+        <v>-0.02423934788255677</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -3616,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>-2.52</v>
+        <v>-49.7</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -3625,16 +3733,19 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>-0.02359992507960292</v>
+        <v>-0.05779069767441861</v>
       </c>
       <c r="AK25">
-        <v>-0.02287166454891995</v>
+        <v>-0.06561056105610562</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>-29.4</v>
+      </c>
+      <c r="AQ25">
+        <v>-1.435374149659864</v>
       </c>
     </row>
     <row r="26">
@@ -3645,7 +3756,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Katana Capital Limited (ASX:KAT)</t>
+          <t>Djerriwarrh Investments Limited (ASX:DJW)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3654,10 +3765,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.4370000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="E26">
-        <v>0.6629999999999999</v>
+        <v>0.0575</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3666,97 +3777,103 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0.8898582333696837</v>
+        <v>0.9239766081871345</v>
       </c>
       <c r="J26">
-        <v>0.6327634511258896</v>
+        <v>0.8473003404032469</v>
       </c>
       <c r="K26">
-        <v>5.71</v>
+        <v>30.7</v>
       </c>
       <c r="L26">
-        <v>0.6226826608505998</v>
+        <v>0.8976608187134502</v>
       </c>
       <c r="M26">
-        <v>2.349</v>
+        <v>17.9</v>
       </c>
       <c r="N26">
-        <v>0.08242105263157895</v>
+        <v>0.03595099417553726</v>
       </c>
       <c r="O26">
-        <v>0.41138353765324</v>
+        <v>0.5830618892508143</v>
       </c>
       <c r="P26">
-        <v>0.5590000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="Q26">
-        <v>0.0196140350877193</v>
+        <v>0.03595099417553726</v>
       </c>
       <c r="R26">
-        <v>0.09789842381786341</v>
+        <v>0.5830618892508143</v>
       </c>
       <c r="S26">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>0.7620263942103022</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>4.33</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>0.1519298245614035</v>
+        <v>0.002008435428800964</v>
       </c>
       <c r="W26">
-        <v>0.2248031496062992</v>
+        <v>0.05327086586847129</v>
       </c>
       <c r="X26">
-        <v>0.04387296409148227</v>
+        <v>0.07535460574292749</v>
       </c>
       <c r="Y26">
-        <v>0.1809301855148169</v>
+        <v>-0.0220837398744562</v>
       </c>
       <c r="Z26">
-        <v>0.4692937563971341</v>
+        <v>0.05479250143790265</v>
       </c>
       <c r="AA26">
-        <v>0.2969519368896831</v>
+        <v>0.04642570511988031</v>
       </c>
       <c r="AB26">
-        <v>0.04387296409148227</v>
+        <v>0.07072371459120814</v>
       </c>
       <c r="AC26">
-        <v>0.2530789727982009</v>
+        <v>-0.02429800947132783</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>61.3</v>
       </c>
       <c r="AG26">
-        <v>-4.33</v>
+        <v>60.3</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>0.109620886981402</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>0.1107497741644083</v>
       </c>
       <c r="AJ26">
-        <v>-0.1791477037649979</v>
+        <v>0.1080257972053028</v>
       </c>
       <c r="AK26">
-        <v>-0.1623547056617923</v>
+        <v>0.1091402714932127</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>0.978</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>0.978</v>
+      </c>
+      <c r="AO26">
+        <v>32.31083844580778</v>
+      </c>
+      <c r="AQ26">
+        <v>32.31083844580778</v>
       </c>
     </row>
     <row r="27">
@@ -3767,7 +3884,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EQT Holdings Limited (ASX:EQT)</t>
+          <t>Australian Foundation Investment Company Limited (ASX:AFI)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3776,49 +3893,46 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0384</v>
+        <v>0.0722</v>
       </c>
       <c r="E27">
-        <v>0.101</v>
-      </c>
-      <c r="F27">
-        <v>0.113</v>
+        <v>0.0803</v>
       </c>
       <c r="G27">
-        <v>0.3614775725593667</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>0.3614775725593667</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0.3337730870712401</v>
+        <v>0.9513094798967169</v>
       </c>
       <c r="J27">
-        <v>0.2257011844292307</v>
+        <v>0.9170150869272155</v>
       </c>
       <c r="K27">
-        <v>16.1</v>
+        <v>248.4</v>
       </c>
       <c r="L27">
-        <v>0.212401055408971</v>
+        <v>0.9162670601254149</v>
       </c>
       <c r="M27">
-        <v>10.9</v>
+        <v>152.2</v>
       </c>
       <c r="N27">
-        <v>0.02684729064039409</v>
+        <v>0.02429369513168396</v>
       </c>
       <c r="O27">
-        <v>0.6770186335403726</v>
+        <v>0.6127214170692431</v>
       </c>
       <c r="P27">
-        <v>10.9</v>
+        <v>152.2</v>
       </c>
       <c r="Q27">
-        <v>0.02684729064039409</v>
+        <v>0.02429369513168396</v>
       </c>
       <c r="R27">
-        <v>0.6770186335403726</v>
+        <v>0.6127214170692431</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -3827,73 +3941,67 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>69.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="V27">
-        <v>0.1701970443349753</v>
+        <v>0.01589784517158819</v>
       </c>
       <c r="W27">
-        <v>0.08674568965517243</v>
+        <v>0.04383658342892438</v>
       </c>
       <c r="X27">
-        <v>0.04540586855773538</v>
+        <v>0.07248012714899429</v>
       </c>
       <c r="Y27">
-        <v>0.04133982109743705</v>
+        <v>-0.02864354372006991</v>
       </c>
       <c r="Z27">
-        <v>1.157251908396947</v>
+        <v>0.04846523767810216</v>
       </c>
       <c r="AA27">
-        <v>0.2611931264081784</v>
+        <v>0.04444335414233301</v>
       </c>
       <c r="AB27">
-        <v>0.04335032971401392</v>
+        <v>0.07243687700014657</v>
       </c>
       <c r="AC27">
-        <v>0.2178427966941645</v>
+        <v>-0.02799352285781356</v>
       </c>
       <c r="AD27">
-        <v>30.9</v>
+        <v>6.89</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>30.9</v>
+        <v>6.89</v>
       </c>
       <c r="AG27">
-        <v>-38.2</v>
+        <v>-92.70999999999999</v>
       </c>
       <c r="AH27">
-        <v>0.07072556649118791</v>
+        <v>0.001098552429969275</v>
       </c>
       <c r="AI27">
-        <v>0.1306553911205074</v>
+        <v>0.001428485535806472</v>
       </c>
       <c r="AJ27">
-        <v>-0.1038607939097335</v>
+        <v>-0.01502035711219013</v>
       </c>
       <c r="AK27">
-        <v>-0.2281959378733572</v>
+        <v>-0.0196266054715699</v>
       </c>
       <c r="AL27">
-        <v>1.16</v>
+        <v>0.582</v>
       </c>
       <c r="AM27">
-        <v>1.16</v>
-      </c>
-      <c r="AN27">
-        <v>1.127737226277372</v>
+        <v>0.582</v>
       </c>
       <c r="AO27">
-        <v>21.81034482758621</v>
-      </c>
-      <c r="AP27">
-        <v>-1.394160583941606</v>
+        <v>443.127147766323</v>
       </c>
       <c r="AQ27">
-        <v>21.81034482758621</v>
+        <v>443.127147766323</v>
       </c>
     </row>
     <row r="28">
@@ -3904,7 +4012,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diverger Limited (ASX:DVR)</t>
+          <t>Diversified United Investment Limited (ASX:DUI)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3913,118 +4021,115 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.355</v>
+        <v>0.0455</v>
+      </c>
+      <c r="E28">
+        <v>0.0692</v>
       </c>
       <c r="G28">
-        <v>0.05915697674418605</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0.05915697674418605</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>0.04836703573709722</v>
+        <v>0.9705014749262537</v>
       </c>
       <c r="J28">
-        <v>0.03480699178937532</v>
+        <v>0.9705014749262537</v>
       </c>
       <c r="K28">
-        <v>1.88</v>
+        <v>31.6</v>
       </c>
       <c r="L28">
-        <v>0.02732558139534884</v>
+        <v>0.9321533923303835</v>
       </c>
       <c r="M28">
-        <v>1.182</v>
+        <v>19.8</v>
       </c>
       <c r="N28">
-        <v>0.03926910299003323</v>
+        <v>0.02782462057335582</v>
       </c>
       <c r="O28">
-        <v>0.6287234042553193</v>
+        <v>0.6265822784810127</v>
       </c>
       <c r="P28">
-        <v>1.07</v>
+        <v>19.8</v>
       </c>
       <c r="Q28">
-        <v>0.03554817275747509</v>
+        <v>0.02782462057335582</v>
       </c>
       <c r="R28">
-        <v>0.5691489361702128</v>
+        <v>0.6265822784810127</v>
       </c>
       <c r="S28">
-        <v>0.1120000000000001</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>0.09475465313028772</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.69</v>
+        <v>3.68</v>
       </c>
       <c r="V28">
-        <v>0.05614617940199335</v>
+        <v>0.005171444631815627</v>
       </c>
       <c r="W28">
-        <v>0.08468468468468468</v>
+        <v>0.04487998863797756</v>
       </c>
       <c r="X28">
-        <v>0.04411033415741668</v>
+        <v>0.0758740287355241</v>
       </c>
       <c r="Y28">
-        <v>0.040574350527268</v>
+        <v>-0.03099404009754653</v>
       </c>
       <c r="Z28">
-        <v>6.665543014719073</v>
+        <v>0.04300229599279489</v>
       </c>
       <c r="AA28">
-        <v>0.2320075009850548</v>
+        <v>0.04173379168622277</v>
       </c>
       <c r="AB28">
-        <v>0.04378688920697861</v>
+        <v>0.07045308853626082</v>
       </c>
       <c r="AC28">
-        <v>0.1882206117780761</v>
+        <v>-0.02871929685003805</v>
       </c>
       <c r="AD28">
-        <v>0.163</v>
+        <v>103.3</v>
       </c>
       <c r="AE28">
-        <v>0.1917397064385588</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>0.3547397064385588</v>
+        <v>103.3</v>
       </c>
       <c r="AG28">
-        <v>-1.335260293561441</v>
+        <v>99.61999999999999</v>
       </c>
       <c r="AH28">
-        <v>0.0116480951686992</v>
+        <v>0.1267640201251687</v>
       </c>
       <c r="AI28">
-        <v>0.01208458020701684</v>
+        <v>0.1439721254355401</v>
       </c>
       <c r="AJ28">
-        <v>-0.0464200374204173</v>
+        <v>0.1228026922413155</v>
       </c>
       <c r="AK28">
-        <v>-0.04826578192061135</v>
+        <v>0.1395589924630859</v>
       </c>
       <c r="AL28">
-        <v>0.168</v>
+        <v>1.53</v>
       </c>
       <c r="AM28">
-        <v>0.168</v>
-      </c>
-      <c r="AN28">
-        <v>0.03847969782813975</v>
+        <v>1.53</v>
       </c>
       <c r="AO28">
-        <v>19.04761904761905</v>
-      </c>
-      <c r="AP28">
-        <v>-0.3152172553261192</v>
+        <v>21.50326797385621</v>
       </c>
       <c r="AQ28">
-        <v>19.04761904761905</v>
+        <v>21.50326797385621</v>
       </c>
     </row>
     <row r="29">
@@ -4035,7 +4140,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bailador Technology Investments Limited (ASX:BTI)</t>
+          <t>Clime Investment Management Limited (ASX:CIW)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4044,106 +4149,121 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.231</v>
+        <v>0.0955</v>
       </c>
       <c r="E29">
-        <v>0.255</v>
+        <v>-0.481</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.1003181336161188</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>0.1003181336161188</v>
       </c>
       <c r="I29">
-        <v>0.7800511508951407</v>
+        <v>0.06542948038176034</v>
       </c>
       <c r="J29">
-        <v>0.545771381507651</v>
+        <v>0.03271474019088017</v>
       </c>
       <c r="K29">
-        <v>20.7</v>
+        <v>0.067</v>
       </c>
       <c r="L29">
-        <v>0.5294117647058824</v>
+        <v>0.007104984093319194</v>
       </c>
       <c r="M29">
-        <v>-0</v>
+        <v>1.587</v>
       </c>
       <c r="N29">
-        <v>-0</v>
+        <v>0.0669620253164557</v>
       </c>
       <c r="O29">
-        <v>-0</v>
+        <v>23.6865671641791</v>
       </c>
       <c r="P29">
-        <v>-0</v>
+        <v>1.26</v>
       </c>
       <c r="Q29">
-        <v>-0</v>
+        <v>0.05316455696202532</v>
       </c>
       <c r="R29">
-        <v>-0</v>
+        <v>18.80597014925373</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>0.327</v>
+      </c>
+      <c r="T29">
+        <v>0.2060491493383743</v>
       </c>
       <c r="U29">
-        <v>32.6</v>
+        <v>5.61</v>
       </c>
       <c r="V29">
-        <v>0.2193808882907133</v>
+        <v>0.2367088607594937</v>
       </c>
       <c r="W29">
-        <v>0.2129629629629629</v>
+        <v>0.003872832369942197</v>
       </c>
       <c r="X29">
-        <v>0.04387296409148227</v>
+        <v>0.07343729143909641</v>
       </c>
       <c r="Y29">
-        <v>0.1690899988714807</v>
+        <v>-0.06956445906915422</v>
       </c>
       <c r="Z29">
-        <v>0.4158689640502021</v>
+        <v>1.234293193717277</v>
       </c>
       <c r="AA29">
-        <v>0.2269693790358344</v>
+        <v>0.04037958115183245</v>
       </c>
       <c r="AB29">
-        <v>0.04387296409148227</v>
+        <v>0.07182184766926911</v>
       </c>
       <c r="AC29">
-        <v>0.1830964149443522</v>
+        <v>-0.03144226651743665</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>0.989</v>
       </c>
       <c r="AG29">
-        <v>-32.6</v>
+        <v>-4.621</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>0.04005832557009194</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>0.05378215237370167</v>
       </c>
       <c r="AJ29">
-        <v>-0.2810344827586207</v>
+        <v>-0.2422034697835316</v>
       </c>
       <c r="AK29">
-        <v>-0.2929020664869721</v>
+        <v>-0.3616088895844746</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="AN29">
+        <v>1.045454545454545</v>
+      </c>
+      <c r="AO29">
+        <v>10.28333333333333</v>
+      </c>
+      <c r="AP29">
+        <v>-4.88477801268499</v>
+      </c>
+      <c r="AQ29">
+        <v>10.28333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4154,7 +4274,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Navigator Global Investments Limited (ASX:NGI)</t>
+          <t>Carlton Investments Limited (ASX:CIN)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4163,46 +4283,46 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0479</v>
+        <v>-0.0283</v>
       </c>
       <c r="E30">
-        <v>0.137</v>
+        <v>-0.0318</v>
       </c>
       <c r="G30">
-        <v>0.2985409652076319</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>0.2985409652076319</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0.2749719416386083</v>
+        <v>0.9715447154471544</v>
       </c>
       <c r="J30">
-        <v>0.2264922731589399</v>
+        <v>0.9442276422764226</v>
       </c>
       <c r="K30">
-        <v>26.8</v>
+        <v>23.3</v>
       </c>
       <c r="L30">
-        <v>0.3007856341189675</v>
+        <v>0.9471544715447154</v>
       </c>
       <c r="M30">
-        <v>18.4</v>
+        <v>14.8</v>
       </c>
       <c r="N30">
-        <v>0.06730065837600585</v>
+        <v>0.02765321375186846</v>
       </c>
       <c r="O30">
-        <v>0.6865671641791045</v>
+        <v>0.6351931330472103</v>
       </c>
       <c r="P30">
-        <v>18.4</v>
+        <v>14.8</v>
       </c>
       <c r="Q30">
-        <v>0.06730065837600585</v>
+        <v>0.02765321375186846</v>
       </c>
       <c r="R30">
-        <v>0.6865671641791045</v>
+        <v>0.6351931330472103</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4211,73 +4331,67 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>52.1</v>
+        <v>8.6</v>
       </c>
       <c r="V30">
-        <v>0.1905632772494514</v>
+        <v>0.01606875934230194</v>
       </c>
       <c r="W30">
-        <v>0.1335992023928216</v>
+        <v>0.03669291338582677</v>
       </c>
       <c r="X30">
-        <v>0.04550104658780718</v>
+        <v>0.07245923699040488</v>
       </c>
       <c r="Y30">
-        <v>0.08809815580501437</v>
+        <v>-0.03576632360457811</v>
       </c>
       <c r="Z30">
-        <v>0.8650485436893205</v>
+        <v>0.03953560132685335</v>
       </c>
       <c r="AA30">
-        <v>0.1959268110530247</v>
+        <v>0.03733060762683535</v>
       </c>
       <c r="AB30">
-        <v>0.04356205828771219</v>
+        <v>0.07245085721140246</v>
       </c>
       <c r="AC30">
-        <v>0.1523647527653125</v>
+        <v>-0.03512024958456711</v>
       </c>
       <c r="AD30">
-        <v>22.1</v>
+        <v>0.114</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>22.1</v>
+        <v>0.114</v>
       </c>
       <c r="AG30">
-        <v>-30</v>
+        <v>-8.485999999999999</v>
       </c>
       <c r="AH30">
-        <v>0.07478849407783418</v>
+        <v>0.000212959123056748</v>
       </c>
       <c r="AI30">
-        <v>0.05627705627705627</v>
+        <v>0.0002019078520901005</v>
       </c>
       <c r="AJ30">
-        <v>-0.123253903040263</v>
+        <v>-0.01611121025831855</v>
       </c>
       <c r="AK30">
-        <v>-0.08807985907222547</v>
+        <v>-0.01526220562791584</v>
       </c>
       <c r="AL30">
-        <v>0.9389999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AM30">
-        <v>-12.261</v>
-      </c>
-      <c r="AN30">
-        <v>0.8308270676691729</v>
+        <v>0.008</v>
       </c>
       <c r="AO30">
-        <v>26.0915867944622</v>
-      </c>
-      <c r="AP30">
-        <v>-1.12781954887218</v>
+        <v>2987.5</v>
       </c>
       <c r="AQ30">
-        <v>-1.998205692847239</v>
+        <v>2987.5</v>
       </c>
     </row>
     <row r="31">
@@ -4288,7 +4402,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Plato Income Maximiser Limited (ASX:PL8)</t>
+          <t>Pinnacle Investment Management Group Limited (ASX:PNI)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4296,41 +4410,50 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D31">
+        <v>0.332</v>
+      </c>
+      <c r="E31">
+        <v>0.423</v>
+      </c>
+      <c r="F31">
+        <v>0.13</v>
+      </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.2280757097791798</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.2280757097791798</v>
       </c>
       <c r="I31">
-        <v>0.9585006693440428</v>
+        <v>0.2066246056782334</v>
       </c>
       <c r="J31">
-        <v>0.7346270864343153</v>
+        <v>0.2066246056782334</v>
       </c>
       <c r="K31">
-        <v>54.7</v>
+        <v>52.6</v>
       </c>
       <c r="L31">
-        <v>0.7322623828647925</v>
+        <v>1.659305993690852</v>
       </c>
       <c r="M31">
-        <v>15.4</v>
+        <v>45.4</v>
       </c>
       <c r="N31">
-        <v>0.0319634703196347</v>
+        <v>0.03912443984832816</v>
       </c>
       <c r="O31">
-        <v>0.2815356489945156</v>
+        <v>0.8631178707224334</v>
       </c>
       <c r="P31">
-        <v>15.4</v>
+        <v>45.4</v>
       </c>
       <c r="Q31">
-        <v>0.0319634703196347</v>
+        <v>0.03912443984832816</v>
       </c>
       <c r="R31">
-        <v>0.2815356489945156</v>
+        <v>0.8631178707224334</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -4339,61 +4462,73 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>0.649</v>
+        <v>26.4</v>
       </c>
       <c r="V31">
-        <v>0.00134703196347032</v>
+        <v>0.02275077559462254</v>
       </c>
       <c r="W31">
-        <v>0.183249581239531</v>
+        <v>0.2875888463641334</v>
       </c>
       <c r="X31">
-        <v>0.04387296409148227</v>
+        <v>0.07415549143722996</v>
       </c>
       <c r="Y31">
-        <v>0.1393766171480487</v>
+        <v>0.2134333549269034</v>
       </c>
       <c r="Z31">
-        <v>0.2507780161343929</v>
+        <v>0.1686170212765957</v>
       </c>
       <c r="AA31">
-        <v>0.1842283233345867</v>
+        <v>0.03484042553191489</v>
       </c>
       <c r="AB31">
-        <v>0.04387296409148227</v>
+        <v>0.07175400439138535</v>
       </c>
       <c r="AC31">
-        <v>0.1403553592431044</v>
+        <v>-0.03691357885947046</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>83.8</v>
       </c>
       <c r="AG31">
-        <v>-0.649</v>
+        <v>57.4</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>0.06735251567272142</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>0.2321972845663619</v>
       </c>
       <c r="AJ31">
-        <v>-0.001348848906060675</v>
+        <v>0.04713417638364262</v>
       </c>
       <c r="AK31">
-        <v>-0.001788612956833521</v>
+        <v>0.1715994020926756</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="AN31">
+        <v>11.59059474412171</v>
+      </c>
+      <c r="AO31">
+        <v>3.99390243902439</v>
+      </c>
+      <c r="AP31">
+        <v>7.939142461964038</v>
+      </c>
+      <c r="AQ31">
+        <v>3.99390243902439</v>
       </c>
     </row>
     <row r="32">
@@ -4404,7 +4539,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clime Investment Management Limited (ASX:CIW)</t>
+          <t>Amcil Limited (ASX:AMH)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4413,46 +4548,46 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.116</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="E32">
-        <v>0.164</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G32">
-        <v>0.1364406779661017</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>0.1364406779661017</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0.1076271186440678</v>
+        <v>0.8094575799721836</v>
       </c>
       <c r="J32">
-        <v>0.07880337528187968</v>
+        <v>0.7888685892620897</v>
       </c>
       <c r="K32">
-        <v>1.71</v>
+        <v>5.59</v>
       </c>
       <c r="L32">
-        <v>0.1449152542372881</v>
+        <v>0.7774687065368567</v>
       </c>
       <c r="M32">
-        <v>0.981</v>
+        <v>11.2</v>
       </c>
       <c r="N32">
-        <v>0.03084905660377358</v>
+        <v>0.0516366989396035</v>
       </c>
       <c r="O32">
-        <v>0.5736842105263158</v>
+        <v>2.003577817531306</v>
       </c>
       <c r="P32">
-        <v>0.981</v>
+        <v>11.2</v>
       </c>
       <c r="Q32">
-        <v>0.03084905660377358</v>
+        <v>0.0516366989396035</v>
       </c>
       <c r="R32">
-        <v>0.5736842105263158</v>
+        <v>2.003577817531306</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -4461,73 +4596,67 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>4.56</v>
+        <v>15</v>
       </c>
       <c r="V32">
-        <v>0.1433962264150943</v>
+        <v>0.06915629322268327</v>
       </c>
       <c r="W32">
-        <v>0.1125</v>
+        <v>0.02223548130469371</v>
       </c>
       <c r="X32">
-        <v>0.04473434339384363</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y32">
-        <v>0.06776565660615638</v>
+        <v>-0.05021873773601114</v>
       </c>
       <c r="Z32">
-        <v>2.076733544526575</v>
+        <v>0.02956414473684211</v>
       </c>
       <c r="AA32">
-        <v>0.1636536128697959</v>
+        <v>0.02332222515129287</v>
       </c>
       <c r="AB32">
-        <v>0.04356989201479841</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC32">
-        <v>0.1200837208549975</v>
+        <v>-0.04913199388941199</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>-3.199999999999999</v>
+        <v>-15</v>
       </c>
       <c r="AH32">
-        <v>0.04101326899879373</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>0.07288317256162916</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>-0.1118881118881119</v>
+        <v>-0.07429420505200594</v>
       </c>
       <c r="AK32">
-        <v>-0.226950354609929</v>
+        <v>-0.07796257796257797</v>
       </c>
       <c r="AL32">
-        <v>0.08799999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="AM32">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AN32">
-        <v>0.84472049689441</v>
+        <v>0.079</v>
       </c>
       <c r="AO32">
-        <v>14.43181818181818</v>
-      </c>
-      <c r="AP32">
-        <v>-1.987577639751552</v>
+        <v>73.67088607594937</v>
       </c>
       <c r="AQ32">
-        <v>14.43181818181818</v>
+        <v>73.67088607594937</v>
       </c>
     </row>
     <row r="33">
@@ -4538,7 +4667,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>K2 Asset Management Holdings Ltd (ASX:KAM)</t>
+          <t>Mirrabooka Investments Limited (ASX:MIR)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4547,118 +4676,115 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.205</v>
+        <v>0.00016</v>
       </c>
       <c r="E33">
-        <v>-0.4370000000000001</v>
+        <v>-0.0234</v>
       </c>
       <c r="G33">
-        <v>0.1101492537313433</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>0.09373134328358208</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>0.08358208955223881</v>
+        <v>0.7224606580829757</v>
       </c>
       <c r="J33">
-        <v>0.0520780711825488</v>
+        <v>0.6716853106273448</v>
       </c>
       <c r="K33">
-        <v>0.162</v>
+        <v>4.63</v>
       </c>
       <c r="L33">
-        <v>0.04835820895522388</v>
+        <v>0.6623748211731044</v>
       </c>
       <c r="M33">
-        <v>-0</v>
+        <v>9.76</v>
       </c>
       <c r="N33">
-        <v>-0</v>
+        <v>0.026550598476605</v>
       </c>
       <c r="O33">
-        <v>-0</v>
+        <v>2.107991360691145</v>
       </c>
       <c r="P33">
-        <v>-0</v>
+        <v>9.76</v>
       </c>
       <c r="Q33">
-        <v>-0</v>
+        <v>0.026550598476605</v>
       </c>
       <c r="R33">
-        <v>-0</v>
+        <v>2.107991360691145</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
       <c r="U33">
-        <v>8.16</v>
+        <v>18.9</v>
       </c>
       <c r="V33">
-        <v>0.6044444444444445</v>
+        <v>0.05141458106637649</v>
       </c>
       <c r="W33">
-        <v>0.01828442437923251</v>
+        <v>0.01192684183410613</v>
       </c>
       <c r="X33">
-        <v>0.04441751907854699</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y33">
-        <v>-0.02613309469931448</v>
+        <v>-0.06052737720659872</v>
       </c>
       <c r="Z33">
-        <v>2.743652743652747</v>
+        <v>0.01903076504219984</v>
       </c>
       <c r="AA33">
-        <v>0.1428841428841431</v>
+        <v>0.01278268532884601</v>
       </c>
       <c r="AB33">
-        <v>0.0437635263727885</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC33">
-        <v>0.09912061651135459</v>
+        <v>-0.05967153371185884</v>
       </c>
       <c r="AD33">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>-7.795</v>
+        <v>-18.9</v>
       </c>
       <c r="AH33">
-        <v>0.02632527948070681</v>
+        <v>0</v>
       </c>
       <c r="AI33">
-        <v>0.03590752582390556</v>
+        <v>0</v>
       </c>
       <c r="AJ33">
-        <v>-1.366345311130587</v>
+        <v>-0.05420131918554631</v>
       </c>
       <c r="AK33">
-        <v>-3.887780548628427</v>
+        <v>-0.06338028169014083</v>
       </c>
       <c r="AL33">
-        <v>0.019</v>
+        <v>0.065</v>
       </c>
       <c r="AM33">
-        <v>0.019</v>
-      </c>
-      <c r="AN33">
-        <v>1.162420382165605</v>
+        <v>0.065</v>
       </c>
       <c r="AO33">
-        <v>14.73684210526316</v>
-      </c>
-      <c r="AP33">
-        <v>-24.82484076433121</v>
+        <v>77.69230769230769</v>
       </c>
       <c r="AQ33">
-        <v>14.73684210526316</v>
+        <v>77.69230769230769</v>
       </c>
     </row>
     <row r="34">
@@ -4669,7 +4795,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BlackWall Limited (ASX:BWF)</t>
+          <t>MA Financial Group Limited (ASX:MAF)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4678,121 +4804,109 @@
         </is>
       </c>
       <c r="D34">
-        <v>-0.0756</v>
+        <v>0.412</v>
       </c>
       <c r="E34">
-        <v>0.00777</v>
+        <v>0.213</v>
       </c>
       <c r="G34">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>0.4688644688644689</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>0.367063073912389</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>2.27</v>
+        <v>26.4</v>
       </c>
       <c r="L34">
-        <v>0.4157509157509158</v>
+        <v>0.07968608511922728</v>
       </c>
       <c r="M34">
-        <v>2.13</v>
+        <v>25.72</v>
       </c>
       <c r="N34">
-        <v>0.07553191489361702</v>
+        <v>0.05145029005801161</v>
       </c>
       <c r="O34">
-        <v>0.9383259911894273</v>
+        <v>0.9742424242424242</v>
       </c>
       <c r="P34">
-        <v>2.13</v>
+        <v>19.4</v>
       </c>
       <c r="Q34">
-        <v>0.07553191489361702</v>
+        <v>0.03880776155231046</v>
       </c>
       <c r="R34">
-        <v>0.9383259911894273</v>
+        <v>0.7348484848484849</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>0.2457231726283048</v>
       </c>
       <c r="U34">
-        <v>2.35</v>
+        <v>82.8</v>
       </c>
       <c r="V34">
-        <v>0.08333333333333334</v>
+        <v>0.1656331266253251</v>
       </c>
       <c r="W34">
-        <v>0.1503311258278146</v>
+        <v>0.1413276231263383</v>
       </c>
       <c r="X34">
-        <v>0.04419222155475266</v>
+        <v>0.09876900427501314</v>
       </c>
       <c r="Y34">
-        <v>0.1061389042730619</v>
+        <v>0.04255861885132517</v>
       </c>
       <c r="Z34">
-        <v>0.3684210526315789</v>
+        <v>0.9990952955367914</v>
       </c>
       <c r="AA34">
-        <v>0.1352337640729854</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.04380809730015687</v>
+        <v>0.06696874727116986</v>
       </c>
       <c r="AC34">
-        <v>0.09142566677282854</v>
+        <v>-0.06696874727116986</v>
       </c>
       <c r="AD34">
-        <v>0.447</v>
+        <v>558.4</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>0.447</v>
+        <v>558.4</v>
       </c>
       <c r="AG34">
-        <v>-1.903</v>
+        <v>475.6</v>
       </c>
       <c r="AH34">
-        <v>0.01560372813907216</v>
+        <v>0.5276386657847492</v>
       </c>
       <c r="AI34">
-        <v>0.02637634979642415</v>
+        <v>0.6743961352657004</v>
       </c>
       <c r="AJ34">
-        <v>-0.07236566908772864</v>
+        <v>0.4875448487954895</v>
       </c>
       <c r="AK34">
-        <v>-0.1303692539562924</v>
+        <v>0.6382179280730005</v>
       </c>
       <c r="AL34">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>0.019</v>
-      </c>
-      <c r="AN34">
-        <v>0.1719230769230769</v>
-      </c>
-      <c r="AO34">
-        <v>134.7368421052632</v>
-      </c>
-      <c r="AP34">
-        <v>-0.7319230769230769</v>
-      </c>
-      <c r="AQ34">
-        <v>134.7368421052632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4803,7 +4917,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teaminvest Private Group Limited (ASX:TIP)</t>
+          <t>ECP Emerging Growth Limited (ASX:ECP)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4811,113 +4925,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D35">
+        <v>0.004759999999999999</v>
+      </c>
       <c r="G35">
-        <v>0.05289139633286318</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>0.05289139633286318</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>0.04007098304317824</v>
+        <v>-0.4539007092198582</v>
       </c>
       <c r="J35">
-        <v>0.03599002117564719</v>
+        <v>-0.4539007092198582</v>
       </c>
       <c r="K35">
-        <v>3.9</v>
+        <v>-7.07</v>
       </c>
       <c r="L35">
-        <v>0.05500705218617771</v>
+        <v>-25.07092198581561</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>0.593</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.04235714285714286</v>
       </c>
       <c r="O35">
-        <v>-0</v>
+        <v>-0.08387553041018386</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>0.593</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.04235714285714286</v>
       </c>
       <c r="R35">
-        <v>-0</v>
+        <v>-0.08387553041018386</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
       <c r="U35">
-        <v>9.26</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>0.1859437751004016</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="W35">
-        <v>0.06951871657754011</v>
+        <v>-0.3087336244541485</v>
       </c>
       <c r="X35">
-        <v>0.04571714096978983</v>
+        <v>0.08260096608147736</v>
       </c>
       <c r="Y35">
-        <v>0.02380157560775028</v>
+        <v>-0.3913345905356259</v>
       </c>
       <c r="Z35">
-        <v>3.063980161039768</v>
+        <v>0.014050822122571</v>
       </c>
       <c r="AA35">
-        <v>0.1102727108775842</v>
+        <v>-0.006377678126557051</v>
       </c>
       <c r="AB35">
-        <v>0.04325310543855292</v>
+        <v>0.06770178857417289</v>
       </c>
       <c r="AC35">
-        <v>0.06701960543903124</v>
+        <v>-0.07407946670072994</v>
       </c>
       <c r="AD35">
-        <v>4.51</v>
+        <v>6.03</v>
       </c>
       <c r="AE35">
-        <v>0.04983651119331094</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>4.559836511193311</v>
+        <v>6.03</v>
       </c>
       <c r="AG35">
-        <v>-4.700163488806689</v>
+        <v>4.03</v>
       </c>
       <c r="AH35">
-        <v>0.08388245447085531</v>
+        <v>0.3010484273589615</v>
       </c>
       <c r="AI35">
-        <v>0.05811682402043739</v>
+        <v>0.2922927775084828</v>
       </c>
       <c r="AJ35">
-        <v>-0.1042168631285428</v>
+        <v>0.223516361619523</v>
       </c>
       <c r="AK35">
-        <v>-0.06792159816803067</v>
+        <v>0.2163177670424047</v>
       </c>
       <c r="AL35">
-        <v>0.299</v>
+        <v>0.146</v>
       </c>
       <c r="AM35">
-        <v>0.299</v>
-      </c>
-      <c r="AN35">
-        <v>1.18652986056301</v>
+        <v>0.146</v>
       </c>
       <c r="AO35">
-        <v>9.364548494983277</v>
-      </c>
-      <c r="AP35">
-        <v>-1.236559718181186</v>
+        <v>-0.8767123287671234</v>
       </c>
       <c r="AQ35">
-        <v>9.364548494983277</v>
+        <v>-0.8767123287671234</v>
       </c>
     </row>
     <row r="36">
@@ -4928,7 +5042,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVC Limited (ASX:CVC)</t>
+          <t>Orion Equities Limited (ASX:OEQ)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4937,121 +5051,109 @@
         </is>
       </c>
       <c r="D36">
-        <v>-0.0406</v>
-      </c>
-      <c r="E36">
-        <v>0.07150000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="G36">
-        <v>0.459016393442623</v>
+        <v>-1.258064516129032</v>
       </c>
       <c r="H36">
-        <v>0.459016393442623</v>
+        <v>-1.258064516129032</v>
       </c>
       <c r="I36">
-        <v>0.4566744730679156</v>
+        <v>-1.258064516129032</v>
       </c>
       <c r="J36">
-        <v>0.3376818286769798</v>
+        <v>-1.258064516129032</v>
       </c>
       <c r="K36">
-        <v>14.6</v>
+        <v>-2.71</v>
       </c>
       <c r="L36">
-        <v>0.3419203747072599</v>
+        <v>-87.41935483870968</v>
       </c>
       <c r="M36">
-        <v>6.029</v>
+        <v>-0</v>
       </c>
       <c r="N36">
-        <v>0.02745446265938069</v>
+        <v>-0</v>
       </c>
       <c r="O36">
-        <v>0.4129452054794521</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>5.38</v>
+        <v>-0</v>
       </c>
       <c r="Q36">
-        <v>0.02449908925318761</v>
+        <v>-0</v>
       </c>
       <c r="R36">
-        <v>0.3684931506849315</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>0.649</v>
-      </c>
-      <c r="T36">
-        <v>0.1076463758500581</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>41.8</v>
+        <v>0.01</v>
       </c>
       <c r="V36">
-        <v>0.1903460837887067</v>
+        <v>0.008</v>
       </c>
       <c r="W36">
-        <v>0.1260794473229706</v>
+        <v>-0.5122873345935728</v>
       </c>
       <c r="X36">
-        <v>0.05033901954646702</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y36">
-        <v>0.07574042777650361</v>
+        <v>-0.5847415536342776</v>
       </c>
       <c r="Z36">
-        <v>0.256425654576027</v>
+        <v>0.006026438569206843</v>
       </c>
       <c r="AA36">
-        <v>0.08659028395692435</v>
+        <v>-0.007581648522550544</v>
       </c>
       <c r="AB36">
-        <v>0.0420771435847858</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC36">
-        <v>0.04451314037213855</v>
+        <v>-0.0800358675632554</v>
       </c>
       <c r="AD36">
-        <v>70.5</v>
+        <v>0</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>70.5</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>28.7</v>
+        <v>-0.01</v>
       </c>
       <c r="AH36">
-        <v>0.2430196483971044</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>0.2997448979591837</v>
+        <v>0</v>
       </c>
       <c r="AJ36">
-        <v>0.1155859846959323</v>
+        <v>-0.008064516129032258</v>
       </c>
       <c r="AK36">
-        <v>0.1483971044467425</v>
+        <v>-0.004672897196261682</v>
       </c>
       <c r="AL36">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>3.596938775510204</v>
-      </c>
-      <c r="AO36">
-        <v>5.064935064935065</v>
+        <v>-0</v>
       </c>
       <c r="AP36">
-        <v>1.464285714285714</v>
-      </c>
-      <c r="AQ36">
-        <v>5.064935064935065</v>
+        <v>0.2564102564102564</v>
       </c>
     </row>
     <row r="37">
@@ -5062,7 +5164,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pacific Current Group Limited (ASX:PAC)</t>
+          <t>Katana Capital Limited (ASX:KAT)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5071,118 +5173,106 @@
         </is>
       </c>
       <c r="D37">
-        <v>0.544</v>
+        <v>-0.231</v>
       </c>
       <c r="G37">
-        <v>0.5040650406504066</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0.5040650406504066</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.4444444444444444</v>
+        <v>-0.8559322033898306</v>
       </c>
       <c r="J37">
-        <v>0.3351010101010101</v>
+        <v>-0.8559322033898306</v>
       </c>
       <c r="K37">
-        <v>13.1</v>
+        <v>-0.194</v>
       </c>
       <c r="L37">
-        <v>0.3550135501355013</v>
+        <v>-0.4110169491525424</v>
       </c>
       <c r="M37">
-        <v>10.421</v>
+        <v>1.688</v>
       </c>
       <c r="N37">
-        <v>0.0384113527460376</v>
+        <v>0.06725099601593625</v>
       </c>
       <c r="O37">
-        <v>0.7954961832061068</v>
+        <v>-8.701030927835051</v>
       </c>
       <c r="P37">
-        <v>9.949999999999999</v>
+        <v>0.428</v>
       </c>
       <c r="Q37">
-        <v>0.03667526723184666</v>
+        <v>0.01705179282868526</v>
       </c>
       <c r="R37">
-        <v>0.7595419847328244</v>
+        <v>-2.206185567010309</v>
       </c>
       <c r="S37">
-        <v>0.4710000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="T37">
-        <v>0.0451971979656463</v>
+        <v>0.7464454976303317</v>
       </c>
       <c r="U37">
-        <v>21.2</v>
+        <v>4.92</v>
       </c>
       <c r="V37">
-        <v>0.07814227792112052</v>
+        <v>0.1960159362549801</v>
       </c>
       <c r="W37">
-        <v>0.04719020172910662</v>
+        <v>-0.006258064516129033</v>
       </c>
       <c r="X37">
-        <v>0.04391082604570512</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y37">
-        <v>0.003279375683401503</v>
+        <v>-0.07871228355683389</v>
       </c>
       <c r="Z37">
-        <v>0.1539039039039039</v>
+        <v>0.01769778777652793</v>
       </c>
       <c r="AA37">
-        <v>0.05157335365668698</v>
+        <v>-0.01514810648668916</v>
       </c>
       <c r="AB37">
-        <v>0.04385909888684093</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC37">
-        <v>0.007714254769846052</v>
+        <v>-0.08760232552739403</v>
       </c>
       <c r="AD37">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>-20.69</v>
+        <v>-4.92</v>
       </c>
       <c r="AH37">
-        <v>0.001876310658180347</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>0.001685894681167565</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>-0.08255855712062565</v>
+        <v>-0.2438057482656095</v>
       </c>
       <c r="AK37">
-        <v>-0.0735487540435818</v>
+        <v>-0.2269372693726937</v>
       </c>
       <c r="AL37">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>0.081</v>
-      </c>
-      <c r="AN37">
-        <v>0.02741935483870967</v>
-      </c>
-      <c r="AO37">
-        <v>202.4691358024691</v>
-      </c>
-      <c r="AP37">
-        <v>-1.112365591397849</v>
-      </c>
-      <c r="AQ37">
-        <v>202.4691358024691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -5193,7 +5283,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Djerriwarrh Investments Limited (ASX:DJW)</t>
+          <t>Teaminvest Private Group Limited (ASX:TIP)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5202,46 +5292,43 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.0612</v>
-      </c>
-      <c r="E38">
-        <v>-0.0561</v>
+        <v>0.0433</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.01887366818873668</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.01887366818873668</v>
       </c>
       <c r="I38">
-        <v>0.9036544850498338</v>
+        <v>-0.01537290715372907</v>
       </c>
       <c r="J38">
-        <v>0.8037953902038599</v>
+        <v>-0.01537290715372907</v>
       </c>
       <c r="K38">
-        <v>22.9</v>
+        <v>-12.2</v>
       </c>
       <c r="L38">
-        <v>0.7607973421926909</v>
+        <v>-0.1856925418569254</v>
       </c>
       <c r="M38">
-        <v>15.8</v>
+        <v>0.5267999999999999</v>
       </c>
       <c r="N38">
-        <v>0.027748507200562</v>
+        <v>0.0145524861878453</v>
       </c>
       <c r="O38">
-        <v>0.6899563318777293</v>
+        <v>-0.04318032786885245</v>
       </c>
       <c r="P38">
-        <v>15.8</v>
+        <v>0.5267999999999999</v>
       </c>
       <c r="Q38">
-        <v>0.027748507200562</v>
+        <v>0.0145524861878453</v>
       </c>
       <c r="R38">
-        <v>0.6899563318777293</v>
+        <v>-0.04318032786885245</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -5250,67 +5337,73 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>0.927</v>
+        <v>4.43</v>
       </c>
       <c r="V38">
-        <v>0.001628029504741834</v>
+        <v>0.1223756906077348</v>
       </c>
       <c r="W38">
-        <v>0.05208096429383671</v>
+        <v>-0.1650879566982408</v>
       </c>
       <c r="X38">
-        <v>0.04559913980866709</v>
+        <v>0.0743414583957499</v>
       </c>
       <c r="Y38">
-        <v>0.006481824485169617</v>
+        <v>-0.2394294150939907</v>
       </c>
       <c r="Z38">
-        <v>0.06106839254194649</v>
+        <v>1.7543391188251</v>
       </c>
       <c r="AA38">
-        <v>0.04908649241237636</v>
+        <v>-0.02696929238985313</v>
       </c>
       <c r="AB38">
-        <v>0.04328963671424566</v>
+        <v>0.07188042951217766</v>
       </c>
       <c r="AC38">
-        <v>0.005796855698130703</v>
+        <v>-0.09884972190203078</v>
       </c>
       <c r="AD38">
-        <v>48.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>48.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG38">
-        <v>47.873</v>
+        <v>-1.53</v>
       </c>
       <c r="AH38">
-        <v>0.07893885473956649</v>
+        <v>0.07416879795396419</v>
       </c>
       <c r="AI38">
-        <v>0.07806750919852824</v>
+        <v>0.04906937394247039</v>
       </c>
       <c r="AJ38">
-        <v>0.07755563583697975</v>
+        <v>-0.04413037207960772</v>
       </c>
       <c r="AK38">
-        <v>0.07669828717358809</v>
+        <v>-0.02798609840863361</v>
       </c>
       <c r="AL38">
-        <v>1.36</v>
+        <v>0.228</v>
       </c>
       <c r="AM38">
-        <v>1.36</v>
+        <v>0.228</v>
+      </c>
+      <c r="AN38">
+        <v>2.338709677419355</v>
       </c>
       <c r="AO38">
-        <v>20</v>
+        <v>-4.429824561403509</v>
+      </c>
+      <c r="AP38">
+        <v>-1.233870967741935</v>
       </c>
       <c r="AQ38">
-        <v>20</v>
+        <v>-4.429824561403509</v>
       </c>
     </row>
     <row r="39">
@@ -5321,7 +5414,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Australian United Investment Company Limited (ASX:AUI)</t>
+          <t>NGE Capital Limited (ASX:NGE)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5330,121 +5423,115 @@
         </is>
       </c>
       <c r="D39">
-        <v>-0.009439999999999999</v>
+        <v>-0.306</v>
       </c>
       <c r="E39">
-        <v>-0.00821</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="G39">
-        <v>0.9682080924855491</v>
+        <v>-1.058947368421053</v>
       </c>
       <c r="H39">
-        <v>0.9682080924855491</v>
+        <v>-1.058947368421053</v>
       </c>
       <c r="I39">
-        <v>0.9682080924855491</v>
+        <v>-1.063157894736842</v>
       </c>
       <c r="J39">
-        <v>0.9258870469335078</v>
+        <v>-1.063157894736842</v>
       </c>
       <c r="K39">
-        <v>30.4</v>
+        <v>2.05</v>
       </c>
       <c r="L39">
-        <v>0.8786127167630057</v>
+        <v>4.315789473684211</v>
       </c>
       <c r="M39">
-        <v>31.5</v>
+        <v>0.104</v>
       </c>
       <c r="N39">
-        <v>0.03515232674924673</v>
+        <v>0.005652173913043478</v>
       </c>
       <c r="O39">
-        <v>1.036184210526316</v>
+        <v>0.05073170731707317</v>
       </c>
       <c r="P39">
-        <v>31.5</v>
+        <v>-0</v>
       </c>
       <c r="Q39">
-        <v>0.03515232674924673</v>
+        <v>-0</v>
       </c>
       <c r="R39">
-        <v>1.036184210526316</v>
+        <v>-0</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39">
-        <v>3.91</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="V39">
-        <v>0.004363352304430309</v>
+        <v>0.4559782608695653</v>
       </c>
       <c r="W39">
-        <v>0.04718298929070309</v>
+        <v>0.08266129032258064</v>
       </c>
       <c r="X39">
-        <v>0.04614982033936421</v>
+        <v>0.07249518939431962</v>
       </c>
       <c r="Y39">
-        <v>0.001033168951338877</v>
+        <v>0.01016610092826102</v>
       </c>
       <c r="Z39">
-        <v>0.05011587485515644</v>
+        <v>0.03957014328557147</v>
       </c>
       <c r="AA39">
-        <v>0.04640163937413003</v>
+        <v>-0.04206931022992336</v>
       </c>
       <c r="AB39">
-        <v>0.0431224452149287</v>
+        <v>0.07242681232939892</v>
       </c>
       <c r="AC39">
-        <v>0.003279194159201332</v>
+        <v>-0.1144961225593223</v>
       </c>
       <c r="AD39">
-        <v>101.3</v>
+        <v>0.032</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>101.3</v>
+        <v>0.032</v>
       </c>
       <c r="AG39">
-        <v>97.39</v>
+        <v>-8.358000000000001</v>
       </c>
       <c r="AH39">
-        <v>0.10156406657309</v>
+        <v>0.001736111111111111</v>
       </c>
       <c r="AI39">
-        <v>0.1097270363951473</v>
+        <v>0.001288659793814433</v>
       </c>
       <c r="AJ39">
-        <v>0.09802816334336531</v>
+        <v>-0.8323043218482377</v>
       </c>
       <c r="AK39">
-        <v>0.1059404540460573</v>
+        <v>-0.5083323196691401</v>
       </c>
       <c r="AL39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>3.023880597014925</v>
-      </c>
-      <c r="AO39">
-        <v>18.92655367231638</v>
+        <v>-0.05818181818181818</v>
       </c>
       <c r="AP39">
-        <v>2.907164179104478</v>
-      </c>
-      <c r="AQ39">
-        <v>18.92655367231638</v>
+        <v>15.19636363636364</v>
       </c>
     </row>
     <row r="40">
@@ -5455,7 +5542,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Argo Investments Limited (ASX:ARG)</t>
+          <t>Plato Income Maximiser Limited (ASX:PL8)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5463,47 +5550,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D40">
-        <v>-0.026</v>
-      </c>
-      <c r="E40">
-        <v>-0.0426</v>
-      </c>
-      <c r="G40">
-        <v>0.9606404269513008</v>
-      </c>
-      <c r="H40">
-        <v>0.9606404269513008</v>
-      </c>
-      <c r="I40">
-        <v>0.9586390927284856</v>
-      </c>
-      <c r="J40">
-        <v>0.9283213307758252</v>
-      </c>
       <c r="K40">
-        <v>130.4</v>
-      </c>
-      <c r="L40">
-        <v>0.8699132755170114</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="M40">
-        <v>123</v>
+        <v>21.1</v>
       </c>
       <c r="N40">
-        <v>0.02285183464932652</v>
+        <v>0.04146197681273335</v>
       </c>
       <c r="O40">
-        <v>0.9432515337423313</v>
+        <v>-2.381489841986456</v>
       </c>
       <c r="P40">
-        <v>123</v>
+        <v>21.1</v>
       </c>
       <c r="Q40">
-        <v>0.02285183464932652</v>
+        <v>0.04146197681273335</v>
       </c>
       <c r="R40">
-        <v>0.9432515337423313</v>
+        <v>-2.381489841986456</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -5512,67 +5578,61 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>134.4</v>
+        <v>0.143</v>
       </c>
       <c r="V40">
-        <v>0.02496980956804459</v>
+        <v>0.000280998231479662</v>
       </c>
       <c r="W40">
-        <v>0.03999631935711438</v>
+        <v>-0.02437414030261348</v>
       </c>
       <c r="X40">
-        <v>0.04387592397819244</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y40">
-        <v>-0.003879604621078066</v>
+        <v>-0.09682835934331833</v>
       </c>
       <c r="Z40">
-        <v>0.04766714026413765</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>0.04425042308428218</v>
+        <v>-0.08653689806559717</v>
       </c>
       <c r="AB40">
-        <v>0.04387187829066282</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC40">
-        <v>0.0003785447936193662</v>
+        <v>-0.158991117106302</v>
       </c>
       <c r="AD40">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0.791</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>-133.609</v>
+        <v>-0.143</v>
       </c>
       <c r="AH40">
-        <v>0.0001469361399931752</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>0.0001868831644730143</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>-0.02545471033785994</v>
+        <v>-0.0002810772136796152</v>
       </c>
       <c r="AK40">
-        <v>-0.03260194559013965</v>
+        <v>-0.0003594256227740117</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
         <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>0.005493055555555556</v>
-      </c>
-      <c r="AP40">
-        <v>-0.9278402777777779</v>
       </c>
     </row>
     <row r="41">
@@ -5583,7 +5643,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Diversified United Investment Limited (ASX:DUI)</t>
+          <t>Cadence Opportunities Fund Limited (ASX:CDO)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5591,47 +5651,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D41">
-        <v>0.0151</v>
-      </c>
-      <c r="E41">
-        <v>0.00328</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0.9625850340136055</v>
-      </c>
-      <c r="J41">
-        <v>0.8459080601937745</v>
-      </c>
       <c r="K41">
-        <v>23.2</v>
-      </c>
-      <c r="L41">
-        <v>0.7891156462585034</v>
+        <v>-1.05</v>
       </c>
       <c r="M41">
-        <v>21.4</v>
+        <v>0.737</v>
       </c>
       <c r="N41">
-        <v>0.02663347853142501</v>
+        <v>0.03122881355932203</v>
       </c>
       <c r="O41">
-        <v>0.9224137931034483</v>
+        <v>-0.7019047619047618</v>
       </c>
       <c r="P41">
-        <v>21.4</v>
+        <v>0.737</v>
       </c>
       <c r="Q41">
-        <v>0.02663347853142501</v>
+        <v>0.03122881355932203</v>
       </c>
       <c r="R41">
-        <v>0.9224137931034483</v>
+        <v>-0.7019047619047618</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -5640,67 +5679,67 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>3.87</v>
+        <v>16.6</v>
       </c>
       <c r="V41">
-        <v>0.004816428126944617</v>
+        <v>0.7033898305084746</v>
       </c>
       <c r="W41">
-        <v>0.04177921844048262</v>
+        <v>-0.06363636363636364</v>
       </c>
       <c r="X41">
-        <v>0.04608133832361882</v>
+        <v>0.07417115462227303</v>
       </c>
       <c r="Y41">
-        <v>-0.004302119883136196</v>
+        <v>-0.1378075182586367</v>
       </c>
       <c r="Z41">
-        <v>0.05046343975283213</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>0.04268743043202364</v>
+        <v>-0.1142225497420781</v>
       </c>
       <c r="AB41">
-        <v>0.04314278837256987</v>
+        <v>0.07192869072218182</v>
       </c>
       <c r="AC41">
-        <v>-0.0004553579405462346</v>
+        <v>-0.1861512404642599</v>
       </c>
       <c r="AD41">
-        <v>88.09999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>88.09999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="AG41">
-        <v>84.22999999999999</v>
+        <v>-14.88</v>
       </c>
       <c r="AH41">
-        <v>0.09881112606550022</v>
+        <v>0.0679304897314376</v>
       </c>
       <c r="AI41">
-        <v>0.1112092905831861</v>
+        <v>0.06661502711076685</v>
       </c>
       <c r="AJ41">
-        <v>0.09488245299809625</v>
+        <v>-1.706422018348624</v>
       </c>
       <c r="AK41">
-        <v>0.1068461177425697</v>
+        <v>-1.613882863340564</v>
       </c>
       <c r="AL41">
-        <v>1.89</v>
+        <v>0.103</v>
       </c>
       <c r="AM41">
-        <v>1.89</v>
+        <v>0.103</v>
       </c>
       <c r="AO41">
-        <v>14.97354497354497</v>
+        <v>-15.04854368932039</v>
       </c>
       <c r="AQ41">
-        <v>14.97354497354497</v>
+        <v>-15.04854368932039</v>
       </c>
     </row>
     <row r="42">
@@ -5711,7 +5750,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Australian Foundation Investment Company Limited (ASX:AFI)</t>
+          <t>Pacific Current Group Limited (ASX:PAC)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5719,47 +5758,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D42">
-        <v>-0.0219</v>
-      </c>
-      <c r="E42">
-        <v>-0.0245</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0.9411167512690356</v>
-      </c>
-      <c r="J42">
-        <v>0.8923143549149016</v>
-      </c>
       <c r="K42">
-        <v>175.9</v>
-      </c>
-      <c r="L42">
-        <v>0.8928934010152284</v>
+        <v>-24.3</v>
       </c>
       <c r="M42">
-        <v>166.3</v>
+        <v>12.8</v>
       </c>
       <c r="N42">
-        <v>0.02205043888726829</v>
+        <v>0.05011746280344558</v>
       </c>
       <c r="O42">
-        <v>0.9454235361000569</v>
+        <v>-0.5267489711934157</v>
       </c>
       <c r="P42">
-        <v>166.3</v>
+        <v>12.8</v>
       </c>
       <c r="Q42">
-        <v>0.02205043888726829</v>
+        <v>0.05011746280344558</v>
       </c>
       <c r="R42">
-        <v>0.9454235361000569</v>
+        <v>-0.5267489711934157</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -5768,67 +5786,73 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>72.8</v>
+        <v>24</v>
       </c>
       <c r="V42">
-        <v>0.009652868015593095</v>
+        <v>0.09397024275646045</v>
       </c>
       <c r="W42">
-        <v>0.04083006429748613</v>
+        <v>-0.08054358634405039</v>
       </c>
       <c r="X42">
-        <v>0.04387296409148227</v>
+        <v>0.07252109263570547</v>
       </c>
       <c r="Y42">
-        <v>-0.003042899793996148</v>
+        <v>-0.1530646789797558</v>
       </c>
       <c r="Z42">
-        <v>0.04655889582151634</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>0.04154517109052647</v>
+        <v>-0.1316047158356508</v>
       </c>
       <c r="AB42">
-        <v>0.04387296409148227</v>
+        <v>0.07240953366191968</v>
       </c>
       <c r="AC42">
-        <v>-0.002327793000955806</v>
+        <v>-0.2040142494975705</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>0.725</v>
       </c>
       <c r="AG42">
-        <v>-72.8</v>
+        <v>-23.275</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>0.002830649097120547</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>0.001993812306634582</v>
       </c>
       <c r="AJ42">
-        <v>-0.009746954076850984</v>
+        <v>-0.1002692514808831</v>
       </c>
       <c r="AK42">
-        <v>-0.01301278040933059</v>
+        <v>-0.06853146853146853</v>
       </c>
       <c r="AL42">
-        <v>1.37</v>
+        <v>0.041</v>
       </c>
       <c r="AM42">
-        <v>1.37</v>
+        <v>0.041</v>
+      </c>
+      <c r="AN42">
+        <v>-0.02301587301587301</v>
       </c>
       <c r="AO42">
-        <v>135.3284671532847</v>
+        <v>-819.5121951219512</v>
+      </c>
+      <c r="AP42">
+        <v>0.7388888888888888</v>
       </c>
       <c r="AQ42">
-        <v>135.3284671532847</v>
+        <v>-819.5121951219512</v>
       </c>
     </row>
     <row r="43">
@@ -5839,7 +5863,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BKI Investment Company Limited (ASX:BKI)</t>
+          <t>Spheria Emerging Companies Limited (ASX:SEC)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5847,47 +5871,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D43">
-        <v>-0.0174</v>
-      </c>
-      <c r="E43">
-        <v>-0.0281</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0.9501661129568106</v>
-      </c>
-      <c r="J43">
-        <v>0.8884376341898885</v>
-      </c>
       <c r="K43">
-        <v>27.5</v>
-      </c>
-      <c r="L43">
-        <v>0.9136212624584718</v>
+        <v>-9.23</v>
       </c>
       <c r="M43">
-        <v>20.1</v>
+        <v>5.22</v>
       </c>
       <c r="N43">
-        <v>0.02241302408563783</v>
+        <v>0.06752910737386805</v>
       </c>
       <c r="O43">
-        <v>0.730909090909091</v>
+        <v>-0.5655471289274105</v>
       </c>
       <c r="P43">
-        <v>20.1</v>
+        <v>5.22</v>
       </c>
       <c r="Q43">
-        <v>0.02241302408563783</v>
+        <v>0.06752910737386805</v>
       </c>
       <c r="R43">
-        <v>0.730909090909091</v>
+        <v>-0.5655471289274105</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -5896,31 +5899,31 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>30.4</v>
+        <v>2.32</v>
       </c>
       <c r="V43">
-        <v>0.03389830508474576</v>
+        <v>0.03001293661060802</v>
       </c>
       <c r="W43">
-        <v>0.03800967519004837</v>
+        <v>-0.08189884649511979</v>
       </c>
       <c r="X43">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y43">
-        <v>-0.005863288901433901</v>
+        <v>-0.1543530655358246</v>
       </c>
       <c r="Z43">
-        <v>0.0436105476673428</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>0.0387452517952994</v>
+        <v>-0.1316028317298965</v>
       </c>
       <c r="AB43">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC43">
-        <v>-0.005127712296182876</v>
+        <v>-0.2040570507706014</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -5932,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>-30.4</v>
+        <v>-2.32</v>
       </c>
       <c r="AH43">
         <v>0</v>
@@ -5941,19 +5944,16 @@
         <v>0</v>
       </c>
       <c r="AJ43">
-        <v>-0.03508771929824561</v>
+        <v>-0.03094158442251266</v>
       </c>
       <c r="AK43">
-        <v>-0.03582370963940608</v>
+        <v>-0.02673427056925559</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-0.766</v>
-      </c>
-      <c r="AQ43">
-        <v>-37.33681462140992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Carlton Investments Limited (ASX:CIN)</t>
+          <t>Tribeca Global Natural Resources Limited (ASX:TGF)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5972,116 +5972,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D44">
-        <v>-0.127</v>
-      </c>
-      <c r="E44">
-        <v>-0.128</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0.9575757575757576</v>
-      </c>
-      <c r="J44">
-        <v>0.9553333333333335</v>
-      </c>
       <c r="K44">
-        <v>15.8</v>
-      </c>
-      <c r="L44">
-        <v>0.9575757575757576</v>
+        <v>-8.15</v>
       </c>
       <c r="M44">
-        <v>16.3</v>
+        <v>-0</v>
       </c>
       <c r="N44">
-        <v>0.02687108473458622</v>
+        <v>-0</v>
       </c>
       <c r="O44">
-        <v>1.031645569620253</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>16.3</v>
+        <v>-0</v>
       </c>
       <c r="Q44">
-        <v>0.02687108473458622</v>
+        <v>-0</v>
       </c>
       <c r="R44">
-        <v>1.031645569620253</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
       </c>
-      <c r="T44">
-        <v>0</v>
-      </c>
       <c r="U44">
-        <v>12.9</v>
+        <v>41.4</v>
       </c>
       <c r="V44">
-        <v>0.02126607319485658</v>
+        <v>0.4404255319148936</v>
       </c>
       <c r="W44">
-        <v>0.03507214206437292</v>
+        <v>-0.06953924914675769</v>
       </c>
       <c r="X44">
-        <v>0.0438770812910918</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y44">
-        <v>-0.008804939226718884</v>
+        <v>-0.1419934681874626</v>
       </c>
       <c r="Z44">
-        <v>0.0379908591690363</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>0.03629393412615268</v>
+        <v>-0.139030612244898</v>
       </c>
       <c r="AB44">
-        <v>0.04387145383033849</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC44">
-        <v>-0.007577519704185812</v>
+        <v>-0.2114848312856028</v>
       </c>
       <c r="AD44">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>-12.776</v>
+        <v>-41.4</v>
       </c>
       <c r="AH44">
-        <v>0.0002043762897132798</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>0.0001952374654398196</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
-        <v>-0.02151479226168022</v>
+        <v>-0.7870722433460076</v>
       </c>
       <c r="AK44">
-        <v>-0.02053279847771863</v>
+        <v>-0.711340206185567</v>
       </c>
       <c r="AL44">
-        <v>0.008999999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="AM44">
-        <v>0.008999999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="AO44">
-        <v>1755.555555555556</v>
+        <v>-15.15994436717664</v>
       </c>
       <c r="AQ44">
-        <v>1755.555555555556</v>
+        <v>-15.15994436717664</v>
       </c>
     </row>
     <row r="45">
@@ -6092,7 +6068,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Amcil Limited (ASX:AMH)</t>
+          <t>Hearts and Minds Investments Limited (ASX:HM1)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6100,47 +6076,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D45">
-        <v>-0.0344</v>
-      </c>
-      <c r="E45">
-        <v>-0.0249</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0.7874617737003059</v>
-      </c>
-      <c r="J45">
-        <v>0.7874617737003059</v>
-      </c>
       <c r="K45">
-        <v>5.08</v>
-      </c>
-      <c r="L45">
-        <v>0.7767584097859327</v>
+        <v>-65.3</v>
       </c>
       <c r="M45">
-        <v>5.16</v>
+        <v>17.4</v>
       </c>
       <c r="N45">
-        <v>0.01755102040816326</v>
+        <v>0.04927782497875955</v>
       </c>
       <c r="O45">
-        <v>1.015748031496063</v>
+        <v>-0.2664624808575804</v>
       </c>
       <c r="P45">
-        <v>5.16</v>
+        <v>17.4</v>
       </c>
       <c r="Q45">
-        <v>0.01755102040816326</v>
+        <v>0.04927782497875955</v>
       </c>
       <c r="R45">
-        <v>1.015748031496063</v>
+        <v>-0.2664624808575804</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -6149,31 +6104,31 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>8.199999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="V45">
-        <v>0.02789115646258503</v>
+        <v>0.2381761540640045</v>
       </c>
       <c r="W45">
-        <v>0.02886363636363637</v>
+        <v>-0.09829896131265994</v>
       </c>
       <c r="X45">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y45">
-        <v>-0.01500932772784591</v>
+        <v>-0.1707531803533648</v>
       </c>
       <c r="Z45">
-        <v>0.03854768360249912</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>0.03035482730166215</v>
+        <v>-0.1630510846745976</v>
       </c>
       <c r="AB45">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC45">
-        <v>-0.01351813678982012</v>
+        <v>-0.2355053037153025</v>
       </c>
       <c r="AD45">
         <v>0</v>
@@ -6185,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="AG45">
-        <v>-8.199999999999999</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="AH45">
         <v>0</v>
@@ -6194,22 +6149,22 @@
         <v>0</v>
       </c>
       <c r="AJ45">
-        <v>-0.02869139258222533</v>
+        <v>-0.3126394052044609</v>
       </c>
       <c r="AK45">
-        <v>-0.03371710526315789</v>
+        <v>-0.2351789709172259</v>
       </c>
       <c r="AL45">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="AM45">
-        <v>0.07099999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="AO45">
-        <v>72.53521126760565</v>
+        <v>-2588.888888888889</v>
       </c>
       <c r="AQ45">
-        <v>72.53521126760565</v>
+        <v>-2588.888888888889</v>
       </c>
     </row>
     <row r="46">
@@ -6220,7 +6175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mirrabooka Investments Limited (ASX:MIR)</t>
+          <t>Auctus Investment Group Limited (ASX:AVC)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6229,115 +6184,112 @@
         </is>
       </c>
       <c r="D46">
-        <v>-0.0336</v>
-      </c>
-      <c r="E46">
-        <v>-0.06150000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>-0.1532663316582915</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>-0.1532663316582915</v>
       </c>
       <c r="I46">
-        <v>0.7452574525745258</v>
+        <v>-0.1595477386934673</v>
       </c>
       <c r="J46">
-        <v>0.6653592413927837</v>
+        <v>-0.1595477386934673</v>
       </c>
       <c r="K46">
-        <v>4.83</v>
+        <v>-1.44</v>
       </c>
       <c r="L46">
-        <v>0.6544715447154472</v>
+        <v>-0.1809045226130653</v>
       </c>
       <c r="M46">
-        <v>10.1</v>
+        <v>0.545</v>
       </c>
       <c r="N46">
-        <v>0.01984672823737473</v>
+        <v>0.01216517857142857</v>
       </c>
       <c r="O46">
-        <v>2.091097308488613</v>
+        <v>-0.3784722222222223</v>
       </c>
       <c r="P46">
-        <v>10.1</v>
+        <v>-0</v>
       </c>
       <c r="Q46">
-        <v>0.01984672823737473</v>
+        <v>-0</v>
       </c>
       <c r="R46">
-        <v>2.091097308488613</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46">
-        <v>20.9</v>
+        <v>7.28</v>
       </c>
       <c r="V46">
-        <v>0.04106897229318137</v>
+        <v>0.1625</v>
       </c>
       <c r="W46">
-        <v>0.02004149377593361</v>
+        <v>-0.07539267015706805</v>
       </c>
       <c r="X46">
-        <v>0.04387296409148227</v>
+        <v>0.0733060914601727</v>
       </c>
       <c r="Y46">
-        <v>-0.02383147031554866</v>
+        <v>-0.1486987616172407</v>
       </c>
       <c r="Z46">
-        <v>0.03251101321585903</v>
+        <v>1.081815710790976</v>
       </c>
       <c r="AA46">
-        <v>0.02163150309021473</v>
+        <v>-0.1726012503397663</v>
       </c>
       <c r="AB46">
-        <v>0.04387296409148227</v>
+        <v>0.07209140235708179</v>
       </c>
       <c r="AC46">
-        <v>-0.02224146100126755</v>
+        <v>-0.244692652696848</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>-20.9</v>
+        <v>-5.66</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>0.03489875053856097</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>0.06347962382445142</v>
       </c>
       <c r="AJ46">
-        <v>-0.04282786885245901</v>
+        <v>-0.14460909555442</v>
       </c>
       <c r="AK46">
-        <v>-0.05690171521916688</v>
+        <v>-0.3103070175438597</v>
       </c>
       <c r="AL46">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM46">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AO46">
-        <v>62.50000000000001</v>
-      </c>
-      <c r="AQ46">
-        <v>62.50000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="AN46">
+        <v>-1.327868852459017</v>
+      </c>
+      <c r="AP46">
+        <v>4.639344262295082</v>
       </c>
     </row>
     <row r="47">
@@ -6348,7 +6300,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pinnacle Investment Management Group Limited (ASX:PNI)</t>
+          <t>Benjamin Hornigold Limited (ASX:BHD)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6356,125 +6308,86 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D47">
-        <v>0.311</v>
-      </c>
-      <c r="E47">
-        <v>0.7140000000000001</v>
-      </c>
-      <c r="F47">
-        <v>0.189</v>
-      </c>
-      <c r="G47">
-        <v>0.109016393442623</v>
-      </c>
-      <c r="H47">
-        <v>0.109016393442623</v>
-      </c>
-      <c r="I47">
-        <v>0.0807377049180328</v>
-      </c>
-      <c r="J47">
-        <v>0.0807377049180328</v>
-      </c>
       <c r="K47">
-        <v>50.2</v>
-      </c>
-      <c r="L47">
-        <v>2.057377049180328</v>
+        <v>-0.854</v>
       </c>
       <c r="M47">
-        <v>27.7</v>
+        <v>-0</v>
       </c>
       <c r="N47">
-        <v>0.01223390159879869</v>
+        <v>-0</v>
       </c>
       <c r="O47">
-        <v>0.5517928286852589</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>27.7</v>
+        <v>-0</v>
       </c>
       <c r="Q47">
-        <v>0.01223390159879869</v>
+        <v>-0</v>
       </c>
       <c r="R47">
-        <v>0.5517928286852589</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
       <c r="U47">
-        <v>72.09999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="V47">
-        <v>0.03184347672467096</v>
+        <v>0.247978436657682</v>
       </c>
       <c r="W47">
-        <v>0.3855606758832566</v>
+        <v>-0.1332293291731669</v>
       </c>
       <c r="X47">
-        <v>0.04455969272830928</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y47">
-        <v>0.3410009831549473</v>
+        <v>-0.2056835482138718</v>
       </c>
       <c r="Z47">
-        <v>0.1712280701754386</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>0.01382456140350877</v>
+        <v>-0.1742857142857143</v>
       </c>
       <c r="AB47">
-        <v>0.0437358962015768</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC47">
-        <v>-0.02991133479806803</v>
+        <v>-0.2467399333264191</v>
       </c>
       <c r="AD47">
-        <v>77.2</v>
+        <v>0</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>77.2</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>5.100000000000009</v>
+        <v>-0.92</v>
       </c>
       <c r="AH47">
-        <v>0.03297172631758778</v>
+        <v>0</v>
       </c>
       <c r="AI47">
-        <v>0.2968089196462899</v>
+        <v>0</v>
       </c>
       <c r="AJ47">
-        <v>0.002247389062706565</v>
+        <v>-0.3297491039426523</v>
       </c>
       <c r="AK47">
-        <v>0.02712765957446813</v>
+        <v>-0.2233009708737864</v>
       </c>
       <c r="AL47">
-        <v>0.487</v>
+        <v>0</v>
       </c>
       <c r="AM47">
-        <v>0.487</v>
-      </c>
-      <c r="AN47">
-        <v>29.02255639097744</v>
-      </c>
-      <c r="AO47">
-        <v>4.04517453798768</v>
-      </c>
-      <c r="AP47">
-        <v>1.91729323308271</v>
-      </c>
-      <c r="AQ47">
-        <v>4.04517453798768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6485,7 +6398,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hearts and Minds Investments Limited (ASX:HM1)</t>
+          <t>Sandon Capital Investments Limited (ASX:SNC)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6493,41 +6406,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0.7772151898734176</v>
-      </c>
-      <c r="J48">
-        <v>0.7772151898734176</v>
-      </c>
       <c r="K48">
-        <v>-9.34</v>
-      </c>
-      <c r="L48">
-        <v>-2.364556962025316</v>
+        <v>-16.3</v>
       </c>
       <c r="M48">
-        <v>16.8</v>
+        <v>3.61</v>
       </c>
       <c r="N48">
-        <v>0.02574712643678161</v>
+        <v>0.0586038961038961</v>
       </c>
       <c r="O48">
-        <v>-1.798715203426124</v>
+        <v>-0.2214723926380368</v>
       </c>
       <c r="P48">
-        <v>16.8</v>
+        <v>3.61</v>
       </c>
       <c r="Q48">
-        <v>0.02574712643678161</v>
+        <v>0.0586038961038961</v>
       </c>
       <c r="R48">
-        <v>-1.798715203426124</v>
+        <v>-0.2214723926380368</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -6536,31 +6434,31 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>92.7</v>
+        <v>0.359</v>
       </c>
       <c r="V48">
-        <v>0.1420689655172414</v>
+        <v>0.005827922077922078</v>
       </c>
       <c r="W48">
-        <v>-0.0180239289849479</v>
+        <v>-0.1858608893956671</v>
       </c>
       <c r="X48">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y48">
-        <v>-0.06189689307643017</v>
+        <v>-0.2583151084363719</v>
       </c>
       <c r="Z48">
-        <v>0.008193320887782617</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>0.006367973449491806</v>
+        <v>-0.2440158029281896</v>
       </c>
       <c r="AB48">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC48">
-        <v>-0.03750499064199047</v>
+        <v>-0.3164700219688945</v>
       </c>
       <c r="AD48">
         <v>0</v>
@@ -6572,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="AG48">
-        <v>-92.7</v>
+        <v>-0.359</v>
       </c>
       <c r="AH48">
         <v>0</v>
@@ -6581,22 +6479,16 @@
         <v>0</v>
       </c>
       <c r="AJ48">
-        <v>-0.1655948553054662</v>
+        <v>-0.005862085857513757</v>
       </c>
       <c r="AK48">
-        <v>-0.1621763470958713</v>
+        <v>-0.004784051385242733</v>
       </c>
       <c r="AL48">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM48">
-        <v>0.004</v>
-      </c>
-      <c r="AO48">
-        <v>767.5</v>
-      </c>
-      <c r="AQ48">
-        <v>767.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6607,7 +6499,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MA Financial Group Limited (ASX:MAF)</t>
+          <t>Thorney Technologies Ltd (ASX:TEK)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6615,104 +6507,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
       <c r="K49">
-        <v>23.9</v>
-      </c>
-      <c r="L49">
-        <v>0.1715721464465183</v>
+        <v>-31.1</v>
       </c>
       <c r="M49">
-        <v>15.93</v>
+        <v>-0</v>
       </c>
       <c r="N49">
-        <v>0.0151858913250715</v>
+        <v>-0</v>
       </c>
       <c r="O49">
-        <v>0.6665271966527196</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>11.2</v>
+        <v>-0</v>
       </c>
       <c r="Q49">
-        <v>0.01067683508102955</v>
+        <v>-0</v>
       </c>
       <c r="R49">
-        <v>0.4686192468619247</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>4.73</v>
-      </c>
-      <c r="T49">
-        <v>0.2969240426867546</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>80.2</v>
+        <v>6.43</v>
       </c>
       <c r="V49">
-        <v>0.07645376549094376</v>
+        <v>0.1099145299145299</v>
       </c>
       <c r="W49">
-        <v>0.1623641304347826</v>
+        <v>-0.236322188449848</v>
       </c>
       <c r="X49">
-        <v>0.04840614595554259</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y49">
-        <v>0.11395798447924</v>
+        <v>-0.3087764074905529</v>
       </c>
       <c r="Z49">
-        <v>0.630830540711892</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>-0.3575092731433983</v>
       </c>
       <c r="AB49">
-        <v>0.04310921078356077</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC49">
-        <v>-0.04310921078356077</v>
+        <v>-0.4299634921841032</v>
       </c>
       <c r="AD49">
-        <v>236.1</v>
+        <v>0</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>236.1</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>155.9</v>
+        <v>-6.43</v>
       </c>
       <c r="AH49">
-        <v>0.1837211111975722</v>
+        <v>0</v>
       </c>
       <c r="AI49">
-        <v>0.558288011350201</v>
+        <v>0</v>
       </c>
       <c r="AJ49">
-        <v>0.1293883309818242</v>
+        <v>-0.1234876128288842</v>
       </c>
       <c r="AK49">
-        <v>0.4549168368835716</v>
+        <v>-0.06412685748479105</v>
       </c>
       <c r="AL49">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM49">
-        <v>0</v>
+        <v>0.001</v>
+      </c>
+      <c r="AO49">
+        <v>-45299.99999999999</v>
+      </c>
+      <c r="AQ49">
+        <v>-45299.99999999999</v>
       </c>
     </row>
     <row r="50">
@@ -6723,7 +6603,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Keybridge Capital Limited (ASX:KBC)</t>
+          <t>First Growth Funds Limited (CNSX:FGFL)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6731,26 +6611,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D50">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
       <c r="K50">
-        <v>2.2</v>
-      </c>
-      <c r="L50">
-        <v>0.04143126177024482</v>
+        <v>-1.76</v>
       </c>
       <c r="M50">
         <v>-0</v>
@@ -6759,7 +6621,7 @@
         <v>-0</v>
       </c>
       <c r="O50">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P50">
         <v>-0</v>
@@ -6768,61 +6630,61 @@
         <v>-0</v>
       </c>
       <c r="R50">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
       </c>
       <c r="U50">
-        <v>0.095</v>
+        <v>0.288</v>
       </c>
       <c r="V50">
-        <v>0.008189655172413794</v>
+        <v>0.5052631578947369</v>
       </c>
       <c r="W50">
-        <v>0.3470031545741326</v>
+        <v>-0.3358778625954199</v>
       </c>
       <c r="X50">
-        <v>0.04409347413525234</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y50">
-        <v>0.3029096804388802</v>
+        <v>-0.4083320816361247</v>
       </c>
       <c r="Z50">
-        <v>5.366889023650698</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>-0.3675048355899419</v>
       </c>
       <c r="AB50">
-        <v>0.04379293676026194</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC50">
-        <v>-0.04379293676026194</v>
+        <v>-0.4399590546306468</v>
       </c>
       <c r="AD50">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="AE50">
         <v>0</v>
       </c>
       <c r="AF50">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>0.032</v>
+        <v>-0.288</v>
       </c>
       <c r="AH50">
-        <v>0.01082970921804383</v>
+        <v>0</v>
       </c>
       <c r="AI50">
-        <v>0.01254073269477634</v>
+        <v>0</v>
       </c>
       <c r="AJ50">
-        <v>0.002751031636863824</v>
+        <v>-1.021276595744681</v>
       </c>
       <c r="AK50">
-        <v>0.003189792663476874</v>
+        <v>-0.110260336906585</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -6839,7 +6701,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iQ3Corp Ltd (ASX:IQ3)</t>
+          <t>Touch Ventures Limited (ASX:TVL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6847,35 +6709,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D51">
-        <v>0.0252</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
       <c r="K51">
-        <v>-4.25</v>
-      </c>
-      <c r="L51">
-        <v>-2.361111111111111</v>
+        <v>-20.6</v>
       </c>
       <c r="M51">
-        <v>-0</v>
+        <v>0.106</v>
       </c>
       <c r="N51">
-        <v>-0</v>
+        <v>0.002334801762114537</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>-0.005145631067961165</v>
       </c>
       <c r="P51">
         <v>-0</v>
@@ -6887,64 +6731,76 @@
         <v>0</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>0.106</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
       </c>
       <c r="U51">
-        <v>0.179</v>
+        <v>44.1</v>
       </c>
       <c r="V51">
-        <v>0.02096018735362998</v>
+        <v>0.9713656387665199</v>
       </c>
       <c r="W51">
-        <v>6.231671554252199</v>
+        <v>-0.2947067238912732</v>
       </c>
       <c r="X51">
-        <v>0.05630194120313076</v>
+        <v>0.07247192550081355</v>
       </c>
       <c r="Y51">
-        <v>6.175369613049068</v>
+        <v>-0.3671786493920868</v>
       </c>
       <c r="Z51">
-        <v>-10.6508875739645</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>-0</v>
+        <v>-0.3993765525303199</v>
       </c>
       <c r="AB51">
-        <v>0.04460047323052364</v>
+        <v>0.07244641094261713</v>
       </c>
       <c r="AC51">
-        <v>-0.04460047323052364</v>
+        <v>-0.471822963472937</v>
       </c>
       <c r="AD51">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>0.03412322274881516</v>
       </c>
       <c r="AF51">
-        <v>5.27</v>
+        <v>0.03412322274881516</v>
       </c>
       <c r="AG51">
-        <v>5.090999999999999</v>
+        <v>-44.06587677725118</v>
       </c>
       <c r="AH51">
-        <v>0.3816075307748009</v>
+        <v>0.0007510483383055515</v>
       </c>
       <c r="AI51">
-        <v>21.08</v>
+        <v>0.0003092717080818711</v>
       </c>
       <c r="AJ51">
-        <v>0.3734869048492407</v>
+        <v>-33.02984014209592</v>
       </c>
       <c r="AK51">
-        <v>71.70422535211294</v>
+        <v>-0.6653047497746039</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>0</v>
+        <v>-0.05</v>
+      </c>
+      <c r="AN51">
+        <v>0</v>
+      </c>
+      <c r="AP51">
+        <v>-1224.052132701422</v>
+      </c>
+      <c r="AQ51">
+        <v>497.9999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -6955,7 +6811,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ECP Emerging Growth Limited (ASX:ECP)</t>
+          <t>Hygrovest Limited (ASX:HGV)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6963,110 +6819,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D52">
-        <v>-0.0532</v>
-      </c>
-      <c r="E52">
-        <v>0.416</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>-6.89922480620155</v>
-      </c>
-      <c r="J52">
-        <v>-4.874352718325664</v>
-      </c>
       <c r="K52">
-        <v>5.32</v>
-      </c>
-      <c r="L52">
-        <v>20.62015503875969</v>
+        <v>-11</v>
       </c>
       <c r="M52">
-        <v>0.357</v>
+        <v>-0</v>
       </c>
       <c r="N52">
-        <v>0.01733009708737864</v>
+        <v>-0</v>
       </c>
       <c r="O52">
-        <v>0.06710526315789472</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>0.357</v>
+        <v>-0</v>
       </c>
       <c r="Q52">
-        <v>0.01733009708737864</v>
+        <v>-0</v>
       </c>
       <c r="R52">
-        <v>0.06710526315789472</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
       </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
       <c r="U52">
-        <v>2.83</v>
+        <v>4.35</v>
       </c>
       <c r="V52">
-        <v>0.137378640776699</v>
+        <v>0.3990825688073394</v>
       </c>
       <c r="W52">
-        <v>0.318562874251497</v>
+        <v>-0.3642384105960265</v>
       </c>
       <c r="X52">
-        <v>0.04387296409148227</v>
+        <v>0.0725750868389901</v>
       </c>
       <c r="Y52">
-        <v>0.2746899101600148</v>
+        <v>-0.4368134974350166</v>
       </c>
       <c r="Z52">
-        <v>0.01884587289992696</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>-0.09186143179897892</v>
+        <v>-0.4427019223853608</v>
       </c>
       <c r="AB52">
-        <v>0.04387296409148227</v>
+        <v>0.07240115162910124</v>
       </c>
       <c r="AC52">
-        <v>-0.1357343958904612</v>
+        <v>-0.515103074014462</v>
       </c>
       <c r="AD52">
         <v>0</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>0.05592417061611375</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>0.05592417061611375</v>
       </c>
       <c r="AG52">
-        <v>-2.83</v>
+        <v>-4.294075829383886</v>
       </c>
       <c r="AH52">
-        <v>0</v>
+        <v>0.005104468572911709</v>
       </c>
       <c r="AI52">
-        <v>0</v>
+        <v>0.003317775403475229</v>
       </c>
       <c r="AJ52">
-        <v>-0.1592571750140686</v>
+        <v>-0.6500340782724109</v>
       </c>
       <c r="AK52">
-        <v>-0.1410064773293473</v>
+        <v>-0.3433633349123638</v>
       </c>
       <c r="AL52">
         <v>0</v>
       </c>
       <c r="AM52">
         <v>0</v>
+      </c>
+      <c r="AN52">
+        <v>-0</v>
+      </c>
+      <c r="AP52">
+        <v>0.3507945289914129</v>
       </c>
     </row>
     <row r="53">
@@ -7077,7 +6915,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fatfish Group Limited (ASX:FFG)</t>
+          <t>K2 Asset Management Holdings Ltd (ASX:KAM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7086,34 +6924,34 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.0356</v>
+        <v>-0.342</v>
       </c>
       <c r="G53">
-        <v>-1.315942028985507</v>
+        <v>-0.7013698630136986</v>
       </c>
       <c r="H53">
-        <v>-1.315942028985507</v>
+        <v>-0.7397260273972603</v>
       </c>
       <c r="I53">
-        <v>-2.098550724637681</v>
+        <v>-0.7602739726027398</v>
       </c>
       <c r="J53">
-        <v>-2.098550724637681</v>
+        <v>-0.7602739726027398</v>
       </c>
       <c r="K53">
-        <v>-1.3</v>
+        <v>-1.66</v>
       </c>
       <c r="L53">
-        <v>-3.768115942028986</v>
+        <v>-1.136986301369863</v>
       </c>
       <c r="M53">
-        <v>0.113</v>
+        <v>-0</v>
       </c>
       <c r="N53">
-        <v>0.003062330623306233</v>
+        <v>-0</v>
       </c>
       <c r="O53">
-        <v>-0.08692307692307692</v>
+        <v>0</v>
       </c>
       <c r="P53">
         <v>-0</v>
@@ -7125,79 +6963,76 @@
         <v>0</v>
       </c>
       <c r="S53">
-        <v>0.113</v>
-      </c>
-      <c r="T53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>0.646</v>
+        <v>7.41</v>
       </c>
       <c r="V53">
-        <v>0.01750677506775068</v>
+        <v>1.027739251040222</v>
       </c>
       <c r="W53">
-        <v>-0.1780821917808219</v>
+        <v>-0.1693877551020408</v>
       </c>
       <c r="X53">
-        <v>0.04390625963529545</v>
+        <v>0.07261432163614122</v>
       </c>
       <c r="Y53">
-        <v>-0.2219884514161174</v>
+        <v>-0.242002076738182</v>
       </c>
       <c r="Z53">
-        <v>0.04899176370349332</v>
+        <v>0.7281795511221942</v>
       </c>
       <c r="AA53">
-        <v>-0.102811701221244</v>
+        <v>-0.5536159600997504</v>
       </c>
       <c r="AB53">
-        <v>0.04394108103335064</v>
+        <v>0.0724019973820882</v>
       </c>
       <c r="AC53">
-        <v>-0.1467527822545946</v>
+        <v>-0.6260179574818386</v>
       </c>
       <c r="AD53">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="AE53">
         <v>0</v>
       </c>
       <c r="AF53">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="AG53">
-        <v>-0.585</v>
+        <v>-7.361</v>
       </c>
       <c r="AH53">
-        <v>0.001650388247071237</v>
+        <v>0.006750241080038573</v>
       </c>
       <c r="AI53">
-        <v>0.00443281738245767</v>
+        <v>0.006622516556291391</v>
       </c>
       <c r="AJ53">
-        <v>-0.0161090458488228</v>
+        <v>48.74834437086099</v>
       </c>
       <c r="AK53">
-        <v>-0.0446054136484941</v>
+        <v>669.1818181818109</v>
       </c>
       <c r="AL53">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="AM53">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="AN53">
-        <v>-0.116412213740458</v>
+        <v>-0.04537037037037037</v>
       </c>
       <c r="AO53">
-        <v>-241.3333333333333</v>
+        <v>-138.75</v>
       </c>
       <c r="AP53">
-        <v>1.116412213740458</v>
+        <v>6.81574074074074</v>
       </c>
       <c r="AQ53">
-        <v>-241.3333333333333</v>
+        <v>-138.75</v>
       </c>
     </row>
     <row r="54">
@@ -7208,7 +7043,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ARC Funds Limited (ASX:ARC)</t>
+          <t>Fatfish Group Limited (ASX:FFG)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7216,32 +7051,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D54">
+        <v>0.119</v>
+      </c>
       <c r="G54">
-        <v>-0</v>
+        <v>-8.233731739707835</v>
       </c>
       <c r="H54">
-        <v>-0</v>
+        <v>-8.233731739707835</v>
       </c>
       <c r="I54">
-        <v>3.390977443609022</v>
+        <v>-9.920318725099602</v>
       </c>
       <c r="J54">
-        <v>3.390977443609022</v>
+        <v>-9.920318725099602</v>
       </c>
       <c r="K54">
-        <v>-0.433</v>
+        <v>-6.9</v>
       </c>
       <c r="L54">
-        <v>3.255639097744361</v>
+        <v>-9.163346613545817</v>
       </c>
       <c r="M54">
-        <v>-0</v>
+        <v>0.103</v>
       </c>
       <c r="N54">
-        <v>-0</v>
+        <v>0.008239999999999999</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>-0.01492753623188406</v>
       </c>
       <c r="P54">
         <v>-0</v>
@@ -7253,70 +7091,79 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>0.103</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
       </c>
       <c r="U54">
-        <v>2.56</v>
+        <v>1.39</v>
       </c>
       <c r="V54">
-        <v>0.1868613138686132</v>
+        <v>0.1112</v>
       </c>
       <c r="W54">
-        <v>-0.1563176895306859</v>
+        <v>-0.4928571428571429</v>
       </c>
       <c r="X54">
-        <v>0.04387296409148227</v>
+        <v>0.08157585856949751</v>
       </c>
       <c r="Y54">
-        <v>-0.2001906536221682</v>
+        <v>-0.5744330014266403</v>
       </c>
       <c r="Z54">
-        <v>-0.04712969525159461</v>
+        <v>0.05693331317102677</v>
       </c>
       <c r="AA54">
-        <v>-0.1598157335223246</v>
+        <v>-0.5647966127324966</v>
       </c>
       <c r="AB54">
-        <v>0.04387296409148227</v>
+        <v>0.08899332365159854</v>
       </c>
       <c r="AC54">
-        <v>-0.2036886976138069</v>
+        <v>-0.6537899363840951</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AE54">
         <v>0</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AG54">
-        <v>-2.56</v>
+        <v>3.45</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>0.279123414071511</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>0.4531835205992509</v>
       </c>
       <c r="AJ54">
-        <v>-0.2298025134649911</v>
+        <v>0.2163009404388715</v>
       </c>
       <c r="AK54">
-        <v>42.66666666666663</v>
+        <v>0.3713670613562972</v>
       </c>
       <c r="AL54">
-        <v>0.002</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AM54">
-        <v>0.002</v>
+        <v>0.5089999999999999</v>
+      </c>
+      <c r="AN54">
+        <v>-0.663013698630137</v>
       </c>
       <c r="AO54">
-        <v>-225.5</v>
+        <v>-13.17460317460318</v>
+      </c>
+      <c r="AP54">
+        <v>-0.4726027397260275</v>
       </c>
       <c r="AQ54">
-        <v>-225.5</v>
+        <v>-14.67583497053045</v>
       </c>
     </row>
     <row r="55">
@@ -7327,7 +7174,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>InvestSMART Group Limited (ASX:INV)</t>
+          <t>DomaCom Limited (ASX:DCL)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7336,37 +7183,34 @@
         </is>
       </c>
       <c r="D55">
-        <v>-0.0487</v>
-      </c>
-      <c r="E55">
-        <v>-0.272</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="G55">
-        <v>0.05917241379310344</v>
+        <v>-0.3336065573770491</v>
       </c>
       <c r="H55">
-        <v>0.05917241379310344</v>
+        <v>-0.3336065573770491</v>
       </c>
       <c r="I55">
-        <v>-0.03503448275862069</v>
+        <v>-0.3344262295081967</v>
       </c>
       <c r="J55">
-        <v>-0.03503448275862069</v>
+        <v>-0.3344262295081967</v>
       </c>
       <c r="K55">
-        <v>0.027</v>
+        <v>-2.36</v>
       </c>
       <c r="L55">
-        <v>0.003724137931034483</v>
+        <v>-0.9672131147540983</v>
       </c>
       <c r="M55">
-        <v>0.02</v>
+        <v>-0</v>
       </c>
       <c r="N55">
-        <v>0.0005376344086021505</v>
+        <v>-0</v>
       </c>
       <c r="O55">
-        <v>0.7407407407407408</v>
+        <v>0</v>
       </c>
       <c r="P55">
         <v>-0</v>
@@ -7375,76 +7219,79 @@
         <v>-0</v>
       </c>
       <c r="R55">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>0.02</v>
-      </c>
-      <c r="T55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>4.86</v>
+        <v>2.44</v>
       </c>
       <c r="V55">
-        <v>0.1306451612903226</v>
+        <v>0.1251282051282051</v>
       </c>
       <c r="W55">
-        <v>0.006192660550458715</v>
+        <v>2.313725490196078</v>
       </c>
       <c r="X55">
-        <v>0.04398991226811217</v>
+        <v>0.07516036342305488</v>
       </c>
       <c r="Y55">
-        <v>-0.03779725171765345</v>
+        <v>2.238565126773024</v>
       </c>
       <c r="Z55">
-        <v>6.438721136767313</v>
+        <v>2.131004366812227</v>
       </c>
       <c r="AA55">
-        <v>-0.2255772646536411</v>
+        <v>-0.7126637554585152</v>
       </c>
       <c r="AB55">
-        <v>0.04384896524127587</v>
+        <v>0.07165710610623598</v>
       </c>
       <c r="AC55">
-        <v>-0.2694262298949169</v>
+        <v>-0.7843208615647512</v>
       </c>
       <c r="AD55">
-        <v>0.216</v>
+        <v>2.24</v>
       </c>
       <c r="AE55">
         <v>0</v>
       </c>
       <c r="AF55">
-        <v>0.216</v>
+        <v>2.24</v>
       </c>
       <c r="AG55">
-        <v>-4.644</v>
+        <v>-0.1999999999999997</v>
       </c>
       <c r="AH55">
-        <v>0.005772931366260422</v>
+        <v>0.1030358785648574</v>
       </c>
       <c r="AI55">
-        <v>0.04213811939133827</v>
+        <v>0.5973333333333334</v>
       </c>
       <c r="AJ55">
-        <v>-0.1426465167711021</v>
+        <v>-0.01036269430051812</v>
       </c>
       <c r="AK55">
-        <v>-17.45864661654135</v>
+        <v>-0.1526717557251906</v>
       </c>
       <c r="AL55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AM55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AN55">
-        <v>0.5034965034965035</v>
+        <v>-2.751842751842752</v>
+      </c>
+      <c r="AO55">
+        <v>-0.8079207920792079</v>
       </c>
       <c r="AP55">
-        <v>-10.82517482517482</v>
+        <v>0.2457002457002454</v>
+      </c>
+      <c r="AQ55">
+        <v>-0.8079207920792079</v>
       </c>
     </row>
     <row r="56">
@@ -7455,7 +7302,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>First Growth Funds Limited (CNSX:FGFL)</t>
+          <t>Associate Global Partners Limited (ASX:APL)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7463,23 +7310,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D56">
+        <v>0.08019999999999999</v>
+      </c>
       <c r="G56">
-        <v>-0</v>
+        <v>-0.1047619047619048</v>
       </c>
       <c r="H56">
-        <v>-0</v>
+        <v>-0.1047619047619048</v>
       </c>
       <c r="I56">
-        <v>5.839285714285714</v>
+        <v>-0.105952380952381</v>
       </c>
       <c r="J56">
-        <v>5.839285714285714</v>
+        <v>-0.105952380952381</v>
       </c>
       <c r="K56">
-        <v>-0.959</v>
+        <v>-0.442</v>
       </c>
       <c r="L56">
-        <v>5.708333333333333</v>
+        <v>-0.1052380952380952</v>
       </c>
       <c r="M56">
         <v>-0</v>
@@ -7503,61 +7353,73 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>0.587</v>
+        <v>4.54</v>
       </c>
       <c r="V56">
-        <v>0.2386178861788618</v>
+        <v>0.461851475076297</v>
       </c>
       <c r="W56">
-        <v>-0.1561889250814332</v>
+        <v>-0.06287339971550497</v>
       </c>
       <c r="X56">
-        <v>0.04387296409148227</v>
+        <v>0.07513833986755253</v>
       </c>
       <c r="Y56">
-        <v>-0.2000618891729155</v>
+        <v>-0.1380117395830575</v>
       </c>
       <c r="Z56">
-        <v>-0.04602739726027398</v>
+        <v>8.076923076923077</v>
       </c>
       <c r="AA56">
-        <v>-0.2687671232876713</v>
+        <v>-0.8557692307692307</v>
       </c>
       <c r="AB56">
-        <v>0.04387296409148227</v>
+        <v>0.0716629297623782</v>
       </c>
       <c r="AC56">
-        <v>-0.3126400873791536</v>
+        <v>-0.9274321605316089</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AG56">
-        <v>-0.587</v>
+        <v>-3.42</v>
       </c>
       <c r="AH56">
-        <v>0</v>
+        <v>0.1022831050228311</v>
       </c>
       <c r="AI56">
-        <v>0</v>
+        <v>0.1544827586206897</v>
       </c>
       <c r="AJ56">
-        <v>-0.3134009610250934</v>
+        <v>-0.5335413416536662</v>
       </c>
       <c r="AK56">
-        <v>-0.1261551687083602</v>
+        <v>-1.261992619926199</v>
       </c>
       <c r="AL56">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AM56">
-        <v>0</v>
+        <v>-0.003000000000000003</v>
+      </c>
+      <c r="AN56">
+        <v>-2.545454545454546</v>
+      </c>
+      <c r="AO56">
+        <v>-6.180555555555556</v>
+      </c>
+      <c r="AP56">
+        <v>7.772727272727272</v>
+      </c>
+      <c r="AQ56">
+        <v>148.3333333333332</v>
       </c>
     </row>
     <row r="57">
@@ -7568,7 +7430,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Contango Asset Management Limited (ASX:CGA)</t>
+          <t>InvestSMART Group Limited (ASX:INV)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7577,25 +7439,25 @@
         </is>
       </c>
       <c r="D57">
-        <v>2.467</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="G57">
-        <v>-0.1612590799031477</v>
+        <v>-0.02947530864197531</v>
       </c>
       <c r="H57">
-        <v>-0.1612590799031477</v>
+        <v>-0.02947530864197531</v>
       </c>
       <c r="I57">
-        <v>-0.1627118644067797</v>
+        <v>-0.09336419753086418</v>
       </c>
       <c r="J57">
-        <v>-0.1627118644067797</v>
+        <v>-0.09336419753086418</v>
       </c>
       <c r="K57">
-        <v>-0.6</v>
+        <v>-0.51</v>
       </c>
       <c r="L57">
-        <v>-0.1452784503631961</v>
+        <v>-0.07870370370370371</v>
       </c>
       <c r="M57">
         <v>-0</v>
@@ -7619,73 +7481,67 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>4.14</v>
+        <v>5.57</v>
       </c>
       <c r="V57">
-        <v>0.1273846153846154</v>
+        <v>0.2390557939914163</v>
       </c>
       <c r="W57">
-        <v>-0.08875739644970414</v>
+        <v>-0.1038696537678208</v>
       </c>
       <c r="X57">
-        <v>0.04463522630941354</v>
+        <v>0.07303154055789668</v>
       </c>
       <c r="Y57">
-        <v>-0.1333926227591177</v>
+        <v>-0.1769011943257174</v>
       </c>
       <c r="Z57">
-        <v>2.607323232323232</v>
+        <v>24.3609022556391</v>
       </c>
       <c r="AA57">
-        <v>-0.4242424242424243</v>
+        <v>-2.274436090225564</v>
       </c>
       <c r="AB57">
-        <v>0.04372136981276468</v>
+        <v>0.07245837480620806</v>
       </c>
       <c r="AC57">
-        <v>-0.467963794055189</v>
+        <v>-2.346894465031772</v>
       </c>
       <c r="AD57">
-        <v>1.23</v>
+        <v>0.571</v>
       </c>
       <c r="AE57">
         <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.23</v>
+        <v>0.571</v>
       </c>
       <c r="AG57">
-        <v>-2.91</v>
+        <v>-4.999000000000001</v>
       </c>
       <c r="AH57">
-        <v>0.03646605395790098</v>
+        <v>0.0239202379456244</v>
       </c>
       <c r="AI57">
-        <v>0.148910411622276</v>
+        <v>0.120185224163334</v>
       </c>
       <c r="AJ57">
-        <v>-0.09834403514700911</v>
+        <v>-0.2731544724332003</v>
       </c>
       <c r="AK57">
-        <v>-0.7063106796116503</v>
+        <v>6.103785103785098</v>
       </c>
       <c r="AL57">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM57">
-        <v>-0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN57">
-        <v>-1.846846846846847</v>
-      </c>
-      <c r="AO57">
-        <v>-7.905882352941177</v>
+        <v>-2.989528795811518</v>
       </c>
       <c r="AP57">
-        <v>4.369369369369369</v>
-      </c>
-      <c r="AQ57">
-        <v>9.333333333333334</v>
+        <v>26.17277486910995</v>
       </c>
     </row>
     <row r="58">
@@ -7696,7 +7552,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Benjamin Hornigold Limited (ASX:BHD)</t>
+          <t>Strategic Elements Ltd (ASX:SOR)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7705,22 +7561,22 @@
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>-17.71653543307087</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>-17.71653543307087</v>
       </c>
       <c r="I58">
-        <v>0.5537414965986395</v>
+        <v>-17.85480862411122</v>
       </c>
       <c r="J58">
-        <v>0.5537414965986395</v>
+        <v>-17.85480862411122</v>
       </c>
       <c r="K58">
-        <v>0.945</v>
+        <v>-2.39</v>
       </c>
       <c r="L58">
-        <v>0.6428571428571428</v>
+        <v>-18.81889763779528</v>
       </c>
       <c r="M58">
         <v>-0</v>
@@ -7729,7 +7585,7 @@
         <v>-0</v>
       </c>
       <c r="O58">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P58">
         <v>-0</v>
@@ -7738,67 +7594,70 @@
         <v>-0</v>
       </c>
       <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>3.24</v>
+      </c>
+      <c r="V58">
+        <v>0.07864077669902912</v>
+      </c>
+      <c r="W58">
+        <v>-0.4127806563039724</v>
+      </c>
+      <c r="X58">
+        <v>0.0724558220543962</v>
+      </c>
+      <c r="Y58">
+        <v>-0.4852364783583686</v>
+      </c>
+      <c r="AB58">
+        <v>0.07245423086174417</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0.002803476310625175</v>
+      </c>
+      <c r="AF58">
+        <v>0.002803476310625175</v>
+      </c>
+      <c r="AG58">
+        <v>-3.237196523689375</v>
+      </c>
+      <c r="AH58">
+        <v>6.80409116393505e-05</v>
+      </c>
+      <c r="AI58">
+        <v>0.0009006274671563677</v>
+      </c>
+      <c r="AJ58">
+        <v>-0.08527285203553092</v>
+      </c>
+      <c r="AK58">
+        <v>25.45035375019281</v>
+      </c>
+      <c r="AL58">
+        <v>0.002</v>
+      </c>
+      <c r="AM58">
+        <v>0.001</v>
+      </c>
+      <c r="AN58">
         <v>-0</v>
       </c>
-      <c r="S58">
-        <v>0</v>
-      </c>
-      <c r="U58">
-        <v>1.51</v>
-      </c>
-      <c r="V58">
-        <v>0.3126293995859213</v>
-      </c>
-      <c r="W58">
-        <v>0.1875</v>
-      </c>
-      <c r="X58">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="Y58">
-        <v>0.1436270359085177</v>
-      </c>
-      <c r="Z58">
-        <v>-8.647058823529415</v>
-      </c>
-      <c r="AA58">
-        <v>-4.788235294117649</v>
-      </c>
-      <c r="AB58">
-        <v>0.04387296409148227</v>
-      </c>
-      <c r="AC58">
-        <v>-4.832108258209131</v>
-      </c>
-      <c r="AD58">
-        <v>0</v>
-      </c>
-      <c r="AE58">
-        <v>0</v>
-      </c>
-      <c r="AF58">
-        <v>0</v>
-      </c>
-      <c r="AG58">
-        <v>-1.51</v>
-      </c>
-      <c r="AH58">
-        <v>0</v>
-      </c>
-      <c r="AI58">
-        <v>0</v>
-      </c>
-      <c r="AJ58">
-        <v>-0.4548192771084337</v>
-      </c>
-      <c r="AK58">
-        <v>-0.3081632653061224</v>
-      </c>
-      <c r="AL58">
-        <v>0</v>
-      </c>
-      <c r="AM58">
-        <v>0</v>
+      <c r="AO58">
+        <v>-1135</v>
+      </c>
+      <c r="AP58">
+        <v>1.440674910409157</v>
+      </c>
+      <c r="AQ58">
+        <v>-2270</v>
       </c>
     </row>
     <row r="59">
@@ -7818,25 +7677,25 @@
         </is>
       </c>
       <c r="D59">
-        <v>-0.156</v>
+        <v>-0.19</v>
       </c>
       <c r="G59">
-        <v>-3.125560538116592</v>
+        <v>-7.527027027027028</v>
       </c>
       <c r="H59">
-        <v>-3.125560538116592</v>
+        <v>-7.527027027027028</v>
       </c>
       <c r="I59">
-        <v>-3.165919282511211</v>
+        <v>-7.675675675675675</v>
       </c>
       <c r="J59">
-        <v>-3.165919282511211</v>
+        <v>-7.675675675675675</v>
       </c>
       <c r="K59">
-        <v>-1.13</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="L59">
-        <v>-5.06726457399103</v>
+        <v>-9.351351351351351</v>
       </c>
       <c r="M59">
         <v>-0</v>
@@ -7860,73 +7719,64 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>0.965</v>
+        <v>0.544</v>
       </c>
       <c r="V59">
-        <v>0.08109243697478991</v>
+        <v>0.04857142857142858</v>
       </c>
       <c r="W59">
-        <v>-5.159817351598173</v>
+        <v>1.051671732522796</v>
       </c>
       <c r="X59">
-        <v>0.04649638140570565</v>
+        <v>0.07617721702208283</v>
       </c>
       <c r="Y59">
-        <v>-5.206313733003879</v>
-      </c>
-      <c r="Z59">
-        <v>1.60431654676259</v>
-      </c>
-      <c r="AA59">
-        <v>-5.079136690647482</v>
+        <v>0.9754945155007134</v>
       </c>
       <c r="AB59">
-        <v>0.04339388915070348</v>
-      </c>
-      <c r="AC59">
-        <v>-5.122530579798185</v>
+        <v>0.07139846034289342</v>
       </c>
       <c r="AD59">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AE59">
         <v>0</v>
       </c>
       <c r="AF59">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AG59">
-        <v>0.5850000000000001</v>
+        <v>1.226</v>
       </c>
       <c r="AH59">
-        <v>0.1152416356877323</v>
+        <v>0.1364687740940632</v>
       </c>
       <c r="AI59">
-        <v>1.737668161434978</v>
+        <v>3.6875</v>
       </c>
       <c r="AJ59">
-        <v>0.04685622747296756</v>
+        <v>0.0986640914212136</v>
       </c>
       <c r="AK59">
-        <v>-8.013698630136993</v>
+        <v>-19.15624999999998</v>
       </c>
       <c r="AL59">
-        <v>0.047</v>
+        <v>0.037</v>
       </c>
       <c r="AM59">
-        <v>0.047</v>
+        <v>0.037</v>
       </c>
       <c r="AN59">
-        <v>-2.223816355810617</v>
+        <v>-3.177737881508079</v>
       </c>
       <c r="AO59">
-        <v>-15.02127659574468</v>
+        <v>-15.35135135135135</v>
       </c>
       <c r="AP59">
-        <v>-0.8393113342898136</v>
+        <v>-2.201077199281867</v>
       </c>
       <c r="AQ59">
-        <v>-15.02127659574468</v>
+        <v>-15.35135135135135</v>
       </c>
     </row>
     <row r="60">
@@ -7937,7 +7787,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eildon Capital Fund (ASX:EDC)</t>
+          <t>WAM Strategic Value Limited (ASX:WAR)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7945,47 +7795,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D60">
-        <v>0.357</v>
-      </c>
-      <c r="E60">
-        <v>-0.131</v>
-      </c>
-      <c r="G60">
-        <v>0.6574654956085321</v>
-      </c>
-      <c r="H60">
-        <v>0.6574654956085321</v>
-      </c>
-      <c r="I60">
-        <v>0.6574654956085321</v>
-      </c>
-      <c r="J60">
-        <v>0.6013205461073085</v>
-      </c>
       <c r="K60">
-        <v>0.754</v>
-      </c>
-      <c r="L60">
-        <v>0.09460476787954832</v>
+        <v>-7.99</v>
       </c>
       <c r="M60">
-        <v>2.39</v>
+        <v>0.911</v>
       </c>
       <c r="N60">
-        <v>0.06675977653631286</v>
+        <v>0.007329042638777153</v>
       </c>
       <c r="O60">
-        <v>3.169761273209549</v>
+        <v>-0.114017521902378</v>
       </c>
       <c r="P60">
-        <v>2.39</v>
+        <v>0.911</v>
       </c>
       <c r="Q60">
-        <v>0.06675977653631286</v>
+        <v>0.007329042638777153</v>
       </c>
       <c r="R60">
-        <v>3.169761273209549</v>
+        <v>-0.114017521902378</v>
       </c>
       <c r="S60">
         <v>0</v>
@@ -7994,73 +7823,40 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>8.32</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>0.2324022346368715</v>
-      </c>
-      <c r="W60">
-        <v>0.1496031746031746</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>0.04399279786092473</v>
-      </c>
-      <c r="Y60">
-        <v>0.1056103767422499</v>
-      </c>
-      <c r="Z60">
-        <v>-9.719512195121947</v>
-      </c>
-      <c r="AA60">
-        <v>-5.844542381067373</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB60">
-        <v>0.04382925801305258</v>
-      </c>
-      <c r="AC60">
-        <v>-5.888371639080425</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD60">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="AE60">
         <v>0</v>
       </c>
       <c r="AF60">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>-8.107000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH60">
-        <v>0.005914530863854719</v>
-      </c>
-      <c r="AI60">
-        <v>0.005431872083237701</v>
+        <v>0</v>
       </c>
       <c r="AJ60">
-        <v>-0.2927454591412993</v>
-      </c>
-      <c r="AK60">
-        <v>-0.2624219078755706</v>
+        <v>0</v>
       </c>
       <c r="AL60">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AM60">
-        <v>0.031</v>
-      </c>
-      <c r="AN60">
-        <v>0.04064885496183206</v>
-      </c>
-      <c r="AO60">
-        <v>169.0322580645161</v>
-      </c>
-      <c r="AP60">
-        <v>-1.547137404580153</v>
-      </c>
-      <c r="AQ60">
-        <v>169.0322580645161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -8071,7 +7867,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Netwealth Group Limited (ASX:NWL)</t>
+          <t>Salter Brothers Emerging Companies Limited (ASX:SB2)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8079,125 +7875,65 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D61">
-        <v>0.242</v>
-      </c>
-      <c r="E61">
-        <v>0.427</v>
-      </c>
-      <c r="F61">
-        <v>0.203</v>
-      </c>
-      <c r="G61">
-        <v>0.5414364640883977</v>
-      </c>
-      <c r="H61">
-        <v>0.5414364640883977</v>
-      </c>
-      <c r="I61">
-        <v>0.5349907918968693</v>
-      </c>
-      <c r="J61">
-        <v>0.3751403480313107</v>
-      </c>
       <c r="K61">
-        <v>40.6</v>
-      </c>
-      <c r="L61">
-        <v>0.3738489871086557</v>
+        <v>-5.64</v>
       </c>
       <c r="M61">
-        <v>30.5</v>
+        <v>-0</v>
       </c>
       <c r="N61">
-        <v>0.009725455183189312</v>
+        <v>-0</v>
       </c>
       <c r="O61">
-        <v>0.7512315270935961</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>30.5</v>
+        <v>-0</v>
       </c>
       <c r="Q61">
-        <v>0.009725455183189312</v>
+        <v>-0</v>
       </c>
       <c r="R61">
-        <v>0.7512315270935961</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <v>0</v>
       </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
       <c r="U61">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="V61">
-        <v>0.01945091036637862</v>
-      </c>
-      <c r="W61">
-        <v>0.7733333333333333</v>
+        <v>0</v>
       </c>
       <c r="X61">
-        <v>0.04395195877303824</v>
-      </c>
-      <c r="Y61">
-        <v>0.7293813745602951</v>
-      </c>
-      <c r="Z61">
-        <v>-36.2</v>
-      </c>
-      <c r="AA61">
-        <v>-13.58008059873345</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB61">
-        <v>0.0438440947587463</v>
-      </c>
-      <c r="AC61">
-        <v>-13.62392469349219</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD61">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="AE61">
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="AG61">
-        <v>-48.7</v>
+        <v>0</v>
       </c>
       <c r="AH61">
-        <v>0.003906746283826706</v>
-      </c>
-      <c r="AI61">
-        <v>0.1496350364963504</v>
+        <v>0</v>
       </c>
       <c r="AJ61">
-        <v>-0.01577379024421844</v>
-      </c>
-      <c r="AK61">
-        <v>-2.297169811320754</v>
+        <v>0</v>
       </c>
       <c r="AL61">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="AM61">
-        <v>0.048</v>
-      </c>
-      <c r="AN61">
-        <v>0.2091836734693878</v>
-      </c>
-      <c r="AO61">
-        <v>1210.416666666667</v>
-      </c>
-      <c r="AP61">
-        <v>-0.8282312925170069</v>
-      </c>
-      <c r="AQ61">
-        <v>1210.416666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -8208,7 +7944,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mariner Corporation Limited (ASX:MCX)</t>
+          <t>ARC Funds Limited (ASX:ARC)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8217,25 +7953,25 @@
         </is>
       </c>
       <c r="D62">
-        <v>-0.271</v>
+        <v>-0.5770000000000001</v>
       </c>
       <c r="G62">
-        <v>-5.921875</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>-5.921875</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>-6.6875</v>
+        <v>-127.3333333333333</v>
       </c>
       <c r="J62">
-        <v>-6.6875</v>
+        <v>-127.3333333333333</v>
       </c>
       <c r="K62">
-        <v>-0.447</v>
+        <v>-0.422</v>
       </c>
       <c r="L62">
-        <v>-6.984375</v>
+        <v>-140.6666666666667</v>
       </c>
       <c r="M62">
         <v>-0</v>
@@ -8259,73 +7995,52 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>0.063</v>
+        <v>1.66</v>
       </c>
       <c r="V62">
-        <v>0.05943396226415094</v>
+        <v>0.2459259259259259</v>
       </c>
       <c r="W62">
-        <v>-1.241666666666667</v>
+        <v>-0.1688</v>
       </c>
       <c r="X62">
-        <v>0.04657110808270241</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y62">
-        <v>-1.288237774749369</v>
-      </c>
-      <c r="Z62">
-        <v>2.06451612903226</v>
-      </c>
-      <c r="AA62">
-        <v>-13.80645161290324</v>
+        <v>-0.2412542190407049</v>
       </c>
       <c r="AB62">
-        <v>0.04409818328211694</v>
-      </c>
-      <c r="AC62">
-        <v>-13.85054979618535</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD62">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>0.07899999999999999</v>
+        <v>-1.66</v>
       </c>
       <c r="AH62">
-        <v>0.1181364392678868</v>
+        <v>0</v>
       </c>
       <c r="AI62">
-        <v>1.56043956043956</v>
+        <v>0</v>
       </c>
       <c r="AJ62">
-        <v>0.06935908691834941</v>
+        <v>-0.3261296660117878</v>
       </c>
       <c r="AK62">
-        <v>2.821428571428572</v>
+        <v>-4.882352941176469</v>
       </c>
       <c r="AL62">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM62">
-        <v>0.002</v>
-      </c>
-      <c r="AN62">
-        <v>-0.3746701846965699</v>
-      </c>
-      <c r="AO62">
-        <v>-214</v>
-      </c>
-      <c r="AP62">
-        <v>-0.20844327176781</v>
-      </c>
-      <c r="AQ62">
-        <v>-214</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_investments_asset_management.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0735</v>
+        <v>0.0521</v>
       </c>
       <c r="E2">
-        <v>0.07475</v>
+        <v>0.0337</v>
       </c>
       <c r="F2">
-        <v>-0.0462</v>
+        <v>0.1082</v>
       </c>
       <c r="G2">
-        <v>0.2542252969126191</v>
+        <v>0.1992319212861452</v>
       </c>
       <c r="H2">
-        <v>0.253407833992644</v>
+        <v>0.1978205234735335</v>
       </c>
       <c r="I2">
-        <v>0.2654127583090516</v>
+        <v>0.338035895702147</v>
       </c>
       <c r="J2">
-        <v>0.2390411495379623</v>
+        <v>0.2907471642137797</v>
       </c>
       <c r="K2">
-        <v>1196.503</v>
+        <v>1260.058</v>
       </c>
       <c r="L2">
-        <v>0.2423431209462316</v>
+        <v>0.2504849443611079</v>
       </c>
       <c r="M2">
-        <v>1342.5248</v>
+        <v>1125.523</v>
       </c>
       <c r="N2">
-        <v>0.0485515732950666</v>
+        <v>0.03755301732077926</v>
       </c>
       <c r="O2">
-        <v>1.122040479631058</v>
+        <v>0.8932311052348383</v>
       </c>
       <c r="P2">
-        <v>1270.2028</v>
+        <v>1046.843</v>
       </c>
       <c r="Q2">
-        <v>0.04593609320572612</v>
+        <v>0.03492786314552126</v>
       </c>
       <c r="R2">
-        <v>1.061596001012952</v>
+        <v>0.8307895350848929</v>
       </c>
       <c r="S2">
-        <v>72.32199999999999</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="T2">
-        <v>0.05387014079739905</v>
+        <v>0.06990527959002171</v>
       </c>
       <c r="U2">
-        <v>2049.956</v>
+        <v>1747.148</v>
       </c>
       <c r="V2">
-        <v>0.07413538206941246</v>
+        <v>0.05829350364760635</v>
       </c>
       <c r="W2">
-        <v>0.03374513994090168</v>
+        <v>0.04734154263396386</v>
       </c>
       <c r="X2">
-        <v>0.07262679410017914</v>
+        <v>0.0623836047787487</v>
       </c>
       <c r="Y2">
-        <v>-0.03888165415927745</v>
+        <v>-0.01504206214478484</v>
       </c>
       <c r="Z2">
-        <v>0.2572138202624148</v>
+        <v>0.251453380485103</v>
       </c>
       <c r="AA2">
-        <v>0.01805245524006944</v>
+        <v>0.05769882572229465</v>
       </c>
       <c r="AB2">
-        <v>0.07238689154631267</v>
+        <v>0.06226315828184265</v>
       </c>
       <c r="AC2">
-        <v>-0.05440176380063541</v>
+        <v>-0.004609562813506982</v>
       </c>
       <c r="AD2">
-        <v>2059.593</v>
+        <v>2855.429</v>
       </c>
       <c r="AE2">
-        <v>0.1548176603804269</v>
+        <v>0.1460780181876972</v>
       </c>
       <c r="AF2">
-        <v>2059.74781766038</v>
+        <v>2855.575078018187</v>
       </c>
       <c r="AG2">
-        <v>9.791817660380275</v>
+        <v>1108.427078018188</v>
       </c>
       <c r="AH2">
-        <v>0.06932547713214937</v>
+        <v>0.08698821692434336</v>
       </c>
       <c r="AI2">
-        <v>0.092570323612422</v>
+        <v>0.1135504705812277</v>
       </c>
       <c r="AJ2">
-        <v>0.00035398963450926</v>
+        <v>0.03566367680938778</v>
       </c>
       <c r="AK2">
-        <v>0.0004847273273267973</v>
+        <v>0.04736681408063873</v>
       </c>
       <c r="AL2">
-        <v>45.288</v>
+        <v>109.731</v>
       </c>
       <c r="AM2">
-        <v>-55.79600000000001</v>
+        <v>37.50000000000001</v>
       </c>
       <c r="AN2">
-        <v>1.658263406810529</v>
+        <v>2.813554862974353</v>
       </c>
       <c r="AO2">
-        <v>28.93196873343932</v>
+        <v>15.49594007162971</v>
       </c>
       <c r="AP2">
-        <v>0.007883796901800357</v>
+        <v>1.092172278004644</v>
       </c>
       <c r="AQ2">
-        <v>-23.48324252634597</v>
+        <v>45.34359999999998</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Australian Ethical Investment Ltd. (ASX:AEF)</t>
+          <t>WAM Strategic Value Limited (ASX:WAR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,113 +724,89 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.201</v>
-      </c>
-      <c r="E3">
-        <v>0.266</v>
-      </c>
       <c r="G3">
-        <v>0.2377049180327869</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.2377049180327869</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.2315573770491804</v>
+        <v>0.8918918918918918</v>
       </c>
       <c r="J3">
-        <v>0.1598209504396345</v>
+        <v>0.7108108108108107</v>
       </c>
       <c r="K3">
-        <v>6.55</v>
+        <v>10.5</v>
       </c>
       <c r="L3">
-        <v>0.1342213114754098</v>
+        <v>0.7094594594594594</v>
       </c>
       <c r="M3">
-        <v>7.27</v>
+        <v>4.2</v>
       </c>
       <c r="N3">
-        <v>0.02437961099932931</v>
+        <v>0.03273577552611068</v>
       </c>
       <c r="O3">
-        <v>1.109923664122137</v>
+        <v>0.4</v>
       </c>
       <c r="P3">
-        <v>5.42</v>
+        <v>4.2</v>
       </c>
       <c r="Q3">
-        <v>0.0181757209926224</v>
+        <v>0.03273577552611068</v>
       </c>
       <c r="R3">
-        <v>0.8274809160305343</v>
+        <v>0.4</v>
       </c>
       <c r="S3">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2544704264099037</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>18.9</v>
+        <v>38.4</v>
       </c>
       <c r="V3">
-        <v>0.06338028169014084</v>
-      </c>
-      <c r="W3">
-        <v>0.361878453038674</v>
+        <v>0.299298519095869</v>
       </c>
       <c r="X3">
-        <v>0.07249964433635839</v>
-      </c>
-      <c r="Y3">
-        <v>0.2893788087023156</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AB3">
-        <v>0.07243421116593447</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AD3">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-18.325</v>
+        <v>-38.4</v>
       </c>
       <c r="AH3">
-        <v>0.001924525144339386</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.03271692745376956</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.06547565877623938</v>
+        <v>-0.4271412680756396</v>
       </c>
       <c r="AK3">
-        <v>13.83018867924529</v>
+        <v>-0.3592142188961646</v>
       </c>
       <c r="AL3">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.028</v>
-      </c>
-      <c r="AN3">
-        <v>0.04956896551724137</v>
-      </c>
-      <c r="AO3">
-        <v>403.5714285714286</v>
-      </c>
-      <c r="AP3">
-        <v>-1.579741379310345</v>
-      </c>
-      <c r="AQ3">
-        <v>403.5714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Centrepoint Alliance Limited (ASX:CAF)</t>
+          <t>Eildon Capital Fund (ASX:EDC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +826,43 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.121</v>
-      </c>
-      <c r="E4">
-        <v>-0.00159</v>
+        <v>0.119</v>
       </c>
       <c r="G4">
-        <v>0.01532104259376987</v>
+        <v>0.401294498381877</v>
       </c>
       <c r="H4">
-        <v>0.01532104259376987</v>
+        <v>0.401294498381877</v>
       </c>
       <c r="I4">
-        <v>0.01176096630642085</v>
+        <v>0.3996763754045308</v>
       </c>
       <c r="J4">
-        <v>0.01176096630642085</v>
+        <v>0.397663616679472</v>
       </c>
       <c r="K4">
-        <v>4.47</v>
+        <v>-0.582</v>
       </c>
       <c r="L4">
-        <v>0.02841703750794659</v>
+        <v>-0.09417475728155339</v>
       </c>
       <c r="M4">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>0.09853479853479853</v>
+        <v>0.06872852233676975</v>
       </c>
       <c r="O4">
-        <v>0.6017897091722595</v>
+        <v>-3.436426116838488</v>
       </c>
       <c r="P4">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>0.09853479853479853</v>
+        <v>0.06872852233676975</v>
       </c>
       <c r="R4">
-        <v>0.6017897091722595</v>
+        <v>-3.436426116838488</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,64 +871,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>10.2</v>
+        <v>4.42</v>
       </c>
       <c r="V4">
-        <v>0.3736263736263736</v>
+        <v>0.1518900343642612</v>
       </c>
       <c r="W4">
-        <v>0.5385542168674698</v>
+        <v>-0.07558441558441557</v>
       </c>
       <c r="X4">
-        <v>0.07395571496713629</v>
+        <v>0.0623530625525037</v>
       </c>
       <c r="Y4">
-        <v>0.4645985019003336</v>
+        <v>-0.1379374781369193</v>
       </c>
       <c r="AB4">
-        <v>0.07183130229348557</v>
+        <v>0.06226961164460255</v>
       </c>
       <c r="AD4">
-        <v>1.74</v>
+        <v>0.079</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.74</v>
+        <v>0.079</v>
       </c>
       <c r="AG4">
-        <v>-8.459999999999999</v>
+        <v>-4.341</v>
       </c>
       <c r="AH4">
-        <v>0.05991735537190083</v>
+        <v>0.002707426573905891</v>
       </c>
       <c r="AI4">
-        <v>0.08192090395480227</v>
+        <v>0.00217158250639105</v>
       </c>
       <c r="AJ4">
-        <v>-0.449044585987261</v>
+        <v>-0.1753301829637708</v>
       </c>
       <c r="AK4">
-        <v>-0.7663043478260868</v>
+        <v>-0.1358302825495166</v>
       </c>
       <c r="AL4">
-        <v>0.083</v>
+        <v>0.611</v>
       </c>
       <c r="AM4">
-        <v>0.083</v>
+        <v>0.611</v>
       </c>
       <c r="AN4">
-        <v>0.7219917012448133</v>
+        <v>0.03185483870967742</v>
       </c>
       <c r="AO4">
-        <v>22.28915662650602</v>
+        <v>4.042553191489362</v>
       </c>
       <c r="AP4">
-        <v>-3.510373443983402</v>
+        <v>-1.750403225806452</v>
       </c>
       <c r="AQ4">
-        <v>22.28915662650602</v>
+        <v>4.042553191489362</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eildon Capital Fund (ASX:EDC)</t>
+          <t>Australian Ethical Investment Limited (ASX:AEF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,112 +948,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="E5">
-        <v>-0.09329999999999999</v>
+        <v>0.0529</v>
       </c>
       <c r="G5">
-        <v>0.6078665077473182</v>
+        <v>0.2296296296296296</v>
       </c>
       <c r="H5">
-        <v>0.6078665077473182</v>
+        <v>0.2296296296296296</v>
       </c>
       <c r="I5">
-        <v>0.6066746126340882</v>
+        <v>0.2240740740740741</v>
       </c>
       <c r="J5">
-        <v>0.5480593276502027</v>
+        <v>0.1390914351851852</v>
       </c>
       <c r="K5">
-        <v>1.54</v>
+        <v>4.38</v>
       </c>
       <c r="L5">
-        <v>0.1835518474374255</v>
+        <v>0.08111111111111111</v>
       </c>
       <c r="M5">
-        <v>2.68</v>
+        <v>3.982</v>
       </c>
       <c r="N5">
-        <v>0.1</v>
+        <v>0.009574416927145949</v>
       </c>
       <c r="O5">
-        <v>1.74025974025974</v>
+        <v>0.9091324200913242</v>
       </c>
       <c r="P5">
-        <v>2.68</v>
+        <v>3.75</v>
       </c>
       <c r="Q5">
-        <v>0.1</v>
+        <v>0.009016590526568887</v>
       </c>
       <c r="R5">
-        <v>1.74025974025974</v>
+        <v>0.8561643835616438</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.2320000000000002</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.05826217980914118</v>
       </c>
       <c r="U5">
-        <v>5.64</v>
+        <v>18.1</v>
       </c>
       <c r="V5">
-        <v>0.2104477611940298</v>
+        <v>0.0435200769415725</v>
       </c>
       <c r="W5">
-        <v>0.2308845577211394</v>
+        <v>0.2576470588235294</v>
       </c>
       <c r="X5">
-        <v>0.07257640394789369</v>
+        <v>0.06236655187266948</v>
       </c>
       <c r="Y5">
-        <v>0.1583081537732458</v>
+        <v>0.1952805069508599</v>
+      </c>
+      <c r="Z5">
+        <v>20.97087378640777</v>
+      </c>
+      <c r="AA5">
+        <v>2.916868932038836</v>
       </c>
       <c r="AB5">
-        <v>0.07237276498027213</v>
+        <v>0.06227227332784636</v>
+      </c>
+      <c r="AC5">
+        <v>2.85459665871099</v>
       </c>
       <c r="AD5">
-        <v>0.139</v>
+        <v>1.47</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.139</v>
+        <v>1.47</v>
       </c>
       <c r="AG5">
-        <v>-5.500999999999999</v>
+        <v>-16.63</v>
       </c>
       <c r="AH5">
-        <v>0.005159805486469432</v>
+        <v>0.003522054771545631</v>
       </c>
       <c r="AI5">
-        <v>0.0036734586009144</v>
+        <v>0.07628437986507525</v>
       </c>
       <c r="AJ5">
-        <v>-0.2582750363866848</v>
+        <v>-0.04165101309890551</v>
       </c>
       <c r="AK5">
-        <v>-0.1708438150253113</v>
+        <v>-14.21367521367524</v>
       </c>
       <c r="AL5">
-        <v>0.303</v>
+        <v>0.059</v>
       </c>
       <c r="AM5">
-        <v>0.303</v>
+        <v>0.059</v>
       </c>
       <c r="AN5">
-        <v>0.02725490196078432</v>
+        <v>0.1185483870967742</v>
       </c>
       <c r="AO5">
-        <v>16.7986798679868</v>
+        <v>205.0847457627119</v>
       </c>
       <c r="AP5">
-        <v>-1.078627450980392</v>
+        <v>-1.341129032258065</v>
       </c>
       <c r="AQ5">
-        <v>16.7986798679868</v>
+        <v>205.0847457627119</v>
       </c>
     </row>
     <row r="6">
@@ -1100,49 +1082,49 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.231</v>
+        <v>0.209</v>
       </c>
       <c r="E6">
-        <v>0.326</v>
+        <v>0.264</v>
       </c>
       <c r="F6">
-        <v>0.236</v>
+        <v>0.181</v>
       </c>
       <c r="G6">
-        <v>0.4782244556113903</v>
+        <v>0.4807557732680196</v>
       </c>
       <c r="H6">
-        <v>0.4782244556113903</v>
+        <v>0.4807557732680196</v>
       </c>
       <c r="I6">
-        <v>0.4731993299832495</v>
+        <v>0.4772568229531141</v>
       </c>
       <c r="J6">
-        <v>0.3242134944250171</v>
+        <v>0.3302380802787028</v>
       </c>
       <c r="K6">
-        <v>38.3</v>
+        <v>44.7</v>
       </c>
       <c r="L6">
-        <v>0.3207705192629816</v>
+        <v>0.3128061581525542</v>
       </c>
       <c r="M6">
-        <v>32.8</v>
+        <v>34.1</v>
       </c>
       <c r="N6">
-        <v>0.01635339283043327</v>
+        <v>0.01331147285006051</v>
       </c>
       <c r="O6">
-        <v>0.856396866840731</v>
+        <v>0.7628635346756152</v>
       </c>
       <c r="P6">
-        <v>32.8</v>
+        <v>34.1</v>
       </c>
       <c r="Q6">
-        <v>0.01635339283043327</v>
+        <v>0.01331147285006051</v>
       </c>
       <c r="R6">
-        <v>0.856396866840731</v>
+        <v>0.7628635346756152</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1133,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>60.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V6">
-        <v>0.03036346412723737</v>
+        <v>0.02845766483194754</v>
       </c>
       <c r="W6">
-        <v>0.5479256080114449</v>
+        <v>0.6225626740947076</v>
       </c>
       <c r="X6">
-        <v>0.07257637226133423</v>
+        <v>0.06236645977078409</v>
       </c>
       <c r="Y6">
-        <v>0.4753492357501106</v>
+        <v>0.5601962143239234</v>
       </c>
       <c r="Z6">
-        <v>5.632075471698113</v>
+        <v>6.708920187793426</v>
       </c>
       <c r="AA6">
-        <v>1.825994869544672</v>
+        <v>2.215540923559935</v>
       </c>
       <c r="AB6">
-        <v>0.07240059017139927</v>
+        <v>0.06225802379813501</v>
       </c>
       <c r="AC6">
-        <v>1.753594279373272</v>
+        <v>2.1532828997618</v>
       </c>
       <c r="AD6">
-        <v>10.4</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>10.4</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AG6">
-        <v>-50.5</v>
+        <v>-63.86000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.005158474282029661</v>
+        <v>0.003516497195360091</v>
       </c>
       <c r="AI6">
-        <v>0.1265206812652068</v>
+        <v>0.09940620189135693</v>
       </c>
       <c r="AJ6">
-        <v>-0.0258285597381342</v>
+        <v>-0.02556608910098326</v>
       </c>
       <c r="AK6">
-        <v>-2.370892018779343</v>
+        <v>-3.539911308203992</v>
       </c>
       <c r="AL6">
-        <v>0.342</v>
+        <v>0.3</v>
       </c>
       <c r="AM6">
-        <v>0.342</v>
+        <v>0.3</v>
       </c>
       <c r="AN6">
-        <v>0.1821366024518389</v>
+        <v>0.1315866084425036</v>
       </c>
       <c r="AO6">
-        <v>165.2046783625731</v>
+        <v>227.3333333333333</v>
       </c>
       <c r="AP6">
-        <v>-0.8844133099824868</v>
+        <v>-0.9295487627365357</v>
       </c>
       <c r="AQ6">
-        <v>165.2046783625731</v>
+        <v>227.3333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microequities Asset Management Group Limited (ASX:MAM)</t>
+          <t>Centrepoint Alliance Limited (ASX:CAF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,121 +1219,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0823</v>
-      </c>
-      <c r="E7">
-        <v>0.0872</v>
+        <v>0.174</v>
       </c>
       <c r="G7">
-        <v>0.7924528301886792</v>
+        <v>0.02894014277869303</v>
       </c>
       <c r="H7">
-        <v>0.7924528301886792</v>
+        <v>0.02894014277869303</v>
       </c>
       <c r="I7">
-        <v>0.7861635220125786</v>
+        <v>0.02465678198791873</v>
       </c>
       <c r="J7">
-        <v>0.6226415094339622</v>
+        <v>0.02363128400978484</v>
       </c>
       <c r="K7">
-        <v>9.720000000000001</v>
+        <v>4.22</v>
       </c>
       <c r="L7">
-        <v>0.6113207547169811</v>
+        <v>0.02317408017572762</v>
       </c>
       <c r="M7">
-        <v>10.106</v>
+        <v>1.96</v>
       </c>
       <c r="N7">
-        <v>0.167317880794702</v>
+        <v>0.04611764705882353</v>
       </c>
       <c r="O7">
-        <v>1.039711934156379</v>
+        <v>0.4644549763033176</v>
       </c>
       <c r="P7">
-        <v>9.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q7">
-        <v>0.1653973509933775</v>
+        <v>0.04611764705882353</v>
       </c>
       <c r="R7">
-        <v>1.027777777777778</v>
+        <v>0.4644549763033176</v>
       </c>
       <c r="S7">
-        <v>0.1159999999999997</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.01147832970512563</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>4.64</v>
+        <v>10.4</v>
       </c>
       <c r="V7">
-        <v>0.07682119205298013</v>
+        <v>0.2447058823529412</v>
       </c>
       <c r="W7">
-        <v>0.648</v>
+        <v>0.2175257731958763</v>
       </c>
       <c r="X7">
-        <v>0.07264650498426359</v>
+        <v>0.06251515172720593</v>
       </c>
       <c r="Y7">
-        <v>0.5753534950157364</v>
+        <v>0.1550106214686704</v>
       </c>
       <c r="Z7">
-        <v>2.561623972933784</v>
+        <v>33.97388059701494</v>
       </c>
       <c r="AA7">
-        <v>1.594973417109715</v>
+        <v>0.8028464213025784</v>
       </c>
       <c r="AB7">
-        <v>0.0723700491197596</v>
+        <v>0.06218114856639522</v>
       </c>
       <c r="AC7">
-        <v>1.522603367989955</v>
+        <v>0.7406652727361832</v>
       </c>
       <c r="AD7">
-        <v>0.493</v>
+        <v>0.534</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.493</v>
+        <v>0.534</v>
       </c>
       <c r="AG7">
-        <v>-4.146999999999999</v>
+        <v>-9.866</v>
       </c>
       <c r="AH7">
-        <v>0.008096168689340318</v>
+        <v>0.0124087930473579</v>
       </c>
       <c r="AI7">
-        <v>0.03653746387015489</v>
+        <v>0.02514834699067534</v>
       </c>
       <c r="AJ7">
-        <v>-0.07372051268376796</v>
+        <v>-0.3023227308941595</v>
       </c>
       <c r="AK7">
-        <v>-0.4684287812041115</v>
+        <v>-0.9106516522060181</v>
       </c>
       <c r="AL7">
-        <v>0.006</v>
+        <v>0.091</v>
       </c>
       <c r="AM7">
-        <v>0.006</v>
+        <v>0.091</v>
       </c>
       <c r="AN7">
-        <v>0.03912698412698413</v>
+        <v>0.1013282732447818</v>
       </c>
       <c r="AO7">
-        <v>2083.333333333333</v>
+        <v>49.34065934065934</v>
       </c>
       <c r="AP7">
-        <v>-0.3291269841269841</v>
+        <v>-1.872106261859583</v>
       </c>
       <c r="AQ7">
-        <v>2083.333333333333</v>
+        <v>49.34065934065934</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Share Registry Limited (ASX:ASW)</t>
+          <t>Prime Financial Group Limited (ASX:PFG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,121 +1350,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.009220000000000001</v>
-      </c>
-      <c r="E8">
-        <v>-0.0308</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G8">
-        <v>0.4285714285714285</v>
+        <v>0.2271111111111111</v>
       </c>
       <c r="H8">
-        <v>0.4285714285714285</v>
+        <v>0.2271111111111111</v>
       </c>
       <c r="I8">
-        <v>0.4110275689223057</v>
+        <v>0.2026666666666667</v>
       </c>
       <c r="J8">
-        <v>0.3056229530882421</v>
+        <v>0.1510870870870871</v>
       </c>
       <c r="K8">
-        <v>1.21</v>
+        <v>2.93</v>
       </c>
       <c r="L8">
-        <v>0.3032581453634085</v>
+        <v>0.1302222222222222</v>
       </c>
       <c r="M8">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="N8">
-        <v>0.0625</v>
+        <v>0.05783132530120481</v>
       </c>
       <c r="O8">
-        <v>1.28099173553719</v>
+        <v>0.6552901023890785</v>
       </c>
       <c r="P8">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q8">
-        <v>0.0625</v>
+        <v>0.05180722891566265</v>
       </c>
       <c r="R8">
-        <v>1.28099173553719</v>
+        <v>0.5870307167235495</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.1041666666666666</v>
       </c>
       <c r="U8">
-        <v>2.88</v>
+        <v>0.694</v>
       </c>
       <c r="V8">
-        <v>0.1161290322580645</v>
+        <v>0.02090361445783132</v>
       </c>
       <c r="W8">
-        <v>0.1881804043545879</v>
+        <v>0.09242902208201893</v>
       </c>
       <c r="X8">
-        <v>0.07271164667586702</v>
+        <v>0.06603574266991187</v>
       </c>
       <c r="Y8">
-        <v>0.1154687576787209</v>
+        <v>0.02639327941210706</v>
       </c>
       <c r="Z8">
-        <v>2.254237288135594</v>
+        <v>3.610977371208475</v>
       </c>
       <c r="AA8">
-        <v>0.6889466569616305</v>
+        <v>0.5455720525532757</v>
       </c>
       <c r="AB8">
-        <v>0.07234184266927933</v>
+        <v>0.05966338429865113</v>
       </c>
       <c r="AC8">
-        <v>0.6166048142923511</v>
+        <v>0.4859086682546245</v>
       </c>
       <c r="AD8">
-        <v>0.271</v>
+        <v>7.52</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.271</v>
+        <v>7.52</v>
       </c>
       <c r="AG8">
-        <v>-2.609</v>
+        <v>6.826</v>
       </c>
       <c r="AH8">
-        <v>0.01080930158350285</v>
+        <v>0.1846758349705304</v>
       </c>
       <c r="AI8">
-        <v>0.04647573315040303</v>
+        <v>0.1865079365079365</v>
       </c>
       <c r="AJ8">
-        <v>-0.1175701861114866</v>
+        <v>0.1705391495527907</v>
       </c>
       <c r="AK8">
-        <v>-0.8841070823449679</v>
+        <v>0.1722606369555343</v>
       </c>
       <c r="AL8">
-        <v>0.013</v>
+        <v>0.525</v>
       </c>
       <c r="AM8">
-        <v>0.013</v>
+        <v>0.525</v>
       </c>
       <c r="AN8">
-        <v>0.1584795321637427</v>
+        <v>1.471624266144814</v>
       </c>
       <c r="AO8">
-        <v>126.1538461538461</v>
+        <v>8.685714285714285</v>
       </c>
       <c r="AP8">
-        <v>-1.525730994152047</v>
+        <v>1.335812133072407</v>
       </c>
       <c r="AQ8">
-        <v>126.1538461538461</v>
+        <v>8.685714285714285</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1472,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pengana Capital Group Limited (ASX:PCG)</t>
+          <t>Fiducian Group Ltd (ASX:FID)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,118 +1481,115 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.119</v>
+        <v>0.0983</v>
+      </c>
+      <c r="E9">
+        <v>0.0602</v>
       </c>
       <c r="G9">
-        <v>0.3929889298892989</v>
+        <v>0.2848360655737705</v>
       </c>
       <c r="H9">
-        <v>0.3929889298892989</v>
+        <v>0.2848360655737705</v>
       </c>
       <c r="I9">
-        <v>0.3597785977859778</v>
+        <v>0.2418032786885246</v>
       </c>
       <c r="J9">
-        <v>0.2404234756633281</v>
+        <v>0.1688524590163935</v>
       </c>
       <c r="K9">
-        <v>12.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L9">
-        <v>0.2380073800738007</v>
+        <v>0.1680327868852459</v>
       </c>
       <c r="M9">
-        <v>12.427</v>
+        <v>5.7</v>
       </c>
       <c r="N9">
-        <v>0.1331939978563773</v>
+        <v>0.04292168674698795</v>
       </c>
       <c r="O9">
-        <v>0.9633333333333333</v>
+        <v>0.6951219512195123</v>
       </c>
       <c r="P9">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="Q9">
-        <v>0.1232583065380493</v>
+        <v>0.04292168674698795</v>
       </c>
       <c r="R9">
-        <v>0.8914728682170543</v>
+        <v>0.6951219512195123</v>
       </c>
       <c r="S9">
-        <v>0.9269999999999996</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>0.07459563852900938</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>17.7</v>
+        <v>13.1</v>
       </c>
       <c r="V9">
-        <v>0.1897106109324759</v>
+        <v>0.098644578313253</v>
       </c>
       <c r="W9">
-        <v>0.2208904109589041</v>
+        <v>0.2523076923076923</v>
       </c>
       <c r="X9">
-        <v>0.07272186567016041</v>
+        <v>0.06265782798587446</v>
       </c>
       <c r="Y9">
-        <v>0.1481685452887437</v>
+        <v>0.1896498643218178</v>
       </c>
       <c r="Z9">
-        <v>2.640038967364831</v>
+        <v>3.098412698412699</v>
       </c>
       <c r="AA9">
-        <v>0.6347273444204762</v>
+        <v>0.5231746031746034</v>
       </c>
       <c r="AB9">
-        <v>0.072337431825201</v>
+        <v>0.06201057689517865</v>
       </c>
       <c r="AC9">
-        <v>0.5623899125952752</v>
+        <v>0.4611640262794248</v>
       </c>
       <c r="AD9">
-        <v>1.06</v>
+        <v>2.82</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.06</v>
+        <v>2.82</v>
       </c>
       <c r="AG9">
-        <v>-16.64</v>
+        <v>-10.28</v>
       </c>
       <c r="AH9">
-        <v>0.01123357354811361</v>
+        <v>0.0207933933048223</v>
       </c>
       <c r="AI9">
-        <v>0.01730329742082925</v>
+        <v>0.07679738562091504</v>
       </c>
       <c r="AJ9">
-        <v>-0.2170623532481085</v>
+        <v>-0.08390466862553052</v>
       </c>
       <c r="AK9">
-        <v>-0.3820018365472911</v>
+        <v>-0.4352243861134632</v>
       </c>
       <c r="AL9">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>0.04976525821596244</v>
-      </c>
-      <c r="AO9">
-        <v>253.2467532467533</v>
+        <v>0.2028776978417266</v>
       </c>
       <c r="AP9">
-        <v>-0.7812206572769953</v>
-      </c>
-      <c r="AQ9">
-        <v>253.2467532467533</v>
+        <v>-0.7395683453237409</v>
       </c>
     </row>
     <row r="10">
@@ -1627,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fiducian Group Ltd (ASX:FID)</t>
+          <t>Microequities Asset Management Group Limited (ASX:MAM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1636,115 +1609,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.113</v>
+        <v>0.0196</v>
       </c>
       <c r="E10">
-        <v>0.121</v>
+        <v>0.0166</v>
       </c>
       <c r="G10">
-        <v>0.3110647181628393</v>
+        <v>0.6658566221142163</v>
       </c>
       <c r="H10">
-        <v>0.3110647181628393</v>
+        <v>0.6658566221142163</v>
       </c>
       <c r="I10">
-        <v>0.2734864300626305</v>
+        <v>0.6476306196840826</v>
       </c>
       <c r="J10">
-        <v>0.1908141962421712</v>
+        <v>0.4954617710741008</v>
       </c>
       <c r="K10">
-        <v>9.18</v>
+        <v>3.77</v>
       </c>
       <c r="L10">
-        <v>0.1916492693110647</v>
+        <v>0.4580801944106926</v>
       </c>
       <c r="M10">
-        <v>6.38</v>
+        <v>3.463</v>
       </c>
       <c r="N10">
-        <v>0.0447719298245614</v>
+        <v>0.0711088295687885</v>
       </c>
       <c r="O10">
-        <v>0.6949891067538126</v>
+        <v>0.9185676392572945</v>
       </c>
       <c r="P10">
-        <v>6.38</v>
+        <v>3.38</v>
       </c>
       <c r="Q10">
-        <v>0.0447719298245614</v>
+        <v>0.06940451745379876</v>
       </c>
       <c r="R10">
-        <v>0.6949891067538126</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.08300000000000018</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.02396765809991342</v>
       </c>
       <c r="U10">
-        <v>12</v>
+        <v>4.13</v>
       </c>
       <c r="V10">
-        <v>0.08421052631578947</v>
+        <v>0.08480492813141684</v>
       </c>
       <c r="W10">
-        <v>0.2859813084112149</v>
+        <v>0.29</v>
       </c>
       <c r="X10">
-        <v>0.0731171481133172</v>
+        <v>0.06243307471154697</v>
       </c>
       <c r="Y10">
-        <v>0.2128641602978977</v>
+        <v>0.227566925288453</v>
       </c>
       <c r="Z10">
-        <v>3.170086035737921</v>
+        <v>0.9296283745622952</v>
       </c>
       <c r="AA10">
-        <v>0.6048974189278623</v>
+        <v>0.4605953209013722</v>
       </c>
       <c r="AB10">
-        <v>0.07202214665311378</v>
+        <v>0.06223127809721692</v>
       </c>
       <c r="AC10">
-        <v>0.5328752722747485</v>
+        <v>0.3983640428041553</v>
       </c>
       <c r="AD10">
-        <v>4.01</v>
+        <v>0.369</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>4.01</v>
+        <v>0.369</v>
       </c>
       <c r="AG10">
-        <v>-7.99</v>
+        <v>-3.761</v>
       </c>
       <c r="AH10">
-        <v>0.02737014538256774</v>
+        <v>0.007520022825001528</v>
       </c>
       <c r="AI10">
-        <v>0.1098329224869899</v>
+        <v>0.02760116687859974</v>
       </c>
       <c r="AJ10">
-        <v>-0.05940078804549848</v>
+        <v>-0.08369122588397605</v>
       </c>
       <c r="AK10">
-        <v>-0.3259893920848634</v>
+        <v>-0.4070786881697153</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AN10">
-        <v>0.2691275167785235</v>
+        <v>0.06733576642335766</v>
+      </c>
+      <c r="AO10">
+        <v>761.4285714285714</v>
       </c>
       <c r="AP10">
-        <v>-0.536241610738255</v>
+        <v>-0.6863138686131387</v>
+      </c>
+      <c r="AQ10">
+        <v>761.4285714285714</v>
       </c>
     </row>
     <row r="11">
@@ -1755,7 +1734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prime Financial Group Limited (ASX:PFG)</t>
+          <t>Magellan Financial Group Limited (ASX:MFG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1764,121 +1743,124 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.06619999999999999</v>
+        <v>-0.009039999999999999</v>
       </c>
       <c r="E11">
-        <v>0.0547</v>
+        <v>-0.0292</v>
+      </c>
+      <c r="F11">
+        <v>0.0285</v>
       </c>
       <c r="G11">
-        <v>0.2911602209944751</v>
+        <v>0.694802929891873</v>
       </c>
       <c r="H11">
-        <v>0.2823204419889503</v>
+        <v>0.694802929891873</v>
       </c>
       <c r="I11">
-        <v>0.2569060773480663</v>
+        <v>0.6857493125013627</v>
       </c>
       <c r="J11">
-        <v>0.1951338716532087</v>
+        <v>0.4902240823055009</v>
       </c>
       <c r="K11">
-        <v>2.63</v>
+        <v>121.6</v>
       </c>
       <c r="L11">
-        <v>0.1453038674033149</v>
+        <v>0.4241367282874084</v>
       </c>
       <c r="M11">
-        <v>1.694</v>
+        <v>162.6</v>
       </c>
       <c r="N11">
-        <v>0.05646666666666667</v>
+        <v>0.1419839329374782</v>
       </c>
       <c r="O11">
-        <v>0.644106463878327</v>
+        <v>1.337171052631579</v>
       </c>
       <c r="P11">
-        <v>1.23</v>
+        <v>135.7</v>
       </c>
       <c r="Q11">
-        <v>0.041</v>
+        <v>0.1184945860984981</v>
       </c>
       <c r="R11">
-        <v>0.467680608365019</v>
+        <v>1.115953947368421</v>
       </c>
       <c r="S11">
-        <v>0.464</v>
+        <v>26.90000000000001</v>
       </c>
       <c r="T11">
-        <v>0.2739079102715467</v>
+        <v>0.1654366543665437</v>
       </c>
       <c r="U11">
-        <v>0.089</v>
+        <v>248.5</v>
       </c>
       <c r="V11">
-        <v>0.002966666666666666</v>
+        <v>0.2169926650366748</v>
       </c>
       <c r="W11">
-        <v>0.08193146417445482</v>
+        <v>0.1718970879276223</v>
       </c>
       <c r="X11">
-        <v>0.07631772338657777</v>
+        <v>0.06240622080023593</v>
       </c>
       <c r="Y11">
-        <v>0.005613740787877047</v>
+        <v>0.1094908671273864</v>
       </c>
       <c r="Z11">
-        <v>2.746169018358367</v>
+        <v>0.8092278266541935</v>
       </c>
       <c r="AA11">
-        <v>0.5358705927663597</v>
+        <v>0.396702968697627</v>
       </c>
       <c r="AB11">
-        <v>0.07023003727369226</v>
+        <v>0.0622477873769812</v>
       </c>
       <c r="AC11">
-        <v>0.4656405554926675</v>
+        <v>0.3344551813206458</v>
       </c>
       <c r="AD11">
-        <v>4.92</v>
+        <v>6.77</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.03836052929659627</v>
       </c>
       <c r="AF11">
-        <v>4.92</v>
+        <v>6.808360529296595</v>
       </c>
       <c r="AG11">
-        <v>4.831</v>
+        <v>-241.6916394707034</v>
       </c>
       <c r="AH11">
-        <v>0.140893470790378</v>
+        <v>0.005909992290479955</v>
       </c>
       <c r="AI11">
-        <v>0.13290113452188</v>
+        <v>0.01051633087303713</v>
       </c>
       <c r="AJ11">
-        <v>0.1386982860095891</v>
+        <v>-0.2675034897619704</v>
       </c>
       <c r="AK11">
-        <v>0.1308115133627576</v>
+        <v>-0.6058826121117437</v>
       </c>
       <c r="AL11">
-        <v>0.266</v>
+        <v>0.3</v>
       </c>
       <c r="AM11">
-        <v>0.266</v>
+        <v>0.3</v>
       </c>
       <c r="AN11">
-        <v>0.9628180039138943</v>
+        <v>0.03398389655241652</v>
       </c>
       <c r="AO11">
-        <v>17.4812030075188</v>
+        <v>655.3333333333334</v>
       </c>
       <c r="AP11">
-        <v>0.9454011741682973</v>
+        <v>-1.21323835647804</v>
       </c>
       <c r="AQ11">
-        <v>17.4812030075188</v>
+        <v>655.3333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1898,124 +1880,124 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0693</v>
+        <v>-0.0922</v>
       </c>
       <c r="E12">
-        <v>-0.114</v>
+        <v>-0.156</v>
       </c>
       <c r="F12">
-        <v>-0.169</v>
+        <v>-0.167</v>
       </c>
       <c r="G12">
-        <v>0.7027431421446384</v>
+        <v>0.6021453287197233</v>
       </c>
       <c r="H12">
-        <v>0.678927680798005</v>
+        <v>0.572318339100346</v>
       </c>
       <c r="I12">
-        <v>0.6754442685180488</v>
+        <v>0.5684570813590833</v>
       </c>
       <c r="J12">
-        <v>0.4669985595391851</v>
+        <v>0.393603487479005</v>
       </c>
       <c r="K12">
-        <v>69.90000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="L12">
-        <v>0.435785536159601</v>
+        <v>0.372318339100346</v>
       </c>
       <c r="M12">
-        <v>95.34999999999999</v>
+        <v>59.96</v>
       </c>
       <c r="N12">
-        <v>0.136780949648544</v>
+        <v>0.1171551387260649</v>
       </c>
       <c r="O12">
-        <v>1.364091559370529</v>
+        <v>1.114498141263941</v>
       </c>
       <c r="P12">
-        <v>87.8</v>
+        <v>53.5</v>
       </c>
       <c r="Q12">
-        <v>0.1259503658011763</v>
+        <v>0.1045330207112153</v>
       </c>
       <c r="R12">
-        <v>1.256080114449213</v>
+        <v>0.9944237918215614</v>
       </c>
       <c r="S12">
-        <v>7.549999999999997</v>
+        <v>6.460000000000001</v>
       </c>
       <c r="T12">
-        <v>0.07918196119559515</v>
+        <v>0.1077384923282188</v>
       </c>
       <c r="U12">
-        <v>60.3</v>
+        <v>57.4</v>
       </c>
       <c r="V12">
-        <v>0.08650121933725433</v>
+        <v>0.1121531848378273</v>
       </c>
       <c r="W12">
-        <v>0.2726209048361935</v>
+        <v>0.2413638402871243</v>
       </c>
       <c r="X12">
-        <v>0.0725781997958653</v>
+        <v>0.06237976029289417</v>
       </c>
       <c r="Y12">
-        <v>0.2000427050403282</v>
+        <v>0.1789840799942301</v>
       </c>
       <c r="Z12">
-        <v>1.039003460206585</v>
+        <v>0.8690696438973214</v>
       </c>
       <c r="AA12">
-        <v>0.4852131192727045</v>
+        <v>0.3420688427001227</v>
       </c>
       <c r="AB12">
-        <v>0.0723715740532959</v>
+        <v>0.06224653817210412</v>
       </c>
       <c r="AC12">
-        <v>0.4128415452194086</v>
+        <v>0.2798223045280185</v>
       </c>
       <c r="AD12">
-        <v>3.62</v>
+        <v>2.17</v>
       </c>
       <c r="AE12">
-        <v>0.048696648524778</v>
+        <v>0.04975871806231897</v>
       </c>
       <c r="AF12">
-        <v>3.668696648524778</v>
+        <v>2.219758718062319</v>
       </c>
       <c r="AG12">
-        <v>-56.63130335147522</v>
+        <v>-55.18024128193768</v>
       </c>
       <c r="AH12">
-        <v>0.005235246189035805</v>
+        <v>0.004318430722582101</v>
       </c>
       <c r="AI12">
-        <v>0.01619242509134443</v>
+        <v>0.01002059017628085</v>
       </c>
       <c r="AJ12">
-        <v>-0.08842165690191919</v>
+        <v>-0.1208450581219996</v>
       </c>
       <c r="AK12">
-        <v>-0.3406011142986708</v>
+        <v>-0.3362193663514373</v>
       </c>
       <c r="AL12">
-        <v>0.105</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AM12">
-        <v>0.105</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AN12">
-        <v>0.03322594560857633</v>
+        <v>0.02622293116782675</v>
       </c>
       <c r="AO12">
-        <v>1031.428571428571</v>
+        <v>1189.855072463768</v>
       </c>
       <c r="AP12">
-        <v>-0.5197869074306359</v>
+        <v>-0.6668145939909329</v>
       </c>
       <c r="AQ12">
-        <v>1031.428571428571</v>
+        <v>1189.855072463768</v>
       </c>
     </row>
     <row r="13">
@@ -2035,46 +2017,46 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.483</v>
+        <v>0.206</v>
       </c>
       <c r="E13">
-        <v>0.186</v>
+        <v>0.0868</v>
       </c>
       <c r="G13">
-        <v>0.05205640423031727</v>
+        <v>0.04634146341463415</v>
       </c>
       <c r="H13">
-        <v>0.05205640423031727</v>
+        <v>0.04634146341463415</v>
       </c>
       <c r="I13">
-        <v>0.04477085781433608</v>
+        <v>0.03635307781649245</v>
       </c>
       <c r="J13">
-        <v>0.03088470940133345</v>
+        <v>0.02466255566974992</v>
       </c>
       <c r="K13">
-        <v>2.45</v>
+        <v>1.88</v>
       </c>
       <c r="L13">
-        <v>0.02878965922444184</v>
+        <v>0.02183507549361208</v>
       </c>
       <c r="M13">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="N13">
-        <v>0.0416</v>
+        <v>0.04259259259259259</v>
       </c>
       <c r="O13">
-        <v>0.4244897959183673</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="P13">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="Q13">
-        <v>0.0416</v>
+        <v>0.04259259259259259</v>
       </c>
       <c r="R13">
-        <v>0.4244897959183673</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2083,73 +2065,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1.74</v>
+        <v>0.256</v>
       </c>
       <c r="V13">
-        <v>0.0696</v>
+        <v>0.007901234567901235</v>
       </c>
       <c r="W13">
-        <v>0.09245283018867925</v>
+        <v>0.07230769230769231</v>
       </c>
       <c r="X13">
-        <v>0.07336732531171725</v>
+        <v>0.0630803924062366</v>
       </c>
       <c r="Y13">
-        <v>0.01908550487696201</v>
+        <v>0.00922729990145571</v>
       </c>
       <c r="Z13">
-        <v>14.7410358565737</v>
+        <v>11.43578164430867</v>
       </c>
       <c r="AA13">
-        <v>0.4552726087049154</v>
+        <v>0.2820356014298667</v>
       </c>
       <c r="AB13">
-        <v>0.07186517473883981</v>
+        <v>0.06166658213331562</v>
       </c>
       <c r="AC13">
-        <v>0.3834074339660756</v>
+        <v>0.2203690192965511</v>
       </c>
       <c r="AD13">
-        <v>0.969</v>
+        <v>1.52</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.969</v>
+        <v>1.52</v>
       </c>
       <c r="AG13">
-        <v>-0.771</v>
+        <v>1.264</v>
       </c>
       <c r="AH13">
-        <v>0.03731372020485964</v>
+        <v>0.04481132075471698</v>
       </c>
       <c r="AI13">
-        <v>0.035930142014906</v>
+        <v>0.05563689604685212</v>
       </c>
       <c r="AJ13">
-        <v>-0.0318213710842379</v>
+        <v>0.03754752851711027</v>
       </c>
       <c r="AK13">
-        <v>-0.03056006976098934</v>
+        <v>0.04670410877919007</v>
       </c>
       <c r="AL13">
-        <v>0.063</v>
+        <v>0.351</v>
       </c>
       <c r="AM13">
-        <v>0.063</v>
+        <v>0.304</v>
       </c>
       <c r="AN13">
-        <v>0.2187358916478555</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="AO13">
-        <v>60.47619047619047</v>
+        <v>8.917378917378917</v>
       </c>
       <c r="AP13">
-        <v>-0.1740406320541761</v>
+        <v>0.3167919799498747</v>
       </c>
       <c r="AQ13">
-        <v>60.47619047619047</v>
+        <v>10.29605263157895</v>
       </c>
     </row>
     <row r="14">
@@ -2160,7 +2142,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Magellan Financial Group Limited (ASX:MFG)</t>
+          <t>Perpetual Limited (ASX:PPT)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2169,124 +2151,124 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.102</v>
+        <v>0.139</v>
       </c>
       <c r="E14">
-        <v>0.143</v>
+        <v>-0.159</v>
       </c>
       <c r="F14">
-        <v>-0.26</v>
+        <v>0.0834</v>
       </c>
       <c r="G14">
-        <v>0.7598944591029023</v>
+        <v>0.2051431062036903</v>
       </c>
       <c r="H14">
-        <v>0.7598944591029023</v>
+        <v>0.2051431062036903</v>
       </c>
       <c r="I14">
-        <v>0.7509534194500369</v>
+        <v>0.1342437890454744</v>
       </c>
       <c r="J14">
-        <v>0.5799725121242749</v>
+        <v>0.08896763759674776</v>
       </c>
       <c r="K14">
-        <v>263.9</v>
+        <v>39.3</v>
       </c>
       <c r="L14">
-        <v>0.6963060686015831</v>
+        <v>0.05709719599012059</v>
       </c>
       <c r="M14">
-        <v>253.25</v>
+        <v>100.8</v>
       </c>
       <c r="N14">
-        <v>0.2296219058844863</v>
+        <v>0.05191059841384282</v>
       </c>
       <c r="O14">
-        <v>0.9596438044713907</v>
+        <v>2.564885496183206</v>
       </c>
       <c r="P14">
-        <v>248.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="Q14">
-        <v>0.2253150784295947</v>
+        <v>0.04511278195488722</v>
       </c>
       <c r="R14">
-        <v>0.9416445623342176</v>
+        <v>2.229007633587786</v>
       </c>
       <c r="S14">
-        <v>4.75</v>
+        <v>13.2</v>
       </c>
       <c r="T14">
-        <v>0.01875616979269496</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="U14">
-        <v>289.3</v>
+        <v>175.2</v>
       </c>
       <c r="V14">
-        <v>0.2623084595158219</v>
+        <v>0.09022556390977443</v>
       </c>
       <c r="W14">
-        <v>0.3557562685359935</v>
+        <v>0.06160840257093588</v>
       </c>
       <c r="X14">
-        <v>0.07263926656421707</v>
+        <v>0.06696345624406257</v>
       </c>
       <c r="Y14">
-        <v>0.2831170019717765</v>
+        <v>-0.005355053673126685</v>
       </c>
       <c r="Z14">
-        <v>0.7330566194089642</v>
+        <v>2.150937499999999</v>
       </c>
       <c r="AA14">
-        <v>0.4251526890879455</v>
+        <v>0.1913638279932545</v>
       </c>
       <c r="AB14">
-        <v>0.07237319292122608</v>
+        <v>0.06004732663671498</v>
       </c>
       <c r="AC14">
-        <v>0.3527794961667194</v>
+        <v>0.1313165013565396</v>
       </c>
       <c r="AD14">
-        <v>8.65</v>
+        <v>549.3</v>
       </c>
       <c r="AE14">
-        <v>0.01327014218009479</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>8.663270142180096</v>
+        <v>549.3</v>
       </c>
       <c r="AG14">
-        <v>-280.6367298578199</v>
+        <v>374.1</v>
       </c>
       <c r="AH14">
-        <v>0.007793771506206727</v>
+        <v>0.22050499779214</v>
       </c>
       <c r="AI14">
-        <v>0.01209847020984603</v>
+        <v>0.2581296992481203</v>
       </c>
       <c r="AJ14">
-        <v>-0.3412979030539623</v>
+        <v>0.1615354721706464</v>
       </c>
       <c r="AK14">
-        <v>-0.657593446981328</v>
+        <v>0.1915710774272839</v>
       </c>
       <c r="AL14">
-        <v>0.377</v>
+        <v>29.8</v>
       </c>
       <c r="AM14">
-        <v>0.377</v>
+        <v>29.8</v>
       </c>
       <c r="AN14">
-        <v>0.03003326227197289</v>
+        <v>3.890226628895184</v>
       </c>
       <c r="AO14">
-        <v>754.9071618037136</v>
+        <v>3.100671140939598</v>
       </c>
       <c r="AP14">
-        <v>-0.9743857238114115</v>
+        <v>2.64943342776204</v>
       </c>
       <c r="AQ14">
-        <v>754.9071618037136</v>
+        <v>3.100671140939598</v>
       </c>
     </row>
     <row r="15">
@@ -2297,7 +2279,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bailador Technology Investments Limited (ASX:BTI)</t>
+          <t>MFF Capital Investments Limited (ASX:MFF)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2306,10 +2288,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.527</v>
+        <v>0.0774</v>
       </c>
       <c r="E15">
-        <v>0.578</v>
+        <v>0.0617</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2318,97 +2300,103 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.7818448023426061</v>
+        <v>0.9895895300416419</v>
       </c>
       <c r="J15">
-        <v>0.54774156018244</v>
+        <v>0.6926483284069099</v>
       </c>
       <c r="K15">
-        <v>36.5</v>
+        <v>215.4</v>
       </c>
       <c r="L15">
-        <v>0.5344070278184481</v>
+        <v>0.6406900654372398</v>
       </c>
       <c r="M15">
-        <v>0.897</v>
+        <v>42.2</v>
       </c>
       <c r="N15">
-        <v>0.007582417582417583</v>
+        <v>0.03460718386091521</v>
       </c>
       <c r="O15">
-        <v>0.02457534246575343</v>
+        <v>0.1959145775301764</v>
       </c>
       <c r="P15">
-        <v>0.897</v>
+        <v>25.1</v>
       </c>
       <c r="Q15">
-        <v>0.007582417582417583</v>
+        <v>0.02058389371822207</v>
       </c>
       <c r="R15">
-        <v>0.02457534246575343</v>
+        <v>0.11652739090065</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.4052132701421801</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>18.8</v>
       </c>
       <c r="V15">
-        <v>0.1014370245139476</v>
+        <v>0.01541741840249303</v>
       </c>
       <c r="W15">
-        <v>0.3074978938500421</v>
+        <v>0.2193929517213282</v>
       </c>
       <c r="X15">
-        <v>0.07245421904070486</v>
+        <v>0.06552830903215197</v>
       </c>
       <c r="Y15">
-        <v>0.2350436748093372</v>
+        <v>0.1538646426891762</v>
       </c>
       <c r="Z15">
-        <v>0.584510055626872</v>
+        <v>0.2721165520032375</v>
       </c>
       <c r="AA15">
-        <v>0.3201604498113877</v>
+        <v>0.1884810748768945</v>
       </c>
       <c r="AB15">
-        <v>0.07245421904070486</v>
+        <v>0.05996454176529911</v>
       </c>
       <c r="AC15">
-        <v>0.2477062307706828</v>
+        <v>0.1285165331115954</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>238.6</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>238.6</v>
       </c>
       <c r="AG15">
-        <v>-12</v>
+        <v>219.8</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.1636488340192044</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>0.175235017626322</v>
       </c>
       <c r="AJ15">
-        <v>-0.1128880526810913</v>
+        <v>0.1527237354085603</v>
       </c>
       <c r="AK15">
-        <v>-0.07863695937090433</v>
+        <v>0.1636878165028299</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>11.1</v>
+      </c>
+      <c r="AO15">
+        <v>29.97297297297297</v>
+      </c>
+      <c r="AQ15">
+        <v>29.97297297297297</v>
       </c>
     </row>
     <row r="16">
@@ -2428,49 +2416,49 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0689</v>
+        <v>0.0983</v>
       </c>
       <c r="E16">
-        <v>0.09429999999999999</v>
+        <v>-0.008920000000000001</v>
       </c>
       <c r="F16">
-        <v>0.0725</v>
+        <v>0.142</v>
       </c>
       <c r="G16">
-        <v>0.3776041666666667</v>
+        <v>0.2518597236981934</v>
       </c>
       <c r="H16">
-        <v>0.3776041666666667</v>
+        <v>0.2518597236981934</v>
       </c>
       <c r="I16">
-        <v>0.3567708333333333</v>
+        <v>0.2380446333687566</v>
       </c>
       <c r="J16">
-        <v>0.2174072265625</v>
+        <v>0.1334211140198543</v>
       </c>
       <c r="K16">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="L16">
-        <v>0.2174479166666667</v>
+        <v>0.1328374070138151</v>
       </c>
       <c r="M16">
-        <v>11.5</v>
+        <v>14.8</v>
       </c>
       <c r="N16">
-        <v>0.02556691863050245</v>
+        <v>0.03197925669835782</v>
       </c>
       <c r="O16">
-        <v>0.688622754491018</v>
+        <v>1.184</v>
       </c>
       <c r="P16">
-        <v>11.5</v>
+        <v>14.8</v>
       </c>
       <c r="Q16">
-        <v>0.02556691863050245</v>
+        <v>0.03197925669835782</v>
       </c>
       <c r="R16">
-        <v>0.688622754491018</v>
+        <v>1.184</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2479,73 +2467,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>74.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="V16">
-        <v>0.1658514895509115</v>
+        <v>0.1432584269662921</v>
       </c>
       <c r="W16">
-        <v>0.08048192771084337</v>
+        <v>0.06358087487283826</v>
       </c>
       <c r="X16">
-        <v>0.07427684415371413</v>
+        <v>0.06373778795973736</v>
       </c>
       <c r="Y16">
-        <v>0.006205083557129232</v>
+        <v>-0.0001569130868991075</v>
       </c>
       <c r="Z16">
-        <v>1.043478260869565</v>
+        <v>1.365747460087083</v>
       </c>
       <c r="AA16">
-        <v>0.226859714673913</v>
+        <v>0.1822195475946052</v>
       </c>
       <c r="AB16">
-        <v>0.07132057882860217</v>
+        <v>0.06116373417050984</v>
       </c>
       <c r="AC16">
-        <v>0.1555391358453108</v>
+        <v>0.1210558134240953</v>
       </c>
       <c r="AD16">
-        <v>34.8</v>
+        <v>40.2</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>34.8</v>
+        <v>40.2</v>
       </c>
       <c r="AG16">
-        <v>-39.8</v>
+        <v>-26.09999999999999</v>
       </c>
       <c r="AH16">
-        <v>0.07181180354931901</v>
+        <v>0.07992047713717694</v>
       </c>
       <c r="AI16">
-        <v>0.1522309711286089</v>
+        <v>0.1313296308395949</v>
       </c>
       <c r="AJ16">
-        <v>-0.09707317073170731</v>
+        <v>-0.05976643004350811</v>
       </c>
       <c r="AK16">
-        <v>-0.2584415584415584</v>
+        <v>-0.1088407005838198</v>
       </c>
       <c r="AL16">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AM16">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AN16">
-        <v>1.2</v>
+        <v>1.69620253164557</v>
       </c>
       <c r="AO16">
-        <v>20.14705882352941</v>
+        <v>15.13513513513514</v>
       </c>
       <c r="AP16">
-        <v>-1.372413793103448</v>
+        <v>-1.10126582278481</v>
       </c>
       <c r="AQ16">
-        <v>20.14705882352941</v>
+        <v>15.13513513513514</v>
       </c>
     </row>
     <row r="17">
@@ -2556,7 +2544,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Perpetual Limited (ASX:PPT)</t>
+          <t>Tribeca Global Natural Resources Limited (ASX:TGF)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2564,125 +2552,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.0755</v>
-      </c>
-      <c r="E17">
-        <v>-0.0592</v>
-      </c>
-      <c r="F17">
-        <v>0.0476</v>
-      </c>
       <c r="G17">
-        <v>0.2373668925459826</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0.2373668925459826</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0.1957405614714424</v>
+        <v>0.845679012345679</v>
       </c>
       <c r="J17">
-        <v>0.1442189971940754</v>
+        <v>0.5356670053261906</v>
       </c>
       <c r="K17">
-        <v>69.7</v>
+        <v>5.08</v>
       </c>
       <c r="L17">
-        <v>0.134946757018393</v>
+        <v>0.3135802469135803</v>
       </c>
       <c r="M17">
-        <v>87.60000000000001</v>
+        <v>2.49</v>
       </c>
       <c r="N17">
-        <v>0.09247334529716036</v>
+        <v>0.02663101604278075</v>
       </c>
       <c r="O17">
-        <v>1.256814921090387</v>
+        <v>0.4901574803149606</v>
       </c>
       <c r="P17">
-        <v>77.40000000000001</v>
+        <v>2.49</v>
       </c>
       <c r="Q17">
-        <v>0.08170590098173758</v>
+        <v>0.02663101604278075</v>
       </c>
       <c r="R17">
-        <v>1.110473457675753</v>
+        <v>0.4901574803149606</v>
       </c>
       <c r="S17">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>0.1164383561643836</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>120.8</v>
+        <v>35</v>
       </c>
       <c r="V17">
-        <v>0.1275203209120659</v>
+        <v>0.374331550802139</v>
       </c>
       <c r="W17">
-        <v>0.1024849286869578</v>
+        <v>0.05100401606425703</v>
       </c>
       <c r="X17">
-        <v>0.0781192689385522</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y17">
-        <v>0.0243656597484056</v>
+        <v>-0.0113043724715446</v>
       </c>
       <c r="Z17">
-        <v>1.515107069521853</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="AA17">
-        <v>0.218507222208096</v>
+        <v>0.1491031870495582</v>
       </c>
       <c r="AB17">
-        <v>0.07043884219682622</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC17">
-        <v>0.1480683800112698</v>
+        <v>0.08679479851375661</v>
       </c>
       <c r="AD17">
-        <v>227.8</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>227.8</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>107</v>
+        <v>-35</v>
       </c>
       <c r="AH17">
-        <v>0.1938558420559953</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.2631396557698972</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>0.101489139713554</v>
+        <v>-0.5982905982905983</v>
       </c>
       <c r="AK17">
-        <v>0.1436434420727615</v>
+        <v>-0.4211793020457281</v>
       </c>
       <c r="AL17">
-        <v>6.34</v>
+        <v>3.19</v>
       </c>
       <c r="AM17">
-        <v>6.34</v>
-      </c>
-      <c r="AN17">
-        <v>1.858075040783034</v>
+        <v>3.19</v>
       </c>
       <c r="AO17">
-        <v>15.94637223974763</v>
-      </c>
-      <c r="AP17">
-        <v>0.8727569331158239</v>
+        <v>4.294670846394984</v>
       </c>
       <c r="AQ17">
-        <v>15.94637223974763</v>
+        <v>4.294670846394984</v>
       </c>
     </row>
     <row r="18">
@@ -2693,7 +2666,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pendal Group Limited (ASX:PDL)</t>
+          <t>Katana Capital Limited (ASX:KAT)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2702,124 +2675,109 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0413</v>
+        <v>-0.0571</v>
       </c>
       <c r="E18">
-        <v>-0.0522</v>
-      </c>
-      <c r="F18">
-        <v>-0.14</v>
+        <v>-0.0533</v>
       </c>
       <c r="G18">
-        <v>0.3244002041858091</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>0.3244002041858091</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0.2743746809596733</v>
+        <v>0.7855750487329435</v>
       </c>
       <c r="J18">
-        <v>0.2077816594350859</v>
+        <v>0.57169074793288</v>
       </c>
       <c r="K18">
-        <v>72.59999999999999</v>
+        <v>2.86</v>
       </c>
       <c r="L18">
-        <v>0.1852986217457886</v>
+        <v>0.5575048732943469</v>
       </c>
       <c r="M18">
-        <v>144.7</v>
+        <v>0.86</v>
       </c>
       <c r="N18">
-        <v>0.1185676827269747</v>
+        <v>0.03385826771653543</v>
       </c>
       <c r="O18">
-        <v>1.993112947658402</v>
+        <v>0.3006993006993007</v>
       </c>
       <c r="P18">
-        <v>107</v>
+        <v>0.451</v>
       </c>
       <c r="Q18">
-        <v>0.08767617174696821</v>
+        <v>0.01775590551181103</v>
       </c>
       <c r="R18">
-        <v>1.473829201101928</v>
+        <v>0.1576923076923077</v>
       </c>
       <c r="S18">
-        <v>37.69999999999999</v>
+        <v>0.409</v>
       </c>
       <c r="T18">
-        <v>0.2605390463026952</v>
+        <v>0.4755813953488372</v>
       </c>
       <c r="U18">
-        <v>203.8</v>
+        <v>7.11</v>
       </c>
       <c r="V18">
-        <v>0.166994428056375</v>
+        <v>0.2799212598425197</v>
       </c>
       <c r="W18">
-        <v>0.07241172950329143</v>
+        <v>0.1075187969924812</v>
       </c>
       <c r="X18">
-        <v>0.07357961127198244</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y18">
-        <v>-0.001167881768691009</v>
+        <v>0.04521040845667956</v>
       </c>
       <c r="Z18">
-        <v>0.8449428509812379</v>
+        <v>0.2366236162361623</v>
       </c>
       <c r="AA18">
-        <v>0.1755636277046941</v>
+        <v>0.1352755321446344</v>
       </c>
       <c r="AB18">
-        <v>0.07198022022079249</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC18">
-        <v>0.1035834074839016</v>
+        <v>0.07296714360883279</v>
       </c>
       <c r="AD18">
-        <v>58.3</v>
+        <v>0</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>58.3</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>-145.5</v>
+        <v>-7.11</v>
       </c>
       <c r="AH18">
-        <v>0.04559318057402049</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>0.06415052816901408</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.1353614289701368</v>
+        <v>-0.3887370147621652</v>
       </c>
       <c r="AK18">
-        <v>-0.2063829787234042</v>
+        <v>-0.345313258863526</v>
       </c>
       <c r="AL18">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.7</v>
-      </c>
-      <c r="AN18">
-        <v>0.4586939417781274</v>
-      </c>
-      <c r="AO18">
-        <v>63.23529411764706</v>
-      </c>
-      <c r="AP18">
-        <v>-1.144767899291896</v>
-      </c>
-      <c r="AQ18">
-        <v>63.23529411764706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2830,7 +2788,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insignia Financial Ltd. (ASX:IFL)</t>
+          <t>NGE Capital Limited (ASX:NGE)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2839,124 +2797,121 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.188</v>
+        <v>0.0386</v>
       </c>
       <c r="E19">
-        <v>-0.205</v>
-      </c>
-      <c r="F19">
-        <v>-0.205</v>
+        <v>-0.258</v>
       </c>
       <c r="G19">
-        <v>0.1134076325565687</v>
+        <v>-0.04535714285714286</v>
       </c>
       <c r="H19">
-        <v>0.1134076325565687</v>
+        <v>-0.04535714285714286</v>
       </c>
       <c r="I19">
-        <v>0.07666328942924687</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="J19">
-        <v>0.05343964827247501</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="K19">
-        <v>25.4</v>
+        <v>1.1</v>
       </c>
       <c r="L19">
-        <v>0.0171563660925363</v>
+        <v>0.3928571428571429</v>
       </c>
       <c r="M19">
-        <v>83.90000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="N19">
-        <v>0.0560154893844305</v>
+        <v>0.002053571428571428</v>
       </c>
       <c r="O19">
-        <v>3.303149606299213</v>
+        <v>0.04181818181818182</v>
       </c>
       <c r="P19">
-        <v>83.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.0560154893844305</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>3.303149606299213</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>353.9</v>
+        <v>3.9</v>
       </c>
       <c r="V19">
-        <v>0.236279877153158</v>
+        <v>0.1741071428571429</v>
       </c>
       <c r="W19">
-        <v>0.01358870104857693</v>
+        <v>0.04435483870967742</v>
       </c>
       <c r="X19">
-        <v>0.08286482747182368</v>
+        <v>0.06231059244722686</v>
       </c>
       <c r="Y19">
-        <v>-0.06927612642324675</v>
+        <v>-0.01795575373754944</v>
       </c>
       <c r="Z19">
-        <v>2.634341637010677</v>
+        <v>0.1702955844787739</v>
       </c>
       <c r="AA19">
-        <v>0.1407782905113867</v>
+        <v>0.1338036735190366</v>
       </c>
       <c r="AB19">
-        <v>0.06761607982002014</v>
+        <v>0.06230647061187707</v>
       </c>
       <c r="AC19">
-        <v>0.07316221069136651</v>
+        <v>0.07149720290715957</v>
       </c>
       <c r="AD19">
-        <v>661.9</v>
+        <v>0.003</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>661.9</v>
+        <v>0.003</v>
       </c>
       <c r="AG19">
-        <v>308</v>
+        <v>-3.897</v>
       </c>
       <c r="AH19">
-        <v>0.3064777515395657</v>
+        <v>0.0001339106369682632</v>
       </c>
       <c r="AI19">
-        <v>0.2857821337593368</v>
+        <v>0.0001199856017277927</v>
       </c>
       <c r="AJ19">
-        <v>0.1705615239782922</v>
+        <v>-0.2106144949467654</v>
       </c>
       <c r="AK19">
-        <v>0.1569666700642136</v>
+        <v>-0.1846656873430318</v>
       </c>
       <c r="AL19">
-        <v>20.2</v>
+        <v>0.001</v>
       </c>
       <c r="AM19">
-        <v>20.2</v>
+        <v>0.001</v>
       </c>
       <c r="AN19">
-        <v>3.942227516378797</v>
+        <v>0.001363636363636364</v>
       </c>
       <c r="AO19">
-        <v>5.618811881188119</v>
+        <v>2200</v>
       </c>
       <c r="AP19">
-        <v>1.834425253126861</v>
+        <v>-1.771363636363636</v>
       </c>
       <c r="AQ19">
-        <v>5.618811881188119</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="20">
@@ -2967,7 +2922,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BlackWall Limited (ASX:BWF)</t>
+          <t>Teaminvest Private Group Limited (ASX:TIP)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2976,46 +2931,46 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.183</v>
+        <v>0.0581</v>
       </c>
       <c r="E20">
-        <v>-0.144</v>
+        <v>-0.0125</v>
       </c>
       <c r="G20">
-        <v>0.3013698630136987</v>
+        <v>0.09082321187584347</v>
       </c>
       <c r="H20">
-        <v>0.3013698630136987</v>
+        <v>0.09082321187584347</v>
       </c>
       <c r="I20">
-        <v>0.2945205479452055</v>
+        <v>0.0678812415654521</v>
       </c>
       <c r="J20">
-        <v>0.2611568921232877</v>
+        <v>0.05841187376325801</v>
       </c>
       <c r="K20">
-        <v>1.13</v>
+        <v>2.7</v>
       </c>
       <c r="L20">
-        <v>0.2579908675799086</v>
+        <v>0.03643724696356276</v>
       </c>
       <c r="M20">
-        <v>2.38</v>
+        <v>0.44</v>
       </c>
       <c r="N20">
-        <v>0.08122866894197951</v>
+        <v>0.0123249299719888</v>
       </c>
       <c r="O20">
-        <v>2.106194690265487</v>
+        <v>0.1629629629629629</v>
       </c>
       <c r="P20">
-        <v>2.38</v>
+        <v>0.44</v>
       </c>
       <c r="Q20">
-        <v>0.08122866894197951</v>
+        <v>0.0123249299719888</v>
       </c>
       <c r="R20">
-        <v>2.106194690265487</v>
+        <v>0.1629629629629629</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -3024,73 +2979,73 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0.803</v>
+        <v>5.24</v>
       </c>
       <c r="V20">
-        <v>0.0274061433447099</v>
+        <v>0.1467787114845938</v>
       </c>
       <c r="W20">
-        <v>0.06848484848484848</v>
+        <v>0.04812834224598931</v>
       </c>
       <c r="X20">
-        <v>0.07271231129389416</v>
+        <v>0.06321184817364812</v>
       </c>
       <c r="Y20">
-        <v>-0.004227462809045679</v>
+        <v>-0.01508350592765881</v>
       </c>
       <c r="Z20">
-        <v>0.3000616565047612</v>
+        <v>2.026251025430681</v>
       </c>
       <c r="AA20">
-        <v>0.07836316965814893</v>
+        <v>0.118357119110129</v>
       </c>
       <c r="AB20">
-        <v>0.07234155568384251</v>
+        <v>0.06177472224639507</v>
       </c>
       <c r="AC20">
-        <v>0.006021613974306422</v>
+        <v>0.05658239686373396</v>
       </c>
       <c r="AD20">
-        <v>0.321</v>
+        <v>1.96</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.321</v>
+        <v>1.96</v>
       </c>
       <c r="AG20">
-        <v>-0.482</v>
+        <v>-3.28</v>
       </c>
       <c r="AH20">
-        <v>0.010836906248945</v>
+        <v>0.0520446096654275</v>
       </c>
       <c r="AI20">
-        <v>0.02028948865432021</v>
+        <v>0.03279785809906292</v>
       </c>
       <c r="AJ20">
-        <v>-0.01672565757512666</v>
+        <v>-0.1011721159777915</v>
       </c>
       <c r="AK20">
-        <v>-0.03209481954987348</v>
+        <v>-0.06016140865737345</v>
       </c>
       <c r="AL20">
-        <v>0.004</v>
+        <v>0.114</v>
       </c>
       <c r="AM20">
-        <v>0.004</v>
+        <v>0.114</v>
       </c>
       <c r="AN20">
-        <v>0.2431818181818182</v>
+        <v>0.2912332838038633</v>
       </c>
       <c r="AO20">
-        <v>322.5</v>
+        <v>44.12280701754386</v>
       </c>
       <c r="AP20">
-        <v>-0.3651515151515152</v>
+        <v>-0.487369985141159</v>
       </c>
       <c r="AQ20">
-        <v>322.5</v>
+        <v>44.12280701754386</v>
       </c>
     </row>
     <row r="21">
@@ -3101,7 +3056,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVC Limited (ASX:CVC)</t>
+          <t>Plato Income Maximiser Limited (ASX:PL8)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3110,46 +3065,46 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.09269999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="E21">
-        <v>-0.26</v>
+        <v>0.246</v>
       </c>
       <c r="G21">
-        <v>0.2793522267206478</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>0.2793522267206478</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>0.2773279352226721</v>
+        <v>0.9240506329113923</v>
       </c>
       <c r="J21">
-        <v>0.2359954064154469</v>
+        <v>0.8099781754692273</v>
       </c>
       <c r="K21">
-        <v>4.21</v>
+        <v>38.2</v>
       </c>
       <c r="L21">
-        <v>0.08522267206477734</v>
+        <v>0.8059071729957806</v>
       </c>
       <c r="M21">
-        <v>10.4</v>
+        <v>26.3</v>
       </c>
       <c r="N21">
-        <v>0.06740116655865197</v>
+        <v>0.043673198272999</v>
       </c>
       <c r="O21">
-        <v>2.470308788598575</v>
+        <v>0.6884816753926701</v>
       </c>
       <c r="P21">
-        <v>10.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q21">
-        <v>0.06740116655865197</v>
+        <v>0.043673198272999</v>
       </c>
       <c r="R21">
-        <v>2.470308788598575</v>
+        <v>0.6884816753926701</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3158,73 +3113,61 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>18.2</v>
+        <v>0.204</v>
       </c>
       <c r="V21">
-        <v>0.1179520414776409</v>
+        <v>0.0003387578877449352</v>
       </c>
       <c r="W21">
-        <v>0.03079736649597659</v>
+        <v>0.09597989949748745</v>
       </c>
       <c r="X21">
-        <v>0.0814773884620526</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y21">
-        <v>-0.05068002196607601</v>
+        <v>0.03367151096168582</v>
       </c>
       <c r="Z21">
-        <v>0.3008159785653392</v>
+        <v>0.119138283353064</v>
       </c>
       <c r="AA21">
-        <v>0.07099118911778758</v>
+        <v>0.09649940937885064</v>
       </c>
       <c r="AB21">
-        <v>0.07031170121693869</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC21">
-        <v>0.000679487900848888</v>
+        <v>0.03419102084304901</v>
       </c>
       <c r="AD21">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>59.1</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>40.90000000000001</v>
+        <v>-0.204</v>
       </c>
       <c r="AH21">
-        <v>0.2769447047797563</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>0.3276053215077605</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>0.2095286885245902</v>
+        <v>-0.0003388726835394254</v>
       </c>
       <c r="AK21">
-        <v>0.2521578298397041</v>
+        <v>-0.0004501363648399368</v>
       </c>
       <c r="AL21">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.23</v>
-      </c>
-      <c r="AN21">
-        <v>4.282608695652174</v>
-      </c>
-      <c r="AO21">
-        <v>4.241486068111455</v>
-      </c>
-      <c r="AP21">
-        <v>2.963768115942029</v>
-      </c>
-      <c r="AQ21">
-        <v>4.241486068111455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3235,7 +3178,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Navigator Global Investments Limited (ASX:NGI)</t>
+          <t>Powerhouse Ventures Limited (ASX:PVL)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3243,122 +3186,101 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.0296</v>
-      </c>
-      <c r="E22">
-        <v>0.17</v>
-      </c>
       <c r="G22">
-        <v>0.2461355529131986</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>0.2461355529131986</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0.2175980975029727</v>
+        <v>0.4330900243309003</v>
       </c>
       <c r="J22">
-        <v>0.1841727442322754</v>
+        <v>0.4330900243309003</v>
       </c>
       <c r="K22">
-        <v>38.7</v>
+        <v>0.477</v>
       </c>
       <c r="L22">
-        <v>0.4601664684898931</v>
+        <v>0.5802919708029197</v>
       </c>
       <c r="M22">
-        <v>31.4</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.1689989235737352</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.8113695090439276</v>
+        <v>-0</v>
       </c>
       <c r="P22">
-        <v>31.4</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.1689989235737352</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.8113695090439276</v>
+        <v>-0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>94</v>
+        <v>2.02</v>
       </c>
       <c r="V22">
-        <v>0.5059203444564047</v>
+        <v>0.5459459459459459</v>
       </c>
       <c r="W22">
-        <v>0.1044252563410685</v>
+        <v>0.07035398230088495</v>
       </c>
       <c r="X22">
-        <v>0.07576349020256534</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y22">
-        <v>0.0286617661385032</v>
+        <v>0.00804559376508332</v>
       </c>
       <c r="Z22">
-        <v>0.3387031816351188</v>
+        <v>0.2049875311720698</v>
       </c>
       <c r="AA22">
-        <v>0.06237989444194263</v>
+        <v>0.08877805486284289</v>
       </c>
       <c r="AB22">
-        <v>0.07117369740272129</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC22">
-        <v>-0.008793802960778661</v>
+        <v>0.02646966632704126</v>
       </c>
       <c r="AD22">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>-67.90000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="AH22">
-        <v>0.123171307220387</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>0.05937215650591447</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.5759117896522477</v>
+        <v>-1.202380952380952</v>
       </c>
       <c r="AK22">
-        <v>-0.1964699074074074</v>
+        <v>-0.398422090729783</v>
       </c>
       <c r="AL22">
-        <v>0.949</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>-70.551</v>
-      </c>
-      <c r="AN22">
-        <v>1.260869565217391</v>
-      </c>
-      <c r="AO22">
-        <v>19.28345626975764</v>
-      </c>
-      <c r="AP22">
-        <v>-3.280193236714976</v>
-      </c>
-      <c r="AQ22">
-        <v>-0.2593868265510056</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -3369,7 +3291,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Australian United Investment Company Limited (ASX:AUI)</t>
+          <t>Auctus Investment Group Limited (ASX:AVC)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3378,121 +3300,112 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.08779999999999999</v>
-      </c>
-      <c r="E23">
-        <v>0.103</v>
+        <v>7.732</v>
       </c>
       <c r="G23">
-        <v>0.9813432835820896</v>
+        <v>0.2971153846153846</v>
       </c>
       <c r="H23">
-        <v>0.9813432835820896</v>
+        <v>0.2971153846153846</v>
       </c>
       <c r="I23">
-        <v>0.9813432835820896</v>
+        <v>0.2846153846153846</v>
       </c>
       <c r="J23">
-        <v>0.9606324884453472</v>
+        <v>0.1423076923076923</v>
       </c>
       <c r="K23">
-        <v>49.6</v>
+        <v>-0.196</v>
       </c>
       <c r="L23">
-        <v>0.9253731343283582</v>
+        <v>-0.01884615384615385</v>
       </c>
       <c r="M23">
-        <v>28.9</v>
+        <v>3.87</v>
       </c>
       <c r="N23">
-        <v>0.0353214373013933</v>
+        <v>0.1023809523809524</v>
       </c>
       <c r="O23">
-        <v>0.5826612903225806</v>
+        <v>-19.74489795918367</v>
       </c>
       <c r="P23">
-        <v>28.9</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.0353214373013933</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>0.5826612903225806</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>4.64</v>
+        <v>4.08</v>
       </c>
       <c r="V23">
-        <v>0.005670985089220239</v>
+        <v>0.1079365079365079</v>
       </c>
       <c r="W23">
-        <v>0.0603479742061078</v>
+        <v>-0.008166666666666668</v>
       </c>
       <c r="X23">
-        <v>0.0757797428850473</v>
+        <v>0.06288739143862786</v>
       </c>
       <c r="Y23">
-        <v>-0.01543176867893949</v>
+        <v>-0.07105405810529453</v>
       </c>
       <c r="Z23">
-        <v>0.05830586648391694</v>
+        <v>0.5928290486233826</v>
       </c>
       <c r="AA23">
-        <v>0.05601050961140729</v>
+        <v>0.08436413384255828</v>
       </c>
       <c r="AB23">
-        <v>0.07050143582365397</v>
+        <v>0.06182158010171564</v>
       </c>
       <c r="AC23">
-        <v>-0.01449092621224667</v>
+        <v>0.02254255374084264</v>
       </c>
       <c r="AD23">
-        <v>115.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>115.5</v>
+        <v>1.33</v>
       </c>
       <c r="AG23">
-        <v>110.86</v>
+        <v>-2.75</v>
       </c>
       <c r="AH23">
-        <v>0.123701403020242</v>
+        <v>0.03398926654740609</v>
       </c>
       <c r="AI23">
-        <v>0.1386388188692834</v>
+        <v>0.06510034263338228</v>
       </c>
       <c r="AJ23">
-        <v>0.1193249090478548</v>
+        <v>-0.07845934379457918</v>
       </c>
       <c r="AK23">
-        <v>0.1338145474736258</v>
+        <v>-0.1681957186544342</v>
       </c>
       <c r="AL23">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>2.195817490494297</v>
-      </c>
-      <c r="AO23">
-        <v>27.2538860103627</v>
+        <v>0.4304207119741101</v>
       </c>
       <c r="AP23">
-        <v>2.107604562737643</v>
-      </c>
-      <c r="AQ23">
-        <v>27.2538860103627</v>
+        <v>-0.8899676375404532</v>
       </c>
     </row>
     <row r="24">
@@ -3503,7 +3416,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Argo Investments Limited (ASX:ARG)</t>
+          <t>BlackWall Limited (ASX:BWF)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3512,46 +3425,43 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.0764</v>
-      </c>
-      <c r="E24">
-        <v>0.0815</v>
+        <v>-0.233</v>
       </c>
       <c r="G24">
-        <v>0.9724650349650349</v>
+        <v>0.2978260869565218</v>
       </c>
       <c r="H24">
-        <v>0.9724650349650349</v>
+        <v>0.2978260869565218</v>
       </c>
       <c r="I24">
-        <v>0.971153846153846</v>
+        <v>0.2717391304347826</v>
       </c>
       <c r="J24">
-        <v>0.9264635806671203</v>
+        <v>0.2717391304347826</v>
       </c>
       <c r="K24">
-        <v>215.6</v>
+        <v>-0.67</v>
       </c>
       <c r="L24">
-        <v>0.9423076923076923</v>
+        <v>-0.1456521739130435</v>
       </c>
       <c r="M24">
-        <v>121.2</v>
+        <v>2.2</v>
       </c>
       <c r="N24">
-        <v>0.02649411970445503</v>
+        <v>0.03754266211604096</v>
       </c>
       <c r="O24">
-        <v>0.562152133580705</v>
+        <v>-3.283582089552239</v>
       </c>
       <c r="P24">
-        <v>121.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q24">
-        <v>0.02649411970445503</v>
+        <v>0.03754266211604096</v>
       </c>
       <c r="R24">
-        <v>0.562152133580705</v>
+        <v>-3.283582089552239</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -3560,67 +3470,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>92.8</v>
+        <v>3.85</v>
       </c>
       <c r="V24">
-        <v>0.02028592663839461</v>
+        <v>0.06569965870307168</v>
       </c>
       <c r="W24">
-        <v>0.0509475873150905</v>
+        <v>-0.04322580645161291</v>
       </c>
       <c r="X24">
-        <v>0.07245687115148267</v>
+        <v>0.06330528862985396</v>
       </c>
       <c r="Y24">
-        <v>-0.02150928383639216</v>
+        <v>-0.1065310950814669</v>
       </c>
       <c r="Z24">
-        <v>0.05582951111844225</v>
+        <v>0.3062991077373818</v>
       </c>
       <c r="AA24">
-        <v>0.05172400877768681</v>
+        <v>0.08323345318950594</v>
       </c>
       <c r="AB24">
-        <v>0.07245244205218287</v>
+        <v>0.06172268042975772</v>
       </c>
       <c r="AC24">
-        <v>-0.02072843327449606</v>
+        <v>0.02151077275974822</v>
       </c>
       <c r="AD24">
-        <v>0.515</v>
+        <v>3.55</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0.515</v>
+        <v>3.55</v>
       </c>
       <c r="AG24">
-        <v>-92.285</v>
+        <v>-0.3000000000000003</v>
       </c>
       <c r="AH24">
-        <v>0.0001125654764962192</v>
+        <v>0.05711987127916331</v>
       </c>
       <c r="AI24">
-        <v>0.0001325913367652606</v>
+        <v>0.2253968253968254</v>
       </c>
       <c r="AJ24">
-        <v>-0.02058869133472324</v>
+        <v>-0.005145797598627791</v>
       </c>
       <c r="AK24">
-        <v>-0.02434115867449684</v>
+        <v>-0.02521008403361347</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="AN24">
-        <v>0.002314606741573034</v>
+        <v>2.591240875912408</v>
+      </c>
+      <c r="AO24">
+        <v>33.78378378378378</v>
       </c>
       <c r="AP24">
-        <v>-0.4147640449438202</v>
+        <v>-0.2189781021897812</v>
+      </c>
+      <c r="AQ24">
+        <v>33.78378378378378</v>
       </c>
     </row>
     <row r="25">
@@ -3631,7 +3547,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKI Investment Company Limited (ASX:BKI)</t>
+          <t>Queste Communications Ltd (ASX:QUE)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3640,79 +3556,73 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0735</v>
-      </c>
-      <c r="E25">
-        <v>0.172</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.460122699386503</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.460122699386503</v>
       </c>
       <c r="I25">
-        <v>0.965675057208238</v>
+        <v>0.4539877300613497</v>
       </c>
       <c r="J25">
-        <v>0.9362732188742442</v>
+        <v>0.4539877300613497</v>
       </c>
       <c r="K25">
-        <v>69.40000000000001</v>
+        <v>-0.334</v>
       </c>
       <c r="L25">
-        <v>1.588100686498856</v>
+        <v>-2.049079754601227</v>
       </c>
       <c r="M25">
-        <v>28.6</v>
+        <v>-0</v>
       </c>
       <c r="N25">
-        <v>0.03143893591293833</v>
+        <v>-0</v>
       </c>
       <c r="O25">
-        <v>0.4121037463976945</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>28.6</v>
+        <v>-0</v>
       </c>
       <c r="Q25">
-        <v>0.03143893591293833</v>
+        <v>-0</v>
       </c>
       <c r="R25">
-        <v>0.4121037463976945</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
       <c r="U25">
-        <v>49.7</v>
+        <v>0.099</v>
       </c>
       <c r="V25">
-        <v>0.0546333956249313</v>
+        <v>0.1341463414634146</v>
       </c>
       <c r="W25">
-        <v>0.0789533560864619</v>
+        <v>-0.3461139896373057</v>
       </c>
       <c r="X25">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y25">
-        <v>0.006499137045757039</v>
+        <v>-0.4084223781731073</v>
       </c>
       <c r="Z25">
-        <v>0.05149658260664625</v>
+        <v>0.1717597471022129</v>
       </c>
       <c r="AA25">
-        <v>0.04821487115814809</v>
+        <v>0.07797681770284511</v>
       </c>
       <c r="AB25">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC25">
-        <v>-0.02423934788255677</v>
+        <v>0.01566842916704347</v>
       </c>
       <c r="AD25">
         <v>0</v>
@@ -3724,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>-49.7</v>
+        <v>-0.099</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -3733,19 +3643,22 @@
         <v>0</v>
       </c>
       <c r="AJ25">
-        <v>-0.05779069767441861</v>
+        <v>-0.1549295774647887</v>
       </c>
       <c r="AK25">
-        <v>-0.06561056105610562</v>
+        <v>-0.0899182561307902</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-29.4</v>
-      </c>
-      <c r="AQ25">
-        <v>-1.435374149659864</v>
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="26">
@@ -3756,7 +3669,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Djerriwarrh Investments Limited (ASX:DJW)</t>
+          <t>Insignia Financial Ltd. (ASX:IFL)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3765,46 +3678,49 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.024</v>
+        <v>0.208</v>
       </c>
       <c r="E26">
-        <v>0.0575</v>
+        <v>-0.103</v>
+      </c>
+      <c r="F26">
+        <v>-0.193</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.1493676742751388</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.1493676742751388</v>
       </c>
       <c r="I26">
-        <v>0.9239766081871345</v>
+        <v>0.1099629858112276</v>
       </c>
       <c r="J26">
-        <v>0.8473003404032469</v>
+        <v>0.1099629858112276</v>
       </c>
       <c r="K26">
-        <v>30.7</v>
+        <v>34.2</v>
       </c>
       <c r="L26">
-        <v>0.8976608187134502</v>
+        <v>0.02637260950030846</v>
       </c>
       <c r="M26">
-        <v>17.9</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N26">
-        <v>0.03595099417553726</v>
+        <v>0.07023820732511063</v>
       </c>
       <c r="O26">
-        <v>0.5830618892508143</v>
+        <v>2.181286549707602</v>
       </c>
       <c r="P26">
-        <v>17.9</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>0.03595099417553726</v>
+        <v>0.07023820732511063</v>
       </c>
       <c r="R26">
-        <v>0.5830618892508143</v>
+        <v>2.181286549707602</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3813,67 +3729,73 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>265.9</v>
       </c>
       <c r="V26">
-        <v>0.002008435428800964</v>
+        <v>0.2503530740984841</v>
       </c>
       <c r="W26">
-        <v>0.05327086586847129</v>
+        <v>0.02067339660279273</v>
       </c>
       <c r="X26">
-        <v>0.07535460574292749</v>
+        <v>0.07197491572273379</v>
       </c>
       <c r="Y26">
-        <v>-0.0220837398744562</v>
+        <v>-0.05130151911994106</v>
       </c>
       <c r="Z26">
-        <v>0.05479250143790265</v>
+        <v>0.6318148599269183</v>
       </c>
       <c r="AA26">
-        <v>0.04642570511988031</v>
+        <v>0.0694762484774665</v>
       </c>
       <c r="AB26">
-        <v>0.07072371459120814</v>
+        <v>0.05700841481560828</v>
       </c>
       <c r="AC26">
-        <v>-0.02429800947132783</v>
+        <v>0.01246783366185822</v>
       </c>
       <c r="AD26">
-        <v>61.3</v>
+        <v>623.9</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>61.3</v>
+        <v>623.9</v>
       </c>
       <c r="AG26">
-        <v>60.3</v>
+        <v>358</v>
       </c>
       <c r="AH26">
-        <v>0.109620886981402</v>
+        <v>0.3700474495848161</v>
       </c>
       <c r="AI26">
-        <v>0.1107497741644083</v>
+        <v>0.2869165325362152</v>
       </c>
       <c r="AJ26">
-        <v>0.1080257972053028</v>
+        <v>0.252094922892754</v>
       </c>
       <c r="AK26">
-        <v>0.1091402714932127</v>
+        <v>0.1875720423346956</v>
       </c>
       <c r="AL26">
-        <v>0.978</v>
+        <v>36.1</v>
       </c>
       <c r="AM26">
-        <v>0.978</v>
+        <v>36.1</v>
+      </c>
+      <c r="AN26">
+        <v>3.220960247805885</v>
       </c>
       <c r="AO26">
-        <v>32.31083844580778</v>
+        <v>3.950138504155124</v>
+      </c>
+      <c r="AP26">
+        <v>1.848218895198761</v>
       </c>
       <c r="AQ26">
-        <v>32.31083844580778</v>
+        <v>3.950138504155124</v>
       </c>
     </row>
     <row r="27">
@@ -3884,7 +3806,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Australian Foundation Investment Company Limited (ASX:AFI)</t>
+          <t>Spheria Emerging Companies Limited (ASX:SEC)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3893,10 +3815,10 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.0722</v>
+        <v>0.0219</v>
       </c>
       <c r="E27">
-        <v>0.0803</v>
+        <v>0.0251</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3905,103 +3827,97 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.9513094798967169</v>
+        <v>0.8220000000000001</v>
       </c>
       <c r="J27">
-        <v>0.9170150869272155</v>
+        <v>0.6472997542997544</v>
       </c>
       <c r="K27">
-        <v>248.4</v>
+        <v>6.41</v>
       </c>
       <c r="L27">
-        <v>0.9162670601254149</v>
+        <v>0.641</v>
       </c>
       <c r="M27">
-        <v>152.2</v>
+        <v>3.716</v>
       </c>
       <c r="N27">
-        <v>0.02429369513168396</v>
+        <v>0.04604708798017348</v>
       </c>
       <c r="O27">
-        <v>0.6127214170692431</v>
+        <v>0.5797191887675507</v>
       </c>
       <c r="P27">
-        <v>152.2</v>
+        <v>3.48</v>
       </c>
       <c r="Q27">
-        <v>0.02429369513168396</v>
+        <v>0.04312267657992565</v>
       </c>
       <c r="R27">
-        <v>0.6127214170692431</v>
+        <v>0.5429017160686427</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>0.2360000000000002</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>0.06350914962325085</v>
       </c>
       <c r="U27">
-        <v>99.59999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="V27">
-        <v>0.01589784517158819</v>
+        <v>0.01623296158612144</v>
       </c>
       <c r="W27">
-        <v>0.04383658342892438</v>
+        <v>0.07194163860830528</v>
       </c>
       <c r="X27">
-        <v>0.07248012714899429</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y27">
-        <v>-0.02864354372006991</v>
+        <v>0.009633250072503652</v>
       </c>
       <c r="Z27">
-        <v>0.04846523767810216</v>
+        <v>0.115233924867481</v>
       </c>
       <c r="AA27">
-        <v>0.04444335414233301</v>
+        <v>0.07459089125371679</v>
       </c>
       <c r="AB27">
-        <v>0.07243687700014657</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC27">
-        <v>-0.02799352285781356</v>
+        <v>0.01228250271791516</v>
       </c>
       <c r="AD27">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>-92.70999999999999</v>
+        <v>-1.31</v>
       </c>
       <c r="AH27">
-        <v>0.001098552429969275</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>0.001428485535806472</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>-0.01502035711219013</v>
+        <v>-0.01650081874291473</v>
       </c>
       <c r="AK27">
-        <v>-0.0196266054715699</v>
+        <v>-0.01497313978740428</v>
       </c>
       <c r="AL27">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>0.582</v>
-      </c>
-      <c r="AO27">
-        <v>443.127147766323</v>
-      </c>
-      <c r="AQ27">
-        <v>443.127147766323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4012,7 +3928,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diversified United Investment Limited (ASX:DUI)</t>
+          <t>CVC Limited (ASX:CVC)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4021,46 +3937,46 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0455</v>
+        <v>0.0852</v>
       </c>
       <c r="E28">
-        <v>0.0692</v>
+        <v>-0.1</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.2657004830917875</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.2657004830917875</v>
       </c>
       <c r="I28">
-        <v>0.9705014749262537</v>
+        <v>0.2624798711755233</v>
       </c>
       <c r="J28">
-        <v>0.9705014749262537</v>
+        <v>0.1886574074074074</v>
       </c>
       <c r="K28">
-        <v>31.6</v>
+        <v>8.93</v>
       </c>
       <c r="L28">
-        <v>0.9321533923303835</v>
+        <v>0.1438003220611916</v>
       </c>
       <c r="M28">
-        <v>19.8</v>
+        <v>7.11</v>
       </c>
       <c r="N28">
-        <v>0.02782462057335582</v>
+        <v>0.04133720930232558</v>
       </c>
       <c r="O28">
-        <v>0.6265822784810127</v>
+        <v>0.7961926091825309</v>
       </c>
       <c r="P28">
-        <v>19.8</v>
+        <v>7.11</v>
       </c>
       <c r="Q28">
-        <v>0.02782462057335582</v>
+        <v>0.04133720930232558</v>
       </c>
       <c r="R28">
-        <v>0.6265822784810127</v>
+        <v>0.7961926091825309</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -4069,67 +3985,73 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>3.68</v>
+        <v>34.1</v>
       </c>
       <c r="V28">
-        <v>0.005171444631815627</v>
+        <v>0.1982558139534884</v>
       </c>
       <c r="W28">
-        <v>0.04487998863797756</v>
+        <v>0.07260162601626016</v>
       </c>
       <c r="X28">
-        <v>0.0758740287355241</v>
+        <v>0.06799140478765414</v>
       </c>
       <c r="Y28">
-        <v>-0.03099404009754653</v>
+        <v>0.004610221228606021</v>
       </c>
       <c r="Z28">
-        <v>0.04300229599279489</v>
+        <v>0.3788895668090299</v>
       </c>
       <c r="AA28">
-        <v>0.04173379168622277</v>
+        <v>0.07148032336790726</v>
       </c>
       <c r="AB28">
-        <v>0.07045308853626082</v>
+        <v>0.06015578886549919</v>
       </c>
       <c r="AC28">
-        <v>-0.02871929685003805</v>
+        <v>0.01132453450240807</v>
       </c>
       <c r="AD28">
-        <v>103.3</v>
+        <v>59.4</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>103.3</v>
+        <v>59.4</v>
       </c>
       <c r="AG28">
-        <v>99.61999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="AH28">
-        <v>0.1267640201251687</v>
+        <v>0.2566983578219533</v>
       </c>
       <c r="AI28">
-        <v>0.1439721254355401</v>
+        <v>0.3320290665176076</v>
       </c>
       <c r="AJ28">
-        <v>0.1228026922413155</v>
+        <v>0.1282311201216421</v>
       </c>
       <c r="AK28">
-        <v>0.1395589924630859</v>
+        <v>0.1747237569060773</v>
       </c>
       <c r="AL28">
-        <v>1.53</v>
+        <v>4.32</v>
       </c>
       <c r="AM28">
-        <v>1.53</v>
+        <v>4.32</v>
+      </c>
+      <c r="AN28">
+        <v>3.6</v>
       </c>
       <c r="AO28">
-        <v>21.50326797385621</v>
+        <v>3.773148148148148</v>
+      </c>
+      <c r="AP28">
+        <v>1.533333333333333</v>
       </c>
       <c r="AQ28">
-        <v>21.50326797385621</v>
+        <v>3.773148148148148</v>
       </c>
     </row>
     <row r="29">
@@ -4140,7 +4062,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clime Investment Management Limited (ASX:CIW)</t>
+          <t>Hearts and Minds Investments Limited (ASX:HM1)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4148,122 +4070,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D29">
-        <v>0.0955</v>
-      </c>
-      <c r="E29">
-        <v>-0.481</v>
-      </c>
       <c r="G29">
-        <v>0.1003181336161188</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0.1003181336161188</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>0.06542948038176034</v>
+        <v>0.9648648648648649</v>
       </c>
       <c r="J29">
-        <v>0.03271474019088017</v>
+        <v>0.6915922830725463</v>
       </c>
       <c r="K29">
-        <v>0.067</v>
+        <v>21.8</v>
       </c>
       <c r="L29">
-        <v>0.007104984093319194</v>
+        <v>0.5891891891891892</v>
       </c>
       <c r="M29">
-        <v>1.587</v>
+        <v>19</v>
       </c>
       <c r="N29">
-        <v>0.0669620253164557</v>
+        <v>0.05054535780792764</v>
       </c>
       <c r="O29">
-        <v>23.6865671641791</v>
+        <v>0.8715596330275229</v>
       </c>
       <c r="P29">
-        <v>1.26</v>
+        <v>19</v>
       </c>
       <c r="Q29">
-        <v>0.05316455696202532</v>
+        <v>0.05054535780792764</v>
       </c>
       <c r="R29">
-        <v>18.80597014925373</v>
+        <v>0.8715596330275229</v>
       </c>
       <c r="S29">
-        <v>0.327</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>0.2060491493383743</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>5.61</v>
+        <v>39.4</v>
       </c>
       <c r="V29">
-        <v>0.2367088607594937</v>
+        <v>0.1048151104017026</v>
       </c>
       <c r="W29">
-        <v>0.003872832369942197</v>
+        <v>0.04935476567806204</v>
       </c>
       <c r="X29">
-        <v>0.07343729143909641</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y29">
-        <v>-0.06956445906915422</v>
+        <v>-0.01295362285773959</v>
       </c>
       <c r="Z29">
-        <v>1.234293193717277</v>
+        <v>0.1034675615212528</v>
       </c>
       <c r="AA29">
-        <v>0.04037958115183245</v>
+        <v>0.07155736709643237</v>
       </c>
       <c r="AB29">
-        <v>0.07182184766926911</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC29">
-        <v>-0.03144226651743665</v>
+        <v>0.009248978560630741</v>
       </c>
       <c r="AD29">
-        <v>0.989</v>
+        <v>0</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0.989</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>-4.621</v>
+        <v>-39.4</v>
       </c>
       <c r="AH29">
-        <v>0.04005832557009194</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>0.05378215237370167</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>-0.2422034697835316</v>
+        <v>-0.1170876671619614</v>
       </c>
       <c r="AK29">
-        <v>-0.3616088895844746</v>
+        <v>-0.09605070697220866</v>
       </c>
       <c r="AL29">
-        <v>0.06</v>
+        <v>0.001</v>
       </c>
       <c r="AM29">
-        <v>0.06</v>
-      </c>
-      <c r="AN29">
-        <v>1.045454545454545</v>
+        <v>0.001</v>
       </c>
       <c r="AO29">
-        <v>10.28333333333333</v>
-      </c>
-      <c r="AP29">
-        <v>-4.88477801268499</v>
+        <v>35700</v>
       </c>
       <c r="AQ29">
-        <v>10.28333333333333</v>
+        <v>35700</v>
       </c>
     </row>
     <row r="30">
@@ -4274,7 +4184,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carlton Investments Limited (ASX:CIN)</t>
+          <t>Bailador Technology Investments Limited (ASX:BTI)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4283,10 +4193,10 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.0283</v>
+        <v>0.135</v>
       </c>
       <c r="E30">
-        <v>-0.0318</v>
+        <v>0.0819</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4295,34 +4205,34 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0.9715447154471544</v>
+        <v>0.5392523364485982</v>
       </c>
       <c r="J30">
-        <v>0.9442276422764226</v>
+        <v>0.347904733192644</v>
       </c>
       <c r="K30">
-        <v>23.3</v>
+        <v>3.6</v>
       </c>
       <c r="L30">
-        <v>0.9471544715447154</v>
+        <v>0.3364485981308412</v>
       </c>
       <c r="M30">
-        <v>14.8</v>
+        <v>6.72</v>
       </c>
       <c r="N30">
-        <v>0.02765321375186846</v>
+        <v>0.05287175452399685</v>
       </c>
       <c r="O30">
-        <v>0.6351931330472103</v>
+        <v>1.866666666666666</v>
       </c>
       <c r="P30">
-        <v>14.8</v>
+        <v>6.72</v>
       </c>
       <c r="Q30">
-        <v>0.02765321375186846</v>
+        <v>0.05287175452399685</v>
       </c>
       <c r="R30">
-        <v>0.6351931330472103</v>
+        <v>1.866666666666666</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4331,67 +4241,61 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>8.6</v>
+        <v>38.4</v>
       </c>
       <c r="V30">
-        <v>0.01606875934230194</v>
+        <v>0.3021243115656963</v>
       </c>
       <c r="W30">
-        <v>0.03669291338582677</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="X30">
-        <v>0.07245923699040488</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y30">
-        <v>-0.03576632360457811</v>
+        <v>-0.03905257458231326</v>
       </c>
       <c r="Z30">
-        <v>0.03953560132685335</v>
+        <v>0.1921005385996409</v>
       </c>
       <c r="AA30">
-        <v>0.03733060762683535</v>
+        <v>0.06683268662767125</v>
       </c>
       <c r="AB30">
-        <v>0.07245085721140246</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC30">
-        <v>-0.03512024958456711</v>
+        <v>0.004524298091869619</v>
       </c>
       <c r="AD30">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>-8.485999999999999</v>
+        <v>-38.4</v>
       </c>
       <c r="AH30">
-        <v>0.000212959123056748</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>0.0002019078520901005</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>-0.01611121025831855</v>
+        <v>-0.4329199549041714</v>
       </c>
       <c r="AK30">
-        <v>-0.01526220562791584</v>
+        <v>-0.3555555555555556</v>
       </c>
       <c r="AL30">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>0.008</v>
-      </c>
-      <c r="AO30">
-        <v>2987.5</v>
-      </c>
-      <c r="AQ30">
-        <v>2987.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -4402,7 +4306,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pinnacle Investment Management Group Limited (ASX:PNI)</t>
+          <t>Pengana Capital Group Limited (ASX:PCG)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4411,124 +4315,118 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.332</v>
-      </c>
-      <c r="E31">
-        <v>0.423</v>
-      </c>
-      <c r="F31">
-        <v>0.13</v>
+        <v>-0.0663</v>
       </c>
       <c r="G31">
-        <v>0.2280757097791798</v>
+        <v>0.1427450980392157</v>
       </c>
       <c r="H31">
-        <v>0.2280757097791798</v>
+        <v>0.1427450980392157</v>
       </c>
       <c r="I31">
-        <v>0.2066246056782334</v>
+        <v>0.05137254901960785</v>
       </c>
       <c r="J31">
-        <v>0.2066246056782334</v>
+        <v>0.03299698340874811</v>
       </c>
       <c r="K31">
-        <v>52.6</v>
+        <v>-0.325</v>
       </c>
       <c r="L31">
-        <v>1.659305993690852</v>
+        <v>-0.01274509803921569</v>
       </c>
       <c r="M31">
-        <v>45.4</v>
+        <v>5.888</v>
       </c>
       <c r="N31">
-        <v>0.03912443984832816</v>
+        <v>0.09764510779436153</v>
       </c>
       <c r="O31">
-        <v>0.8631178707224334</v>
+        <v>-18.11692307692308</v>
       </c>
       <c r="P31">
-        <v>45.4</v>
+        <v>5.65</v>
       </c>
       <c r="Q31">
-        <v>0.03912443984832816</v>
+        <v>0.09369817578772803</v>
       </c>
       <c r="R31">
-        <v>0.8631178707224334</v>
+        <v>-17.38461538461539</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>0.2379999999999995</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>0.04042119565217384</v>
       </c>
       <c r="U31">
-        <v>26.4</v>
+        <v>9.44</v>
       </c>
       <c r="V31">
-        <v>0.02275077559462254</v>
+        <v>0.1565505804311774</v>
       </c>
       <c r="W31">
-        <v>0.2875888463641334</v>
+        <v>-0.005371900826446281</v>
       </c>
       <c r="X31">
-        <v>0.07415549143722996</v>
+        <v>0.06296334861441102</v>
       </c>
       <c r="Y31">
-        <v>0.2134333549269034</v>
+        <v>-0.06833524944085731</v>
       </c>
       <c r="Z31">
-        <v>0.1686170212765957</v>
+        <v>1.83982683982684</v>
       </c>
       <c r="AA31">
-        <v>0.03484042553191489</v>
+        <v>0.0607087357087357</v>
       </c>
       <c r="AB31">
-        <v>0.07175400439138535</v>
+        <v>0.06176016206457711</v>
       </c>
       <c r="AC31">
-        <v>-0.03691357885947046</v>
+        <v>-0.001051426355841413</v>
       </c>
       <c r="AD31">
-        <v>83.8</v>
+        <v>2.4</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>83.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG31">
-        <v>57.4</v>
+        <v>-7.039999999999999</v>
       </c>
       <c r="AH31">
-        <v>0.06735251567272142</v>
+        <v>0.03827751196172249</v>
       </c>
       <c r="AI31">
-        <v>0.2321972845663619</v>
+        <v>0.04436229205175601</v>
       </c>
       <c r="AJ31">
-        <v>0.04713417638364262</v>
+        <v>-0.1321817499061209</v>
       </c>
       <c r="AK31">
-        <v>0.1715994020926756</v>
+        <v>-0.1576354679802955</v>
       </c>
       <c r="AL31">
-        <v>1.64</v>
+        <v>0.126</v>
       </c>
       <c r="AM31">
-        <v>1.64</v>
+        <v>0.126</v>
       </c>
       <c r="AN31">
-        <v>11.59059474412171</v>
+        <v>0.6593406593406593</v>
       </c>
       <c r="AO31">
-        <v>3.99390243902439</v>
+        <v>10.3968253968254</v>
       </c>
       <c r="AP31">
-        <v>7.939142461964038</v>
+        <v>-1.934065934065934</v>
       </c>
       <c r="AQ31">
-        <v>3.99390243902439</v>
+        <v>10.3968253968254</v>
       </c>
     </row>
     <row r="32">
@@ -4539,7 +4437,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amcil Limited (ASX:AMH)</t>
+          <t>Orion Equities Limited (ASX:OEQ)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4548,79 +4446,73 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.06860000000000001</v>
-      </c>
-      <c r="E32">
-        <v>0.08560000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.7209302325581396</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.7209302325581396</v>
       </c>
       <c r="I32">
-        <v>0.8094575799721836</v>
+        <v>0.7209302325581396</v>
       </c>
       <c r="J32">
-        <v>0.7888685892620897</v>
+        <v>0.7209302325581396</v>
       </c>
       <c r="K32">
-        <v>5.59</v>
+        <v>-0.576</v>
       </c>
       <c r="L32">
-        <v>0.7774687065368567</v>
+        <v>-3.348837209302326</v>
       </c>
       <c r="M32">
-        <v>11.2</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.0516366989396035</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>2.003577817531306</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>11.2</v>
+        <v>-0</v>
       </c>
       <c r="Q32">
-        <v>0.0516366989396035</v>
+        <v>-0</v>
       </c>
       <c r="R32">
-        <v>2.003577817531306</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
-        <v>15</v>
+        <v>0.091</v>
       </c>
       <c r="V32">
-        <v>0.06915629322268327</v>
+        <v>0.1263888888888889</v>
       </c>
       <c r="W32">
-        <v>0.02223548130469371</v>
+        <v>-0.2679069767441861</v>
       </c>
       <c r="X32">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y32">
-        <v>-0.05021873773601114</v>
+        <v>-0.3302153652799877</v>
       </c>
       <c r="Z32">
-        <v>0.02956414473684211</v>
+        <v>0.08037383177570093</v>
       </c>
       <c r="AA32">
-        <v>0.02332222515129287</v>
+        <v>0.05794392523364485</v>
       </c>
       <c r="AB32">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC32">
-        <v>-0.04913199388941199</v>
+        <v>-0.004364463302156778</v>
       </c>
       <c r="AD32">
         <v>0</v>
@@ -4632,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>-15</v>
+        <v>-0.091</v>
       </c>
       <c r="AH32">
         <v>0</v>
@@ -4641,22 +4533,22 @@
         <v>0</v>
       </c>
       <c r="AJ32">
-        <v>-0.07429420505200594</v>
+        <v>-0.1446740858505564</v>
       </c>
       <c r="AK32">
-        <v>-0.07796257796257797</v>
+        <v>-0.06458481192334989</v>
       </c>
       <c r="AL32">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>0.079</v>
-      </c>
-      <c r="AO32">
-        <v>73.67088607594937</v>
-      </c>
-      <c r="AQ32">
-        <v>73.67088607594937</v>
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0</v>
+      </c>
+      <c r="AP32">
+        <v>-0.7338709677419355</v>
       </c>
     </row>
     <row r="33">
@@ -4667,7 +4559,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mirrabooka Investments Limited (ASX:MIR)</t>
+          <t>BKI Investment Company Limited (ASX:BKI)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4676,10 +4568,10 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.00016</v>
+        <v>0.0862</v>
       </c>
       <c r="E33">
-        <v>-0.0234</v>
+        <v>0.0926</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4688,34 +4580,34 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0.7224606580829757</v>
+        <v>0.9669421487603306</v>
       </c>
       <c r="J33">
-        <v>0.6716853106273448</v>
+        <v>0.8991982976196368</v>
       </c>
       <c r="K33">
-        <v>4.63</v>
+        <v>46.6</v>
       </c>
       <c r="L33">
-        <v>0.6623748211731044</v>
+        <v>0.9628099173553719</v>
       </c>
       <c r="M33">
-        <v>9.76</v>
+        <v>38.4</v>
       </c>
       <c r="N33">
-        <v>0.026550598476605</v>
+        <v>0.03964484823456535</v>
       </c>
       <c r="O33">
-        <v>2.107991360691145</v>
+        <v>0.8240343347639485</v>
       </c>
       <c r="P33">
-        <v>9.76</v>
+        <v>38.4</v>
       </c>
       <c r="Q33">
-        <v>0.026550598476605</v>
+        <v>0.03964484823456535</v>
       </c>
       <c r="R33">
-        <v>2.107991360691145</v>
+        <v>0.8240343347639485</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -4724,31 +4616,31 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>18.9</v>
+        <v>70</v>
       </c>
       <c r="V33">
-        <v>0.05141458106637649</v>
+        <v>0.07226925459425976</v>
       </c>
       <c r="W33">
-        <v>0.01192684183410613</v>
+        <v>0.05773042616451932</v>
       </c>
       <c r="X33">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y33">
-        <v>-0.06052737720659872</v>
+        <v>-0.004577962371282308</v>
       </c>
       <c r="Z33">
-        <v>0.01903076504219984</v>
+        <v>0.06389438943894389</v>
       </c>
       <c r="AA33">
-        <v>0.01278268532884601</v>
+        <v>0.05745372621094445</v>
       </c>
       <c r="AB33">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC33">
-        <v>-0.05967153371185884</v>
+        <v>-0.004854662324857185</v>
       </c>
       <c r="AD33">
         <v>0</v>
@@ -4760,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>-18.9</v>
+        <v>-70</v>
       </c>
       <c r="AH33">
         <v>0</v>
@@ -4769,22 +4661,19 @@
         <v>0</v>
       </c>
       <c r="AJ33">
-        <v>-0.05420131918554631</v>
+        <v>-0.07789895392833296</v>
       </c>
       <c r="AK33">
-        <v>-0.06338028169014083</v>
+        <v>-0.08795074758135445</v>
       </c>
       <c r="AL33">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>0.065</v>
-      </c>
-      <c r="AO33">
-        <v>77.69230769230769</v>
+        <v>-3.33</v>
       </c>
       <c r="AQ33">
-        <v>77.69230769230769</v>
+        <v>-14.05405405405405</v>
       </c>
     </row>
     <row r="34">
@@ -4795,7 +4684,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA Financial Group Limited (ASX:MAF)</t>
+          <t>Djerriwarrh Investments Limited (ASX:DJW)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4804,10 +4693,10 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.412</v>
+        <v>0.0185</v>
       </c>
       <c r="E34">
-        <v>0.213</v>
+        <v>0.0443</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4816,97 +4705,103 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>0.9198813056379821</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>0.8225192980309379</v>
       </c>
       <c r="K34">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="L34">
-        <v>0.07968608511922728</v>
+        <v>0.7715133531157269</v>
       </c>
       <c r="M34">
-        <v>25.72</v>
+        <v>20.8</v>
       </c>
       <c r="N34">
-        <v>0.05145029005801161</v>
+        <v>0.03827046918123275</v>
       </c>
       <c r="O34">
-        <v>0.9742424242424242</v>
+        <v>0.8</v>
       </c>
       <c r="P34">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="Q34">
-        <v>0.03880776155231046</v>
+        <v>0.03827046918123275</v>
       </c>
       <c r="R34">
-        <v>0.7348484848484849</v>
+        <v>0.8</v>
       </c>
       <c r="S34">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>0.2457231726283048</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>82.8</v>
+        <v>0.525</v>
       </c>
       <c r="V34">
-        <v>0.1656331266253251</v>
+        <v>0.0009659613615455382</v>
       </c>
       <c r="W34">
-        <v>0.1413276231263383</v>
+        <v>0.05282405526208858</v>
       </c>
       <c r="X34">
-        <v>0.09876900427501314</v>
+        <v>0.06419165484095123</v>
       </c>
       <c r="Y34">
-        <v>0.04255861885132517</v>
+        <v>-0.01136759957886264</v>
       </c>
       <c r="Z34">
-        <v>0.9990952955367914</v>
+        <v>0.06099547511312218</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>0.0501699553731088</v>
       </c>
       <c r="AB34">
-        <v>0.06696874727116986</v>
+        <v>0.06083760380725936</v>
       </c>
       <c r="AC34">
-        <v>-0.06696874727116986</v>
+        <v>-0.01066764843415056</v>
       </c>
       <c r="AD34">
-        <v>558.4</v>
+        <v>62.2</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>558.4</v>
+        <v>62.2</v>
       </c>
       <c r="AG34">
-        <v>475.6</v>
+        <v>61.675</v>
       </c>
       <c r="AH34">
-        <v>0.5276386657847492</v>
+        <v>0.1026911012052171</v>
       </c>
       <c r="AI34">
-        <v>0.6743961352657004</v>
+        <v>0.1017004578155657</v>
       </c>
       <c r="AJ34">
-        <v>0.4875448487954895</v>
+        <v>0.1019126698888751</v>
       </c>
       <c r="AK34">
-        <v>0.6382179280730005</v>
+        <v>0.1009286912408461</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AM34">
-        <v>0</v>
+        <v>2.36</v>
+      </c>
+      <c r="AO34">
+        <v>13.13559322033898</v>
+      </c>
+      <c r="AQ34">
+        <v>13.13559322033898</v>
       </c>
     </row>
     <row r="35">
@@ -4917,7 +4812,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ECP Emerging Growth Limited (ASX:ECP)</t>
+          <t>Australian United Investment Company Limited (ASX:AUI)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4926,43 +4821,46 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.004759999999999999</v>
+        <v>0.0317</v>
+      </c>
+      <c r="E35">
+        <v>0.0337</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.9764705882352941</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.9764705882352941</v>
       </c>
       <c r="I35">
-        <v>-0.4539007092198582</v>
+        <v>0.9764705882352941</v>
       </c>
       <c r="J35">
-        <v>-0.4539007092198582</v>
+        <v>0.9622720395244712</v>
       </c>
       <c r="K35">
-        <v>-7.07</v>
+        <v>37.5</v>
       </c>
       <c r="L35">
-        <v>-25.07092198581561</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="M35">
-        <v>0.593</v>
+        <v>28.9</v>
       </c>
       <c r="N35">
-        <v>0.04235714285714286</v>
+        <v>0.03351890512642078</v>
       </c>
       <c r="O35">
-        <v>-0.08387553041018386</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="P35">
-        <v>0.593</v>
+        <v>28.9</v>
       </c>
       <c r="Q35">
-        <v>0.04235714285714286</v>
+        <v>0.03351890512642078</v>
       </c>
       <c r="R35">
-        <v>-0.08387553041018386</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4971,67 +4869,73 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="V35">
-        <v>0.1428571428571428</v>
+        <v>0.003966597077244258</v>
       </c>
       <c r="W35">
-        <v>-0.3087336244541485</v>
+        <v>0.05225752508361204</v>
       </c>
       <c r="X35">
-        <v>0.08260096608147736</v>
+        <v>0.06340010261255122</v>
       </c>
       <c r="Y35">
-        <v>-0.3913345905356259</v>
+        <v>-0.01114257752893918</v>
       </c>
       <c r="Z35">
-        <v>0.014050822122571</v>
+        <v>0.05130000241411776</v>
       </c>
       <c r="AA35">
-        <v>-0.006377678126557051</v>
+        <v>0.04936455795064339</v>
       </c>
       <c r="AB35">
-        <v>0.06770178857417289</v>
+        <v>0.06141732672671488</v>
       </c>
       <c r="AC35">
-        <v>-0.07407946670072994</v>
+        <v>-0.01205276877607149</v>
       </c>
       <c r="AD35">
-        <v>6.03</v>
+        <v>57.2</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>6.03</v>
+        <v>57.2</v>
       </c>
       <c r="AG35">
-        <v>4.03</v>
+        <v>53.78</v>
       </c>
       <c r="AH35">
-        <v>0.3010484273589615</v>
+        <v>0.06221448770937568</v>
       </c>
       <c r="AI35">
-        <v>0.2922927775084828</v>
+        <v>0.07034805067027426</v>
       </c>
       <c r="AJ35">
-        <v>0.223516361619523</v>
+        <v>0.05871307233782397</v>
       </c>
       <c r="AK35">
-        <v>0.2163177670424047</v>
+        <v>0.06642130224286139</v>
       </c>
       <c r="AL35">
-        <v>0.146</v>
+        <v>3.41</v>
       </c>
       <c r="AM35">
-        <v>0.146</v>
+        <v>3.41</v>
+      </c>
+      <c r="AN35">
+        <v>1.378313253012048</v>
       </c>
       <c r="AO35">
-        <v>-0.8767123287671234</v>
+        <v>12.17008797653959</v>
+      </c>
+      <c r="AP35">
+        <v>1.295903614457831</v>
       </c>
       <c r="AQ35">
-        <v>-0.8767123287671234</v>
+        <v>12.17008797653959</v>
       </c>
     </row>
     <row r="36">
@@ -5042,7 +4946,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Orion Equities Limited (ASX:OEQ)</t>
+          <t>Diversified United Investment Limited (ASX:DUI)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5051,109 +4955,115 @@
         </is>
       </c>
       <c r="D36">
-        <v>-0.103</v>
+        <v>0.0507</v>
+      </c>
+      <c r="E36">
+        <v>0.04389999999999999</v>
       </c>
       <c r="G36">
-        <v>-1.258064516129032</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>-1.258064516129032</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>-1.258064516129032</v>
+        <v>0.9688385269121814</v>
       </c>
       <c r="J36">
-        <v>-1.258064516129032</v>
+        <v>0.9049904797287884</v>
       </c>
       <c r="K36">
-        <v>-2.71</v>
+        <v>28.5</v>
       </c>
       <c r="L36">
-        <v>-87.41935483870968</v>
+        <v>0.8073654390934845</v>
       </c>
       <c r="M36">
-        <v>-0</v>
+        <v>20</v>
       </c>
       <c r="N36">
-        <v>-0</v>
+        <v>0.02680605816914623</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="P36">
-        <v>-0</v>
+        <v>20</v>
       </c>
       <c r="Q36">
-        <v>-0</v>
+        <v>0.02680605816914623</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
       <c r="U36">
-        <v>0.01</v>
+        <v>2.74</v>
       </c>
       <c r="V36">
-        <v>0.008</v>
+        <v>0.003672429969173033</v>
       </c>
       <c r="W36">
-        <v>-0.5122873345935728</v>
+        <v>0.04640182351025724</v>
       </c>
       <c r="X36">
-        <v>0.07245421904070486</v>
+        <v>0.06362953413465723</v>
       </c>
       <c r="Y36">
-        <v>-0.5847415536342776</v>
+        <v>-0.01722771062439999</v>
       </c>
       <c r="Z36">
-        <v>0.006026438569206843</v>
+        <v>0.04945224286234624</v>
       </c>
       <c r="AA36">
-        <v>-0.007581648522550544</v>
+        <v>0.04475380899165928</v>
       </c>
       <c r="AB36">
-        <v>0.07245421904070486</v>
+        <v>0.06124398065492278</v>
       </c>
       <c r="AC36">
-        <v>-0.0800358675632554</v>
+        <v>-0.0164901716632635</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>59.9</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>59.9</v>
       </c>
       <c r="AG36">
-        <v>-0.01</v>
+        <v>57.16</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>0.07431761786600496</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>0.0843661971830986</v>
       </c>
       <c r="AJ36">
-        <v>-0.008064516129032258</v>
+        <v>0.07116002290665538</v>
       </c>
       <c r="AK36">
-        <v>-0.004672897196261682</v>
+        <v>0.08081893504510364</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AM36">
-        <v>0</v>
-      </c>
-      <c r="AN36">
-        <v>-0</v>
-      </c>
-      <c r="AP36">
-        <v>0.2564102564102564</v>
+        <v>3.72</v>
+      </c>
+      <c r="AO36">
+        <v>9.193548387096774</v>
+      </c>
+      <c r="AQ36">
+        <v>9.193548387096774</v>
       </c>
     </row>
     <row r="37">
@@ -5164,7 +5074,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Katana Capital Limited (ASX:KAT)</t>
+          <t>Navigator Global Investments Limited (ASX:NGI)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5173,106 +5083,118 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.231</v>
+        <v>0.0008100000000000001</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.1940119760479042</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.1940119760479042</v>
       </c>
       <c r="I37">
-        <v>-0.8559322033898306</v>
+        <v>0.162874251497006</v>
       </c>
       <c r="J37">
-        <v>-0.8559322033898306</v>
+        <v>0.1314469243331519</v>
       </c>
       <c r="K37">
-        <v>-0.194</v>
+        <v>35.5</v>
       </c>
       <c r="L37">
-        <v>-0.4110169491525424</v>
+        <v>0.4251497005988024</v>
       </c>
       <c r="M37">
-        <v>1.688</v>
+        <v>9</v>
       </c>
       <c r="N37">
-        <v>0.06725099601593625</v>
+        <v>0.04265402843601896</v>
       </c>
       <c r="O37">
-        <v>-8.701030927835051</v>
+        <v>0.2535211267605634</v>
       </c>
       <c r="P37">
-        <v>0.428</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>0.01705179282868526</v>
+        <v>0.04265402843601896</v>
       </c>
       <c r="R37">
-        <v>-2.206185567010309</v>
+        <v>0.2535211267605634</v>
       </c>
       <c r="S37">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>0.7464454976303317</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>4.92</v>
+        <v>67.8</v>
       </c>
       <c r="V37">
-        <v>0.1960159362549801</v>
+        <v>0.3213270142180095</v>
       </c>
       <c r="W37">
-        <v>-0.006258064516129033</v>
+        <v>0.08585247883917775</v>
       </c>
       <c r="X37">
-        <v>0.07245421904070486</v>
+        <v>0.06527200528960411</v>
       </c>
       <c r="Y37">
-        <v>-0.07871228355683389</v>
+        <v>0.02058047354957364</v>
       </c>
       <c r="Z37">
-        <v>0.01769778777652793</v>
+        <v>0.3316123907863384</v>
       </c>
       <c r="AA37">
-        <v>-0.01514810648668916</v>
+        <v>0.0435894288396274</v>
       </c>
       <c r="AB37">
-        <v>0.07245421904070486</v>
+        <v>0.06012263821729505</v>
       </c>
       <c r="AC37">
-        <v>-0.08760232552739403</v>
+        <v>-0.01653320937766765</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG37">
-        <v>-4.92</v>
+        <v>-29.8</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>0.1526104417670683</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>0.08269858541893363</v>
       </c>
       <c r="AJ37">
-        <v>-0.2438057482656095</v>
+        <v>-0.1644591611479029</v>
       </c>
       <c r="AK37">
-        <v>-0.2269372693726937</v>
+        <v>-0.07607863160582078</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>-65.34999999999999</v>
+      </c>
+      <c r="AN37">
+        <v>2.345679012345679</v>
+      </c>
+      <c r="AO37">
+        <v>6.044444444444444</v>
+      </c>
+      <c r="AP37">
+        <v>-1.839506172839506</v>
+      </c>
+      <c r="AQ37">
+        <v>-0.2081101759755165</v>
       </c>
     </row>
     <row r="38">
@@ -5283,7 +5205,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teaminvest Private Group Limited (ASX:TIP)</t>
+          <t>Carlton Investments Ltd. (ASX:CIN)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5292,43 +5214,46 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.0433</v>
+        <v>-0.0197</v>
+      </c>
+      <c r="E38">
+        <v>-0.0213</v>
       </c>
       <c r="G38">
-        <v>0.01887366818873668</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>0.01887366818873668</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>-0.01537290715372907</v>
+        <v>0.9731800766283524</v>
       </c>
       <c r="J38">
-        <v>-0.01537290715372907</v>
+        <v>0.9538697318007662</v>
       </c>
       <c r="K38">
-        <v>-12.2</v>
+        <v>24.9</v>
       </c>
       <c r="L38">
-        <v>-0.1856925418569254</v>
+        <v>0.9540229885057471</v>
       </c>
       <c r="M38">
-        <v>0.5267999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="N38">
-        <v>0.0145524861878453</v>
+        <v>0.02770497940846125</v>
       </c>
       <c r="O38">
-        <v>-0.04318032786885245</v>
+        <v>0.5943775100401607</v>
       </c>
       <c r="P38">
-        <v>0.5267999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="Q38">
-        <v>0.0145524861878453</v>
+        <v>0.02770497940846125</v>
       </c>
       <c r="R38">
-        <v>-0.04318032786885245</v>
+        <v>0.5943775100401607</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -5337,73 +5262,67 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>4.43</v>
+        <v>16</v>
       </c>
       <c r="V38">
-        <v>0.1223756906077348</v>
+        <v>0.02995132909022838</v>
       </c>
       <c r="W38">
-        <v>-0.1650879566982408</v>
+        <v>0.04410983170947741</v>
       </c>
       <c r="X38">
-        <v>0.0743414583957499</v>
+        <v>0.06231177705305595</v>
       </c>
       <c r="Y38">
-        <v>-0.2394294150939907</v>
+        <v>-0.01820194534357854</v>
       </c>
       <c r="Z38">
-        <v>1.7543391188251</v>
+        <v>0.04782725017133516</v>
       </c>
       <c r="AA38">
-        <v>-0.02696929238985313</v>
+        <v>0.04562096629369962</v>
       </c>
       <c r="AB38">
-        <v>0.07188042951217766</v>
+        <v>0.06230543993700752</v>
       </c>
       <c r="AC38">
-        <v>-0.09884972190203078</v>
+        <v>-0.01668447364330791</v>
       </c>
       <c r="AD38">
-        <v>2.9</v>
+        <v>0.11</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>2.9</v>
+        <v>0.11</v>
       </c>
       <c r="AG38">
-        <v>-1.53</v>
+        <v>-15.89</v>
       </c>
       <c r="AH38">
-        <v>0.07416879795396419</v>
+        <v>0.0002058729950777638</v>
       </c>
       <c r="AI38">
-        <v>0.04906937394247039</v>
+        <v>0.0002000691147851076</v>
       </c>
       <c r="AJ38">
-        <v>-0.04413037207960772</v>
+        <v>-0.03065732862572591</v>
       </c>
       <c r="AK38">
-        <v>-0.02798609840863361</v>
+        <v>-0.02976714561360784</v>
       </c>
       <c r="AL38">
-        <v>0.228</v>
+        <v>0.008</v>
       </c>
       <c r="AM38">
-        <v>0.228</v>
-      </c>
-      <c r="AN38">
-        <v>2.338709677419355</v>
+        <v>0.008</v>
       </c>
       <c r="AO38">
-        <v>-4.429824561403509</v>
-      </c>
-      <c r="AP38">
-        <v>-1.233870967741935</v>
+        <v>3175</v>
       </c>
       <c r="AQ38">
-        <v>-4.429824561403509</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="39">
@@ -5414,7 +5333,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NGE Capital Limited (ASX:NGE)</t>
+          <t>Argo Investments Limited (ASX:ARG)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5423,103 +5342,103 @@
         </is>
       </c>
       <c r="D39">
-        <v>-0.306</v>
+        <v>0.0337</v>
       </c>
       <c r="E39">
-        <v>-0.09609999999999999</v>
+        <v>0.0442</v>
       </c>
       <c r="G39">
-        <v>-1.058947368421053</v>
+        <v>0.9641135511515802</v>
       </c>
       <c r="H39">
-        <v>-1.058947368421053</v>
+        <v>0.9641135511515802</v>
       </c>
       <c r="I39">
-        <v>-1.063157894736842</v>
+        <v>0.9625066952329941</v>
       </c>
       <c r="J39">
-        <v>-1.063157894736842</v>
+        <v>0.892874348374168</v>
       </c>
       <c r="K39">
-        <v>2.05</v>
+        <v>180.8</v>
       </c>
       <c r="L39">
-        <v>4.315789473684211</v>
+        <v>0.9683985002678095</v>
       </c>
       <c r="M39">
-        <v>0.104</v>
+        <v>134.9</v>
       </c>
       <c r="N39">
-        <v>0.005652173913043478</v>
+        <v>0.02914929017480931</v>
       </c>
       <c r="O39">
-        <v>0.05073170731707317</v>
+        <v>0.7461283185840708</v>
       </c>
       <c r="P39">
-        <v>-0</v>
+        <v>134.9</v>
       </c>
       <c r="Q39">
-        <v>-0</v>
+        <v>0.02914929017480931</v>
       </c>
       <c r="R39">
-        <v>-0</v>
+        <v>0.7461283185840708</v>
       </c>
       <c r="S39">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>8.390000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="V39">
-        <v>0.4559782608695653</v>
+        <v>0.01802113269517492</v>
       </c>
       <c r="W39">
-        <v>0.08266129032258064</v>
+        <v>0.04655474302193841</v>
       </c>
       <c r="X39">
-        <v>0.07249518939431962</v>
+        <v>0.0623093734915131</v>
       </c>
       <c r="Y39">
-        <v>0.01016610092826102</v>
+        <v>-0.01575463046957469</v>
       </c>
       <c r="Z39">
-        <v>0.03957014328557147</v>
+        <v>0.04924412769711829</v>
       </c>
       <c r="AA39">
-        <v>-0.04206931022992336</v>
+        <v>0.04396881842881881</v>
       </c>
       <c r="AB39">
-        <v>0.07242681232939892</v>
+        <v>0.0623075313280096</v>
       </c>
       <c r="AC39">
-        <v>-0.1144961225593223</v>
+        <v>-0.01833871289919079</v>
       </c>
       <c r="AD39">
-        <v>0.032</v>
+        <v>0.277</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>0.032</v>
+        <v>0.277</v>
       </c>
       <c r="AG39">
-        <v>-8.358000000000001</v>
+        <v>-83.123</v>
       </c>
       <c r="AH39">
-        <v>0.001736111111111111</v>
+        <v>5.985077925930664e-05</v>
       </c>
       <c r="AI39">
-        <v>0.001288659793814433</v>
+        <v>6.938396308672971e-05</v>
       </c>
       <c r="AJ39">
-        <v>-0.8323043218482377</v>
+        <v>-0.01828978627554223</v>
       </c>
       <c r="AK39">
-        <v>-0.5083323196691401</v>
+        <v>-0.02126518690662306</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -5528,10 +5447,10 @@
         <v>0</v>
       </c>
       <c r="AN39">
-        <v>-0.05818181818181818</v>
+        <v>0.001538888888888889</v>
       </c>
       <c r="AP39">
-        <v>15.19636363636364</v>
+        <v>-0.4617944444444445</v>
       </c>
     </row>
     <row r="40">
@@ -5542,7 +5461,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Plato Income Maximiser Limited (ASX:PL8)</t>
+          <t>Australian Foundation Investment Company Limited (ASX:AFI)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5550,26 +5469,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D40">
+        <v>0.0256</v>
+      </c>
+      <c r="E40">
+        <v>0.0214</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0.948905109489051</v>
+      </c>
+      <c r="J40">
+        <v>0.8898410476989557</v>
+      </c>
       <c r="K40">
-        <v>-8.859999999999999</v>
+        <v>206.2</v>
+      </c>
+      <c r="L40">
+        <v>0.8853585229712322</v>
       </c>
       <c r="M40">
-        <v>21.1</v>
+        <v>153.4</v>
       </c>
       <c r="N40">
-        <v>0.04146197681273335</v>
+        <v>0.02423189321538583</v>
       </c>
       <c r="O40">
-        <v>-2.381489841986456</v>
+        <v>0.7439379243452959</v>
       </c>
       <c r="P40">
-        <v>21.1</v>
+        <v>153.4</v>
       </c>
       <c r="Q40">
-        <v>0.04146197681273335</v>
+        <v>0.02423189321538583</v>
       </c>
       <c r="R40">
-        <v>-2.381489841986456</v>
+        <v>0.7439379243452959</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -5578,61 +5518,67 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>0.143</v>
+        <v>110.1</v>
       </c>
       <c r="V40">
-        <v>0.000280998231479662</v>
+        <v>0.01739199115393729</v>
       </c>
       <c r="W40">
-        <v>-0.02437414030261348</v>
+        <v>0.04281917102749398</v>
       </c>
       <c r="X40">
-        <v>0.07245421904070486</v>
+        <v>0.06232570092934936</v>
       </c>
       <c r="Y40">
-        <v>-0.09682835934331833</v>
+        <v>-0.01950652990185538</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>0.04931302655789146</v>
       </c>
       <c r="AA40">
-        <v>-0.08653689806559717</v>
+        <v>0.04388075521748056</v>
       </c>
       <c r="AB40">
-        <v>0.07245421904070486</v>
+        <v>0.06229333647868227</v>
       </c>
       <c r="AC40">
-        <v>-0.158991117106302</v>
+        <v>-0.01841258126120171</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AG40">
-        <v>-0.143</v>
+        <v>-103.44</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>0.001050943955967657</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>0.001322304860760901</v>
       </c>
       <c r="AJ40">
-        <v>-0.0002810772136796152</v>
+        <v>-0.01661137037382007</v>
       </c>
       <c r="AK40">
-        <v>-0.0003594256227740117</v>
+        <v>-0.02099639505050177</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>0.842</v>
+      </c>
+      <c r="AO40">
+        <v>262.4703087885986</v>
+      </c>
+      <c r="AQ40">
+        <v>262.4703087885986</v>
       </c>
     </row>
     <row r="41">
@@ -5643,7 +5589,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cadence Opportunities Fund Limited (ASX:CDO)</t>
+          <t>Regal Partners Limited (ASX:RPL)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5651,26 +5597,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F41">
+        <v>0.19</v>
+      </c>
+      <c r="G41">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="H41">
+        <v>0.3651685393258427</v>
+      </c>
+      <c r="I41">
+        <v>0.1850187265917603</v>
+      </c>
+      <c r="J41">
+        <v>0.09250936329588016</v>
+      </c>
       <c r="K41">
-        <v>-1.05</v>
+        <v>1.79</v>
+      </c>
+      <c r="L41">
+        <v>0.03352059925093633</v>
       </c>
       <c r="M41">
-        <v>0.737</v>
+        <v>6.65</v>
       </c>
       <c r="N41">
-        <v>0.03122881355932203</v>
+        <v>0.01425203600514359</v>
       </c>
       <c r="O41">
-        <v>-0.7019047619047618</v>
+        <v>3.715083798882682</v>
       </c>
       <c r="P41">
-        <v>0.737</v>
+        <v>6.65</v>
       </c>
       <c r="Q41">
-        <v>0.03122881355932203</v>
+        <v>0.01425203600514359</v>
       </c>
       <c r="R41">
-        <v>-0.7019047619047618</v>
+        <v>3.715083798882682</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -5679,67 +5643,67 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>16.6</v>
+        <v>24.8</v>
       </c>
       <c r="V41">
-        <v>0.7033898305084746</v>
+        <v>0.0531504500642949</v>
       </c>
       <c r="W41">
-        <v>-0.06363636363636364</v>
+        <v>0.008475378787878789</v>
       </c>
       <c r="X41">
-        <v>0.07417115462227303</v>
+        <v>0.06239408885491736</v>
       </c>
       <c r="Y41">
-        <v>-0.1378075182586367</v>
+        <v>-0.05391871006703857</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>0.292202462380301</v>
       </c>
       <c r="AA41">
-        <v>-0.1142225497420781</v>
+        <v>0.02703146374829002</v>
       </c>
       <c r="AB41">
-        <v>0.07192869072218182</v>
+        <v>0.06225526344733693</v>
       </c>
       <c r="AC41">
-        <v>-0.1861512404642599</v>
+        <v>-0.03522379969904692</v>
       </c>
       <c r="AD41">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="AG41">
-        <v>-14.88</v>
+        <v>-22.37</v>
       </c>
       <c r="AH41">
-        <v>0.0679304897314376</v>
+        <v>0.005180905272583843</v>
       </c>
       <c r="AI41">
-        <v>0.06661502711076685</v>
+        <v>0.008211401344912649</v>
       </c>
       <c r="AJ41">
-        <v>-1.706422018348624</v>
+        <v>-0.0503567971546271</v>
       </c>
       <c r="AK41">
-        <v>-1.613882863340564</v>
+        <v>-0.08250654667502674</v>
       </c>
       <c r="AL41">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>0.103</v>
-      </c>
-      <c r="AO41">
-        <v>-15.04854368932039</v>
-      </c>
-      <c r="AQ41">
-        <v>-15.04854368932039</v>
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>0.1748201438848921</v>
+      </c>
+      <c r="AP41">
+        <v>-1.609352517985612</v>
       </c>
     </row>
     <row r="42">
@@ -5750,7 +5714,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pacific Current Group Limited (ASX:PAC)</t>
+          <t>AMCIL Limited (ASX:AMH)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5758,26 +5722,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D42">
+        <v>0.0521</v>
+      </c>
+      <c r="E42">
+        <v>0.0388</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0.7834302325581395</v>
+      </c>
+      <c r="J42">
+        <v>0.7388937671800689</v>
+      </c>
       <c r="K42">
-        <v>-24.3</v>
+        <v>5.03</v>
+      </c>
+      <c r="L42">
+        <v>0.7311046511627908</v>
       </c>
       <c r="M42">
-        <v>12.8</v>
+        <v>7.14</v>
       </c>
       <c r="N42">
-        <v>0.05011746280344558</v>
+        <v>0.0323516085183507</v>
       </c>
       <c r="O42">
-        <v>-0.5267489711934157</v>
+        <v>1.41948310139165</v>
       </c>
       <c r="P42">
-        <v>12.8</v>
+        <v>7.14</v>
       </c>
       <c r="Q42">
-        <v>0.05011746280344558</v>
+        <v>0.0323516085183507</v>
       </c>
       <c r="R42">
-        <v>-0.5267489711934157</v>
+        <v>1.41948310139165</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -5786,73 +5771,67 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>24</v>
+        <v>3.3</v>
       </c>
       <c r="V42">
-        <v>0.09397024275646045</v>
+        <v>0.01495242410512007</v>
       </c>
       <c r="W42">
-        <v>-0.08054358634405039</v>
+        <v>0.0242526518804243</v>
       </c>
       <c r="X42">
-        <v>0.07252109263570547</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y42">
-        <v>-0.1530646789797558</v>
+        <v>-0.03805573665537733</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>0.03575883575883575</v>
       </c>
       <c r="AA42">
-        <v>-0.1316047158356508</v>
+        <v>0.02642198086381951</v>
       </c>
       <c r="AB42">
-        <v>0.07240953366191968</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC42">
-        <v>-0.2040142494975705</v>
+        <v>-0.03588640767198212</v>
       </c>
       <c r="AD42">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>0.725</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>-23.275</v>
+        <v>-3.3</v>
       </c>
       <c r="AH42">
-        <v>0.002830649097120547</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>0.001993812306634582</v>
+        <v>0</v>
       </c>
       <c r="AJ42">
-        <v>-0.1002692514808831</v>
+        <v>-0.01517939282428703</v>
       </c>
       <c r="AK42">
-        <v>-0.06853146853146853</v>
+        <v>-0.01572926596758818</v>
       </c>
       <c r="AL42">
-        <v>0.041</v>
+        <v>0.061</v>
       </c>
       <c r="AM42">
-        <v>0.041</v>
-      </c>
-      <c r="AN42">
-        <v>-0.02301587301587301</v>
+        <v>0.061</v>
       </c>
       <c r="AO42">
-        <v>-819.5121951219512</v>
-      </c>
-      <c r="AP42">
-        <v>0.7388888888888888</v>
+        <v>88.36065573770492</v>
       </c>
       <c r="AQ42">
-        <v>-819.5121951219512</v>
+        <v>88.36065573770492</v>
       </c>
     </row>
     <row r="43">
@@ -5863,7 +5842,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spheria Emerging Companies Limited (ASX:SEC)</t>
+          <t>Mirrabooka Investments Limited (ASX:MIR)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5871,26 +5850,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D43">
+        <v>0.0383</v>
+      </c>
+      <c r="E43">
+        <v>0.0177</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0.8091743119266055</v>
+      </c>
+      <c r="J43">
+        <v>0.6955573708684177</v>
+      </c>
       <c r="K43">
-        <v>-9.23</v>
+        <v>7.53</v>
+      </c>
+      <c r="L43">
+        <v>0.6908256880733945</v>
       </c>
       <c r="M43">
-        <v>5.22</v>
+        <v>8.32</v>
       </c>
       <c r="N43">
-        <v>0.06752910737386805</v>
+        <v>0.0214488270172725</v>
       </c>
       <c r="O43">
-        <v>-0.5655471289274105</v>
+        <v>1.104913678618858</v>
       </c>
       <c r="P43">
-        <v>5.22</v>
+        <v>8.32</v>
       </c>
       <c r="Q43">
-        <v>0.06752910737386805</v>
+        <v>0.0214488270172725</v>
       </c>
       <c r="R43">
-        <v>-0.5655471289274105</v>
+        <v>1.104913678618858</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -5899,31 +5899,31 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>2.32</v>
+        <v>15.5</v>
       </c>
       <c r="V43">
-        <v>0.03001293661060802</v>
+        <v>0.03995875225573602</v>
       </c>
       <c r="W43">
-        <v>-0.08189884649511979</v>
+        <v>0.02374645222327341</v>
       </c>
       <c r="X43">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y43">
-        <v>-0.1543530655358246</v>
+        <v>-0.03856193631252822</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>0.03655264922870556</v>
       </c>
       <c r="AA43">
-        <v>-0.1316028317298965</v>
+        <v>0.02542446459579394</v>
       </c>
       <c r="AB43">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC43">
-        <v>-0.2040570507706014</v>
+        <v>-0.0368839239400077</v>
       </c>
       <c r="AD43">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>-2.32</v>
+        <v>-15.5</v>
       </c>
       <c r="AH43">
         <v>0</v>
@@ -5944,16 +5944,22 @@
         <v>0</v>
       </c>
       <c r="AJ43">
-        <v>-0.03094158442251266</v>
+        <v>-0.0416219119226638</v>
       </c>
       <c r="AK43">
-        <v>-0.02673427056925559</v>
+        <v>-0.04840724547158026</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="AO43">
+        <v>147</v>
+      </c>
+      <c r="AQ43">
+        <v>147</v>
       </c>
     </row>
     <row r="44">
@@ -5964,7 +5970,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tribeca Global Natural Resources Limited (ASX:TGF)</t>
+          <t>Sandon Capital Investments Limited (ASX:SNC)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5972,56 +5978,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D44">
+        <v>-0.0347</v>
+      </c>
+      <c r="E44">
+        <v>-0.108</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0.4911242603550296</v>
+      </c>
+      <c r="J44">
+        <v>0.4011376216835274</v>
+      </c>
       <c r="K44">
-        <v>-8.15</v>
+        <v>1.26</v>
+      </c>
+      <c r="L44">
+        <v>0.3727810650887574</v>
       </c>
       <c r="M44">
-        <v>-0</v>
+        <v>3.51</v>
       </c>
       <c r="N44">
-        <v>-0</v>
+        <v>0.04936708860759494</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="P44">
-        <v>-0</v>
+        <v>3.51</v>
       </c>
       <c r="Q44">
-        <v>-0</v>
+        <v>0.04936708860759494</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.785714285714286</v>
       </c>
       <c r="S44">
         <v>0</v>
       </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
       <c r="U44">
-        <v>41.4</v>
+        <v>0.098</v>
       </c>
       <c r="V44">
-        <v>0.4404255319148936</v>
+        <v>0.001378340365682138</v>
       </c>
       <c r="W44">
-        <v>-0.06953924914675769</v>
+        <v>0.01671087533156499</v>
       </c>
       <c r="X44">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y44">
-        <v>-0.1419934681874626</v>
+        <v>-0.04559751320423665</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>0.04504204368278673</v>
       </c>
       <c r="AA44">
-        <v>-0.139030612244898</v>
+        <v>0.01806805827867862</v>
       </c>
       <c r="AB44">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC44">
-        <v>-0.2114848312856028</v>
+        <v>-0.04424033025712301</v>
       </c>
       <c r="AD44">
         <v>0</v>
@@ -6033,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="AG44">
-        <v>-41.4</v>
+        <v>-0.098</v>
       </c>
       <c r="AH44">
         <v>0</v>
@@ -6042,22 +6072,16 @@
         <v>0</v>
       </c>
       <c r="AJ44">
-        <v>-0.7870722433460076</v>
+        <v>-0.001380242810061689</v>
       </c>
       <c r="AK44">
-        <v>-0.711340206185567</v>
+        <v>-0.001390031488468412</v>
       </c>
       <c r="AL44">
-        <v>0.719</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>0.719</v>
-      </c>
-      <c r="AO44">
-        <v>-15.15994436717664</v>
-      </c>
-      <c r="AQ44">
-        <v>-15.15994436717664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -6068,7 +6092,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hearts and Minds Investments Limited (ASX:HM1)</t>
+          <t>Pinnacle Investment Management Group Limited (ASX:PNI)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6076,26 +6100,50 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D45">
+        <v>0.224</v>
+      </c>
+      <c r="E45">
+        <v>0.266</v>
+      </c>
+      <c r="F45">
+        <v>0.0934</v>
+      </c>
+      <c r="G45">
+        <v>0.1646864686468647</v>
+      </c>
+      <c r="H45">
+        <v>0.1646864686468647</v>
+      </c>
+      <c r="I45">
+        <v>0.1580858085808581</v>
+      </c>
+      <c r="J45">
+        <v>0.1580858085808581</v>
+      </c>
       <c r="K45">
-        <v>-65.3</v>
+        <v>50.9</v>
+      </c>
+      <c r="L45">
+        <v>1.67986798679868</v>
       </c>
       <c r="M45">
-        <v>17.4</v>
+        <v>42</v>
       </c>
       <c r="N45">
-        <v>0.04927782497875955</v>
+        <v>0.03112955825674474</v>
       </c>
       <c r="O45">
-        <v>-0.2664624808575804</v>
+        <v>0.825147347740668</v>
       </c>
       <c r="P45">
-        <v>17.4</v>
+        <v>42</v>
       </c>
       <c r="Q45">
-        <v>0.04927782497875955</v>
+        <v>0.03112955825674474</v>
       </c>
       <c r="R45">
-        <v>-0.2664624808575804</v>
+        <v>0.825147347740668</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -6104,67 +6152,73 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>84.09999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="V45">
-        <v>0.2381761540640045</v>
+        <v>0.01363771123628817</v>
       </c>
       <c r="W45">
-        <v>-0.09829896131265994</v>
+        <v>0.1836881992060628</v>
       </c>
       <c r="X45">
-        <v>0.07245421904070486</v>
+        <v>0.06328656888889969</v>
       </c>
       <c r="Y45">
-        <v>-0.1707531803533648</v>
+        <v>0.1204016303171631</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>0.09058295964125559</v>
       </c>
       <c r="AA45">
-        <v>-0.1630510846745976</v>
+        <v>0.01431988041853513</v>
       </c>
       <c r="AB45">
-        <v>0.07245421904070486</v>
+        <v>0.06173306173562577</v>
       </c>
       <c r="AC45">
-        <v>-0.2355053037153025</v>
+        <v>-0.04741318131709064</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>80.2</v>
       </c>
       <c r="AG45">
-        <v>-84.09999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>0.05610745767454876</v>
       </c>
       <c r="AI45">
-        <v>0</v>
+        <v>0.2219147758716104</v>
       </c>
       <c r="AJ45">
-        <v>-0.3126394052044609</v>
+        <v>0.04379872430900071</v>
       </c>
       <c r="AK45">
-        <v>-0.2351789709172259</v>
+        <v>0.1801749271137026</v>
       </c>
       <c r="AL45">
-        <v>0.036</v>
+        <v>4.04</v>
       </c>
       <c r="AM45">
-        <v>0.036</v>
+        <v>4.04</v>
+      </c>
+      <c r="AN45">
+        <v>16.07214428857715</v>
       </c>
       <c r="AO45">
-        <v>-2588.888888888889</v>
+        <v>1.185643564356436</v>
+      </c>
+      <c r="AP45">
+        <v>12.38476953907816</v>
       </c>
       <c r="AQ45">
-        <v>-2588.888888888889</v>
+        <v>1.185643564356436</v>
       </c>
     </row>
     <row r="46">
@@ -6175,7 +6229,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Auctus Investment Group Limited (ASX:AVC)</t>
+          <t>MA Financial Group Limited (ASX:MAF)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6184,112 +6238,112 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.715</v>
+        <v>0.41</v>
+      </c>
+      <c r="E46">
+        <v>0.0525</v>
+      </c>
+      <c r="F46">
+        <v>0.133</v>
       </c>
       <c r="G46">
-        <v>-0.1532663316582915</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>-0.1532663316582915</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>-0.1595477386934673</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>-0.1595477386934673</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>-1.44</v>
+        <v>27.7</v>
       </c>
       <c r="L46">
-        <v>-0.1809045226130653</v>
+        <v>0.05752855659397715</v>
       </c>
       <c r="M46">
-        <v>0.545</v>
+        <v>29.81</v>
       </c>
       <c r="N46">
-        <v>0.01216517857142857</v>
+        <v>0.04860590249470081</v>
       </c>
       <c r="O46">
-        <v>-0.3784722222222223</v>
+        <v>1.076173285198556</v>
       </c>
       <c r="P46">
-        <v>-0</v>
+        <v>23.1</v>
       </c>
       <c r="Q46">
-        <v>-0</v>
+        <v>0.03766509049404859</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>0.8339350180505416</v>
       </c>
       <c r="S46">
-        <v>0.545</v>
+        <v>6.710000000000001</v>
       </c>
       <c r="T46">
-        <v>1</v>
+        <v>0.2250922509225092</v>
       </c>
       <c r="U46">
-        <v>7.28</v>
+        <v>77.2</v>
       </c>
       <c r="V46">
-        <v>0.1625</v>
+        <v>0.1258764063264308</v>
       </c>
       <c r="W46">
-        <v>-0.07539267015706805</v>
+        <v>0.1027448071216617</v>
       </c>
       <c r="X46">
-        <v>0.0733060914601727</v>
+        <v>0.08851221141342223</v>
       </c>
       <c r="Y46">
-        <v>-0.1486987616172407</v>
+        <v>0.01423259570823948</v>
       </c>
       <c r="Z46">
-        <v>1.081815710790976</v>
+        <v>0.7326536822884966</v>
       </c>
       <c r="AA46">
-        <v>-0.1726012503397663</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.07209140235708179</v>
+        <v>0.05600983354918665</v>
       </c>
       <c r="AC46">
-        <v>-0.244692652696848</v>
+        <v>-0.05600983354918665</v>
       </c>
       <c r="AD46">
-        <v>1.62</v>
+        <v>976.6</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>976.6</v>
       </c>
       <c r="AG46">
-        <v>-5.66</v>
+        <v>899.4</v>
       </c>
       <c r="AH46">
-        <v>0.03489875053856097</v>
+        <v>0.6142524687087239</v>
       </c>
       <c r="AI46">
-        <v>0.06347962382445142</v>
+        <v>0.7844176706827309</v>
       </c>
       <c r="AJ46">
-        <v>-0.14460909555442</v>
+        <v>0.5945660078006214</v>
       </c>
       <c r="AK46">
-        <v>-0.3103070175438597</v>
+        <v>0.770166124336359</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
         <v>0</v>
-      </c>
-      <c r="AN46">
-        <v>-1.327868852459017</v>
-      </c>
-      <c r="AP46">
-        <v>4.639344262295082</v>
       </c>
     </row>
     <row r="47">
@@ -6300,7 +6354,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Benjamin Hornigold Limited (ASX:BHD)</t>
+          <t>ECP Emerging Growth Limited (ASX:ECP)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6308,86 +6362,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D47">
+        <v>0.0692</v>
+      </c>
+      <c r="E47">
+        <v>0.188</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>-0.002386634844868735</v>
+      </c>
+      <c r="J47">
+        <v>-0.002386634844868735</v>
+      </c>
       <c r="K47">
-        <v>-0.854</v>
+        <v>2.66</v>
+      </c>
+      <c r="L47">
+        <v>6.348448687350836</v>
       </c>
       <c r="M47">
-        <v>-0</v>
+        <v>0.604</v>
       </c>
       <c r="N47">
-        <v>-0</v>
+        <v>0.04345323741007194</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>0.2270676691729323</v>
       </c>
       <c r="P47">
-        <v>-0</v>
+        <v>0.604</v>
       </c>
       <c r="Q47">
-        <v>-0</v>
+        <v>0.04345323741007194</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>0.2270676691729323</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
       <c r="U47">
-        <v>0.92</v>
+        <v>1.26</v>
       </c>
       <c r="V47">
-        <v>0.247978436657682</v>
+        <v>0.09064748201438849</v>
       </c>
       <c r="W47">
-        <v>-0.1332293291731669</v>
+        <v>0.1821917808219178</v>
       </c>
       <c r="X47">
-        <v>0.07245421904070486</v>
+        <v>0.0695181914371054</v>
       </c>
       <c r="Y47">
-        <v>-0.2056835482138718</v>
+        <v>0.1126735893848124</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>0.02249060654857757</v>
       </c>
       <c r="AA47">
-        <v>-0.1742857142857143</v>
+        <v>-5.367686527106817e-05</v>
       </c>
       <c r="AB47">
-        <v>0.07245421904070486</v>
+        <v>0.05918447853805728</v>
       </c>
       <c r="AC47">
-        <v>-0.2467399333264191</v>
+        <v>-0.05923815540332834</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AG47">
-        <v>-0.92</v>
+        <v>4.83</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>0.3046523261630815</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>0.2732166890982504</v>
       </c>
       <c r="AJ47">
-        <v>-0.3297491039426523</v>
+        <v>0.2578750667378537</v>
       </c>
       <c r="AK47">
-        <v>-0.2233009708737864</v>
+        <v>0.2296718972895863</v>
       </c>
       <c r="AL47">
-        <v>0</v>
+        <v>0.662</v>
       </c>
       <c r="AM47">
-        <v>0</v>
+        <v>0.662</v>
+      </c>
+      <c r="AO47">
+        <v>-0.001510574018126888</v>
+      </c>
+      <c r="AQ47">
+        <v>-0.001510574018126888</v>
       </c>
     </row>
     <row r="48">
@@ -6398,7 +6482,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sandon Capital Investments Limited (ASX:SNC)</t>
+          <t>Pacific Current Group Limited (ASX:PAC)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6406,89 +6490,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D48">
+        <v>-0.268</v>
+      </c>
+      <c r="F48">
+        <v>0.123</v>
+      </c>
+      <c r="G48">
+        <v>0.1470873786407767</v>
+      </c>
+      <c r="H48">
+        <v>0.1470873786407767</v>
+      </c>
+      <c r="I48">
+        <v>0.03762135922330097</v>
+      </c>
+      <c r="J48">
+        <v>0.03762135922330097</v>
+      </c>
       <c r="K48">
-        <v>-16.3</v>
+        <v>-10.5</v>
+      </c>
+      <c r="L48">
+        <v>-0.5097087378640777</v>
       </c>
       <c r="M48">
-        <v>3.61</v>
+        <v>11.035</v>
       </c>
       <c r="N48">
-        <v>0.0586038961038961</v>
+        <v>0.03571197411003237</v>
       </c>
       <c r="O48">
-        <v>-0.2214723926380368</v>
+        <v>-1.050952380952381</v>
       </c>
       <c r="P48">
-        <v>3.61</v>
+        <v>11</v>
       </c>
       <c r="Q48">
-        <v>0.0586038961038961</v>
+        <v>0.03559870550161812</v>
       </c>
       <c r="R48">
-        <v>-0.2214723926380368</v>
+        <v>-1.047619047619048</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>0.03500000000000014</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.003171726325328513</v>
       </c>
       <c r="U48">
-        <v>0.359</v>
+        <v>15.4</v>
       </c>
       <c r="V48">
-        <v>0.005827922077922078</v>
+        <v>0.04983818770226537</v>
       </c>
       <c r="W48">
-        <v>-0.1858608893956671</v>
+        <v>-0.02903761061946902</v>
       </c>
       <c r="X48">
-        <v>0.07245421904070486</v>
+        <v>0.06240850840412887</v>
       </c>
       <c r="Y48">
-        <v>-0.2583151084363719</v>
+        <v>-0.09144611902359789</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>0.0658725717483412</v>
       </c>
       <c r="AA48">
-        <v>-0.2440158029281896</v>
+        <v>0.002478215684707011</v>
       </c>
       <c r="AB48">
-        <v>0.07245421904070486</v>
+        <v>0.06224637891429433</v>
       </c>
       <c r="AC48">
-        <v>-0.3164700219688945</v>
+        <v>-0.05976816322958732</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE48">
         <v>0</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG48">
-        <v>-0.359</v>
+        <v>-13.52</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>0.006047349459598558</v>
       </c>
       <c r="AI48">
-        <v>0</v>
+        <v>0.005505446878294482</v>
       </c>
       <c r="AJ48">
-        <v>-0.005862085857513757</v>
+        <v>-0.04575605793962366</v>
       </c>
       <c r="AK48">
-        <v>-0.004784051385242733</v>
+        <v>-0.04146221786064769</v>
       </c>
       <c r="AL48">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AM48">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="AN48">
+        <v>0.6204620462046204</v>
+      </c>
+      <c r="AO48">
+        <v>0.3506787330316742</v>
+      </c>
+      <c r="AP48">
+        <v>-4.462046204620462</v>
+      </c>
+      <c r="AQ48">
+        <v>0.3506787330316742</v>
       </c>
     </row>
     <row r="49">
@@ -6499,7 +6616,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thorney Technologies Ltd (ASX:TEK)</t>
+          <t>Salter Brothers Emerging Companies Limited (ASX:SB2)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6508,16 +6625,16 @@
         </is>
       </c>
       <c r="K49">
-        <v>-31.1</v>
+        <v>-1.21</v>
       </c>
       <c r="M49">
-        <v>-0</v>
+        <v>0.888</v>
       </c>
       <c r="N49">
-        <v>-0</v>
+        <v>0.02690909090909091</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>-0.7338842975206612</v>
       </c>
       <c r="P49">
         <v>-0</v>
@@ -6529,34 +6646,37 @@
         <v>0</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>0.888</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
       </c>
       <c r="U49">
-        <v>6.43</v>
+        <v>3.79</v>
       </c>
       <c r="V49">
-        <v>0.1099145299145299</v>
+        <v>0.1148484848484849</v>
       </c>
       <c r="W49">
-        <v>-0.236322188449848</v>
+        <v>-0.01967479674796748</v>
       </c>
       <c r="X49">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y49">
-        <v>-0.3087764074905529</v>
+        <v>-0.08198318528376911</v>
       </c>
       <c r="Z49">
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>-0.3575092731433983</v>
+        <v>-0.03637331440738112</v>
       </c>
       <c r="AB49">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC49">
-        <v>-0.4299634921841032</v>
+        <v>-0.09868170294318275</v>
       </c>
       <c r="AD49">
         <v>0</v>
@@ -6568,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="AG49">
-        <v>-6.43</v>
+        <v>-3.79</v>
       </c>
       <c r="AH49">
         <v>0</v>
@@ -6577,22 +6697,16 @@
         <v>0</v>
       </c>
       <c r="AJ49">
-        <v>-0.1234876128288842</v>
+        <v>-0.1297500855871277</v>
       </c>
       <c r="AK49">
-        <v>-0.06412685748479105</v>
+        <v>-0.07082788263875911</v>
       </c>
       <c r="AL49">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM49">
-        <v>0.001</v>
-      </c>
-      <c r="AO49">
-        <v>-45299.99999999999</v>
-      </c>
-      <c r="AQ49">
-        <v>-45299.99999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6611,8 +6725,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D50">
+        <v>-0.377</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>-6.657894736842105</v>
+      </c>
+      <c r="J50">
+        <v>-6.657894736842105</v>
+      </c>
       <c r="K50">
-        <v>-1.76</v>
+        <v>-0.439</v>
+      </c>
+      <c r="L50">
+        <v>-11.55263157894737</v>
       </c>
       <c r="M50">
         <v>-0</v>
@@ -6636,31 +6768,31 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>0.288</v>
+        <v>0.022</v>
       </c>
       <c r="V50">
-        <v>0.5052631578947369</v>
+        <v>0.07457627118644068</v>
       </c>
       <c r="W50">
-        <v>-0.3358778625954199</v>
+        <v>-0.1513793103448276</v>
       </c>
       <c r="X50">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y50">
-        <v>-0.4083320816361247</v>
+        <v>-0.2136876988806292</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>0.01454823889739663</v>
       </c>
       <c r="AA50">
-        <v>-0.3675048355899419</v>
+        <v>-0.09686064318529862</v>
       </c>
       <c r="AB50">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC50">
-        <v>-0.4399590546306468</v>
+        <v>-0.1591690317211003</v>
       </c>
       <c r="AD50">
         <v>0</v>
@@ -6672,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>-0.288</v>
+        <v>-0.022</v>
       </c>
       <c r="AH50">
         <v>0</v>
@@ -6681,10 +6813,10 @@
         <v>0</v>
       </c>
       <c r="AJ50">
-        <v>-1.021276595744681</v>
+        <v>-0.08058608058608059</v>
       </c>
       <c r="AK50">
-        <v>-0.110260336906585</v>
+        <v>-0.008986928104575161</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -6701,7 +6833,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Touch Ventures Limited (ASX:TVL)</t>
+          <t>Cadence Opportunities Fund Limited (ASX:CDO)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6710,97 +6842,94 @@
         </is>
       </c>
       <c r="K51">
-        <v>-20.6</v>
+        <v>-0.894</v>
       </c>
       <c r="M51">
-        <v>0.106</v>
+        <v>0.988</v>
       </c>
       <c r="N51">
-        <v>0.002334801762114537</v>
+        <v>0.06136645962732919</v>
       </c>
       <c r="O51">
-        <v>-0.005145631067961165</v>
+        <v>-1.105145413870246</v>
       </c>
       <c r="P51">
-        <v>-0</v>
+        <v>0.988</v>
       </c>
       <c r="Q51">
-        <v>-0</v>
+        <v>0.06136645962732919</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>-1.105145413870246</v>
       </c>
       <c r="S51">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>44.1</v>
+        <v>14.1</v>
       </c>
       <c r="V51">
-        <v>0.9713656387665199</v>
+        <v>0.8757763975155278</v>
       </c>
       <c r="W51">
-        <v>-0.2947067238912732</v>
+        <v>-0.0370954356846473</v>
       </c>
       <c r="X51">
-        <v>0.07247192550081355</v>
+        <v>0.06499652165967808</v>
       </c>
       <c r="Y51">
-        <v>-0.3671786493920868</v>
+        <v>-0.1020919573443254</v>
       </c>
       <c r="Z51">
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>-0.3993765525303199</v>
+        <v>-0.1160520607375271</v>
       </c>
       <c r="AB51">
-        <v>0.07244641094261713</v>
+        <v>0.06113089603421341</v>
       </c>
       <c r="AC51">
-        <v>-0.471822963472937</v>
+        <v>-0.1771829567717405</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE51">
-        <v>0.03412322274881516</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>0.03412322274881516</v>
+        <v>2.63</v>
       </c>
       <c r="AG51">
-        <v>-44.06587677725118</v>
+        <v>-11.47</v>
       </c>
       <c r="AH51">
-        <v>0.0007510483383055515</v>
+        <v>0.1404164442071543</v>
       </c>
       <c r="AI51">
-        <v>0.0003092717080818711</v>
+        <v>0.1094465251768623</v>
       </c>
       <c r="AJ51">
-        <v>-33.02984014209592</v>
+        <v>-2.477321814254858</v>
       </c>
       <c r="AK51">
-        <v>-0.6653047497746039</v>
+        <v>-1.15508559919436</v>
       </c>
       <c r="AL51">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AM51">
-        <v>-0.05</v>
-      </c>
-      <c r="AN51">
-        <v>0</v>
-      </c>
-      <c r="AP51">
-        <v>-1224.052132701422</v>
+        <v>0.337</v>
+      </c>
+      <c r="AO51">
+        <v>-3.175074183976261</v>
       </c>
       <c r="AQ51">
-        <v>497.9999999999999</v>
+        <v>-3.175074183976261</v>
       </c>
     </row>
     <row r="52">
@@ -6811,7 +6940,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hygrovest Limited (ASX:HGV)</t>
+          <t>BPH Energy Limited (ASX:BPH)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6819,8 +6948,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D52">
+        <v>0.0521</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>-4.633663366336633</v>
+      </c>
+      <c r="J52">
+        <v>-4.633663366336633</v>
+      </c>
       <c r="K52">
-        <v>-11</v>
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="L52">
+        <v>2.811881188118811</v>
       </c>
       <c r="M52">
         <v>-0</v>
@@ -6829,7 +6976,7 @@
         <v>-0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P52">
         <v>-0</v>
@@ -6838,73 +6985,67 @@
         <v>-0</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S52">
         <v>0</v>
       </c>
       <c r="U52">
-        <v>4.35</v>
+        <v>3.74</v>
       </c>
       <c r="V52">
-        <v>0.3990825688073394</v>
+        <v>0.113677811550152</v>
       </c>
       <c r="W52">
-        <v>-0.3642384105960265</v>
+        <v>0.05702811244979919</v>
       </c>
       <c r="X52">
-        <v>0.0725750868389901</v>
+        <v>0.06233789906609126</v>
       </c>
       <c r="Y52">
-        <v>-0.4368134974350166</v>
+        <v>-0.00530978661629207</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>0.02511812981845312</v>
       </c>
       <c r="AA52">
-        <v>-0.4427019223853608</v>
+        <v>-0.1163889579706541</v>
       </c>
       <c r="AB52">
-        <v>0.07240115162910124</v>
+        <v>0.06229337724064452</v>
       </c>
       <c r="AC52">
-        <v>-0.515103074014462</v>
+        <v>-0.1786823352112986</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AE52">
-        <v>0.05592417061611375</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>0.05592417061611375</v>
+        <v>0.059</v>
       </c>
       <c r="AG52">
-        <v>-4.294075829383886</v>
+        <v>-3.681</v>
       </c>
       <c r="AH52">
-        <v>0.005104468572911709</v>
+        <v>0.00179010285506235</v>
       </c>
       <c r="AI52">
-        <v>0.003317775403475229</v>
+        <v>0.004552820433675438</v>
       </c>
       <c r="AJ52">
-        <v>-0.6500340782724109</v>
+        <v>-0.1259796707621753</v>
       </c>
       <c r="AK52">
-        <v>-0.3433633349123638</v>
+        <v>-0.3992840872111942</v>
       </c>
       <c r="AL52">
         <v>0</v>
       </c>
       <c r="AM52">
         <v>0</v>
-      </c>
-      <c r="AN52">
-        <v>-0</v>
-      </c>
-      <c r="AP52">
-        <v>0.3507945289914129</v>
       </c>
     </row>
     <row r="53">
@@ -6915,7 +7056,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>K2 Asset Management Holdings Ltd (ASX:KAM)</t>
+          <t>Thorney Technologies Ltd (ASX:TEK)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6923,35 +7064,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D53">
-        <v>-0.342</v>
-      </c>
-      <c r="G53">
-        <v>-0.7013698630136986</v>
-      </c>
-      <c r="H53">
-        <v>-0.7397260273972603</v>
-      </c>
-      <c r="I53">
-        <v>-0.7602739726027398</v>
-      </c>
-      <c r="J53">
-        <v>-0.7602739726027398</v>
-      </c>
       <c r="K53">
-        <v>-1.66</v>
-      </c>
-      <c r="L53">
-        <v>-1.136986301369863</v>
+        <v>-17</v>
       </c>
       <c r="M53">
-        <v>-0</v>
+        <v>0.769</v>
       </c>
       <c r="N53">
-        <v>-0</v>
+        <v>0.01629237288135593</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>-0.04523529411764706</v>
       </c>
       <c r="P53">
         <v>-0</v>
@@ -6963,76 +7086,67 @@
         <v>0</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>0.769</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
       </c>
       <c r="U53">
-        <v>7.41</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="V53">
-        <v>1.027739251040222</v>
+        <v>0.1809322033898305</v>
       </c>
       <c r="W53">
-        <v>-0.1693877551020408</v>
+        <v>-0.1593252108716026</v>
       </c>
       <c r="X53">
-        <v>0.07261432163614122</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y53">
-        <v>-0.242002076738182</v>
+        <v>-0.2216335994074042</v>
       </c>
       <c r="Z53">
-        <v>0.7281795511221942</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>-0.5536159600997504</v>
+        <v>-0.1695422359629002</v>
       </c>
       <c r="AB53">
-        <v>0.0724019973820882</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC53">
-        <v>-0.6260179574818386</v>
+        <v>-0.2318506244987018</v>
       </c>
       <c r="AD53">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="AE53">
         <v>0</v>
       </c>
       <c r="AF53">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>-7.361</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="AH53">
-        <v>0.006750241080038573</v>
+        <v>0</v>
       </c>
       <c r="AI53">
-        <v>0.006622516556291391</v>
+        <v>0</v>
       </c>
       <c r="AJ53">
-        <v>48.74834437086099</v>
+        <v>-0.2209001551991722</v>
       </c>
       <c r="AK53">
-        <v>669.1818181818109</v>
+        <v>-0.1112558624283481</v>
       </c>
       <c r="AL53">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM53">
-        <v>0.008</v>
-      </c>
-      <c r="AN53">
-        <v>-0.04537037037037037</v>
-      </c>
-      <c r="AO53">
-        <v>-138.75</v>
-      </c>
-      <c r="AP53">
-        <v>6.81574074074074</v>
-      </c>
-      <c r="AQ53">
-        <v>-138.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -7043,7 +7157,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fatfish Group Limited (ASX:FFG)</t>
+          <t>Hygrovest Limited (ASX:HGV)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7051,35 +7165,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D54">
-        <v>0.119</v>
-      </c>
-      <c r="G54">
-        <v>-8.233731739707835</v>
-      </c>
-      <c r="H54">
-        <v>-8.233731739707835</v>
-      </c>
-      <c r="I54">
-        <v>-9.920318725099602</v>
-      </c>
-      <c r="J54">
-        <v>-9.920318725099602</v>
-      </c>
       <c r="K54">
-        <v>-6.9</v>
-      </c>
-      <c r="L54">
-        <v>-9.163346613545817</v>
+        <v>-2.65</v>
       </c>
       <c r="M54">
-        <v>0.103</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="N54">
-        <v>0.008239999999999999</v>
+        <v>0.09466484268125855</v>
       </c>
       <c r="O54">
-        <v>-0.01492753623188406</v>
+        <v>-0.2611320754716981</v>
       </c>
       <c r="P54">
         <v>-0</v>
@@ -7091,79 +7187,73 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0.103</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T54">
         <v>1</v>
       </c>
       <c r="U54">
-        <v>1.39</v>
+        <v>2.47</v>
       </c>
       <c r="V54">
-        <v>0.1112</v>
+        <v>0.3378932968536252</v>
       </c>
       <c r="W54">
-        <v>-0.4928571428571429</v>
+        <v>-0.1577380952380952</v>
       </c>
       <c r="X54">
-        <v>0.08157585856949751</v>
+        <v>0.06238744926460323</v>
       </c>
       <c r="Y54">
-        <v>-0.5744330014266403</v>
+        <v>-0.2201255445026984</v>
       </c>
       <c r="Z54">
-        <v>0.05693331317102677</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>-0.5647966127324966</v>
+        <v>-0.2194631686054569</v>
       </c>
       <c r="AB54">
-        <v>0.08899332365159854</v>
+        <v>0.06226829276555028</v>
       </c>
       <c r="AC54">
-        <v>-0.6537899363840951</v>
+        <v>-0.2817314613710072</v>
       </c>
       <c r="AD54">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>0.03512022507318296</v>
       </c>
       <c r="AF54">
-        <v>4.84</v>
+        <v>0.03512022507318296</v>
       </c>
       <c r="AG54">
-        <v>3.45</v>
+        <v>-2.434879774926817</v>
       </c>
       <c r="AH54">
-        <v>0.279123414071511</v>
+        <v>0.00478143638184398</v>
       </c>
       <c r="AI54">
-        <v>0.4531835205992509</v>
+        <v>0.002715106196315563</v>
       </c>
       <c r="AJ54">
-        <v>0.2163009404388715</v>
+        <v>-0.4994502007158739</v>
       </c>
       <c r="AK54">
-        <v>0.3713670613562972</v>
+        <v>-0.2326662018744071</v>
       </c>
       <c r="AL54">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM54">
-        <v>0.5089999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN54">
-        <v>-0.663013698630137</v>
-      </c>
-      <c r="AO54">
-        <v>-13.17460317460318</v>
+        <v>-0</v>
       </c>
       <c r="AP54">
-        <v>-0.4726027397260275</v>
-      </c>
-      <c r="AQ54">
-        <v>-14.67583497053045</v>
+        <v>0.8909183223296075</v>
       </c>
     </row>
     <row r="55">
@@ -7174,7 +7264,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DomaCom Limited (ASX:DCL)</t>
+          <t>Touch Ventures Limited (ASX:TVL)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7182,35 +7272,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D55">
-        <v>0.3720000000000001</v>
-      </c>
-      <c r="G55">
-        <v>-0.3336065573770491</v>
-      </c>
-      <c r="H55">
-        <v>-0.3336065573770491</v>
-      </c>
-      <c r="I55">
-        <v>-0.3344262295081967</v>
-      </c>
-      <c r="J55">
-        <v>-0.3344262295081967</v>
-      </c>
       <c r="K55">
-        <v>-2.36</v>
-      </c>
-      <c r="L55">
-        <v>-0.9672131147540983</v>
+        <v>-24.3</v>
       </c>
       <c r="M55">
-        <v>-0</v>
+        <v>0.404</v>
       </c>
       <c r="N55">
-        <v>-0</v>
+        <v>0.01195266272189349</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>-0.01662551440329218</v>
       </c>
       <c r="P55">
         <v>-0</v>
@@ -7222,76 +7294,76 @@
         <v>0</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>0.404</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
       </c>
       <c r="U55">
-        <v>2.44</v>
+        <v>5.17</v>
       </c>
       <c r="V55">
-        <v>0.1251282051282051</v>
+        <v>0.1529585798816568</v>
       </c>
       <c r="W55">
-        <v>2.313725490196078</v>
+        <v>-0.2203082502266546</v>
       </c>
       <c r="X55">
-        <v>0.07516036342305488</v>
+        <v>0.06234967740150642</v>
       </c>
       <c r="Y55">
-        <v>2.238565126773024</v>
+        <v>-0.282657927628161</v>
       </c>
       <c r="Z55">
-        <v>2.131004366812227</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>-0.7126637554585152</v>
+        <v>-0.3987196916697615</v>
       </c>
       <c r="AB55">
-        <v>0.07165710610623598</v>
+        <v>0.06228272492514781</v>
       </c>
       <c r="AC55">
-        <v>-0.7843208615647512</v>
+        <v>-0.4610024165949093</v>
       </c>
       <c r="AD55">
-        <v>2.24</v>
+        <v>0.081</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>0.003806424292599835</v>
       </c>
       <c r="AF55">
-        <v>2.24</v>
+        <v>0.08480642429259984</v>
       </c>
       <c r="AG55">
-        <v>-0.1999999999999997</v>
+        <v>-5.0851935757074</v>
       </c>
       <c r="AH55">
-        <v>0.1030358785648574</v>
+        <v>0.002502786152315176</v>
       </c>
       <c r="AI55">
-        <v>0.5973333333333334</v>
+        <v>0.001034416350923666</v>
       </c>
       <c r="AJ55">
-        <v>-0.01036269430051812</v>
+        <v>-0.1770930822436382</v>
       </c>
       <c r="AK55">
-        <v>-0.1526717557251906</v>
+        <v>-0.06620069505374959</v>
       </c>
       <c r="AL55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AM55">
-        <v>1.01</v>
+        <v>-1.08</v>
       </c>
       <c r="AN55">
-        <v>-2.751842751842752</v>
-      </c>
-      <c r="AO55">
-        <v>-0.8079207920792079</v>
+        <v>-0.003068646764661313</v>
       </c>
       <c r="AP55">
-        <v>0.2457002457002454</v>
+        <v>0.1926501581947038</v>
       </c>
       <c r="AQ55">
-        <v>-0.8079207920792079</v>
+        <v>24.44444444444444</v>
       </c>
     </row>
     <row r="56">
@@ -7302,7 +7374,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Associate Global Partners Limited (ASX:APL)</t>
+          <t>DomaCom Limited (ASX:DCL)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7311,34 +7383,34 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.08019999999999999</v>
+        <v>0.266</v>
       </c>
       <c r="G56">
-        <v>-0.1047619047619048</v>
+        <v>-0.9464285714285715</v>
       </c>
       <c r="H56">
-        <v>-0.1047619047619048</v>
+        <v>-0.9464285714285715</v>
       </c>
       <c r="I56">
-        <v>-0.105952380952381</v>
+        <v>-0.9464285714285715</v>
       </c>
       <c r="J56">
-        <v>-0.105952380952381</v>
+        <v>-0.9464285714285715</v>
       </c>
       <c r="K56">
-        <v>-0.442</v>
+        <v>-2.52</v>
       </c>
       <c r="L56">
-        <v>-0.1052380952380952</v>
+        <v>-1.5</v>
       </c>
       <c r="M56">
-        <v>-0</v>
+        <v>0.1</v>
       </c>
       <c r="N56">
-        <v>-0</v>
+        <v>0.01677852348993289</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>-0.03968253968253969</v>
       </c>
       <c r="P56">
         <v>-0</v>
@@ -7350,76 +7422,79 @@
         <v>0</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
       </c>
       <c r="U56">
-        <v>4.54</v>
+        <v>0.323</v>
       </c>
       <c r="V56">
-        <v>0.461851475076297</v>
+        <v>0.05419463087248323</v>
       </c>
       <c r="W56">
-        <v>-0.06287339971550497</v>
+        <v>-1.668874172185431</v>
       </c>
       <c r="X56">
-        <v>0.07513833986755253</v>
+        <v>0.06824465107714081</v>
       </c>
       <c r="Y56">
-        <v>-0.1380117395830575</v>
+        <v>-1.737118823262571</v>
       </c>
       <c r="Z56">
-        <v>8.076923076923077</v>
+        <v>1.282442748091603</v>
       </c>
       <c r="AA56">
-        <v>-0.8557692307692307</v>
+        <v>-1.213740458015267</v>
       </c>
       <c r="AB56">
-        <v>0.0716629297623782</v>
+        <v>0.0670776991886263</v>
       </c>
       <c r="AC56">
-        <v>-0.9274321605316089</v>
+        <v>-1.280818157203893</v>
       </c>
       <c r="AD56">
-        <v>1.12</v>
+        <v>2.15</v>
       </c>
       <c r="AE56">
         <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG56">
-        <v>-3.42</v>
+        <v>1.827</v>
       </c>
       <c r="AH56">
-        <v>0.1022831050228311</v>
+        <v>0.2651048088779285</v>
       </c>
       <c r="AI56">
-        <v>0.1544827586206897</v>
+        <v>1.377322229340167</v>
       </c>
       <c r="AJ56">
-        <v>-0.5335413416536662</v>
+        <v>0.2346218055733915</v>
       </c>
       <c r="AK56">
-        <v>-1.261992619926199</v>
+        <v>1.475767366720517</v>
       </c>
       <c r="AL56">
-        <v>0.07199999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="AM56">
-        <v>-0.003000000000000003</v>
+        <v>0.845</v>
       </c>
       <c r="AN56">
-        <v>-2.545454545454546</v>
+        <v>-1.352201257861635</v>
       </c>
       <c r="AO56">
-        <v>-6.180555555555556</v>
+        <v>-1.881656804733728</v>
       </c>
       <c r="AP56">
-        <v>7.772727272727272</v>
+        <v>-1.149056603773585</v>
       </c>
       <c r="AQ56">
-        <v>148.3333333333332</v>
+        <v>-1.881656804733728</v>
       </c>
     </row>
     <row r="57">
@@ -7430,7 +7505,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>InvestSMART Group Limited (ASX:INV)</t>
+          <t>ARC Funds Limited (ASX:ARC)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7439,25 +7514,25 @@
         </is>
       </c>
       <c r="D57">
-        <v>-0.07919999999999999</v>
+        <v>-0.5379999999999999</v>
       </c>
       <c r="G57">
-        <v>-0.02947530864197531</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>-0.02947530864197531</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>-0.09336419753086418</v>
+        <v>-21.375</v>
       </c>
       <c r="J57">
-        <v>-0.09336419753086418</v>
+        <v>-21.375</v>
       </c>
       <c r="K57">
-        <v>-0.51</v>
+        <v>-0.642</v>
       </c>
       <c r="L57">
-        <v>-0.07870370370370371</v>
+        <v>-26.75</v>
       </c>
       <c r="M57">
         <v>-0</v>
@@ -7481,67 +7556,61 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>5.57</v>
+        <v>0.399</v>
       </c>
       <c r="V57">
-        <v>0.2390557939914163</v>
+        <v>0.09731707317073172</v>
       </c>
       <c r="W57">
-        <v>-0.1038696537678208</v>
+        <v>-0.321</v>
       </c>
       <c r="X57">
-        <v>0.07303154055789668</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y57">
-        <v>-0.1769011943257174</v>
+        <v>-0.3833083885358016</v>
       </c>
       <c r="Z57">
-        <v>24.3609022556391</v>
+        <v>0.07058823529411763</v>
       </c>
       <c r="AA57">
-        <v>-2.274436090225564</v>
+        <v>-1.508823529411764</v>
       </c>
       <c r="AB57">
-        <v>0.07245837480620806</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC57">
-        <v>-2.346894465031772</v>
+        <v>-1.571131917947566</v>
       </c>
       <c r="AD57">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AE57">
         <v>0</v>
       </c>
       <c r="AF57">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>-4.999000000000001</v>
+        <v>-0.399</v>
       </c>
       <c r="AH57">
-        <v>0.0239202379456244</v>
+        <v>0</v>
       </c>
       <c r="AI57">
-        <v>0.120185224163334</v>
+        <v>0</v>
       </c>
       <c r="AJ57">
-        <v>-0.2731544724332003</v>
+        <v>-0.1078087003512564</v>
       </c>
       <c r="AK57">
-        <v>6.103785103785098</v>
+        <v>-0.4478114478114478</v>
       </c>
       <c r="AL57">
         <v>0</v>
       </c>
       <c r="AM57">
         <v>0</v>
-      </c>
-      <c r="AN57">
-        <v>-2.989528795811518</v>
-      </c>
-      <c r="AP57">
-        <v>26.17277486910995</v>
       </c>
     </row>
     <row r="58">
@@ -7552,7 +7621,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Strategic Elements Ltd (ASX:SOR)</t>
+          <t>Associate Global Partners Limited (ASX:APL)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7560,23 +7629,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D58">
+        <v>0.0965</v>
+      </c>
       <c r="G58">
-        <v>-17.71653543307087</v>
+        <v>-0.3623978201634878</v>
       </c>
       <c r="H58">
-        <v>-17.71653543307087</v>
+        <v>-0.3623978201634878</v>
       </c>
       <c r="I58">
-        <v>-17.85480862411122</v>
+        <v>-0.3651226158038147</v>
       </c>
       <c r="J58">
-        <v>-17.85480862411122</v>
+        <v>-0.3651226158038147</v>
       </c>
       <c r="K58">
-        <v>-2.39</v>
+        <v>-1.32</v>
       </c>
       <c r="L58">
-        <v>-18.81889763779528</v>
+        <v>-0.3596730245231608</v>
       </c>
       <c r="M58">
         <v>-0</v>
@@ -7600,64 +7672,64 @@
         <v>0</v>
       </c>
       <c r="U58">
-        <v>3.24</v>
+        <v>2.7</v>
       </c>
       <c r="V58">
-        <v>0.07864077669902912</v>
+        <v>0.4122137404580153</v>
       </c>
       <c r="W58">
-        <v>-0.4127806563039724</v>
+        <v>-0.2153344208809136</v>
       </c>
       <c r="X58">
-        <v>0.0724558220543962</v>
+        <v>0.06557443946214965</v>
       </c>
       <c r="Y58">
-        <v>-0.4852364783583686</v>
+        <v>-0.2809088603430632</v>
       </c>
       <c r="AB58">
-        <v>0.07245423086174417</v>
+        <v>0.0609196711435771</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE58">
-        <v>0.002803476310625175</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>0.002803476310625175</v>
+        <v>1.3</v>
       </c>
       <c r="AG58">
-        <v>-3.237196523689375</v>
+        <v>-1.4</v>
       </c>
       <c r="AH58">
-        <v>6.80409116393505e-05</v>
+        <v>0.1656050955414013</v>
       </c>
       <c r="AI58">
-        <v>0.0009006274671563677</v>
+        <v>0.21630615640599</v>
       </c>
       <c r="AJ58">
-        <v>-0.08527285203553092</v>
+        <v>-0.2718446601941748</v>
       </c>
       <c r="AK58">
-        <v>25.45035375019281</v>
+        <v>-0.4229607250755288</v>
       </c>
       <c r="AL58">
-        <v>0.002</v>
+        <v>0.077</v>
       </c>
       <c r="AM58">
-        <v>0.001</v>
+        <v>-0.02200000000000001</v>
       </c>
       <c r="AN58">
-        <v>-0</v>
+        <v>-0.9774436090225563</v>
       </c>
       <c r="AO58">
-        <v>-1135</v>
+        <v>-17.4025974025974</v>
       </c>
       <c r="AP58">
-        <v>1.440674910409157</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="AQ58">
-        <v>-2270</v>
+        <v>60.9090909090909</v>
       </c>
     </row>
     <row r="59">
@@ -7668,7 +7740,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A1 Investments &amp; Resources Ltd (ASX:AYI)</t>
+          <t>Strategic Elements Ltd (ASX:SOR)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -7676,26 +7748,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D59">
-        <v>-0.19</v>
-      </c>
       <c r="G59">
-        <v>-7.527027027027028</v>
+        <v>-155</v>
       </c>
       <c r="H59">
-        <v>-7.527027027027028</v>
+        <v>-155</v>
       </c>
       <c r="I59">
-        <v>-7.675675675675675</v>
+        <v>-155.38064242926</v>
       </c>
       <c r="J59">
-        <v>-7.675675675675675</v>
+        <v>-155.38064242926</v>
       </c>
       <c r="K59">
-        <v>-0.6919999999999999</v>
+        <v>-1.64</v>
       </c>
       <c r="L59">
-        <v>-9.351351351351351</v>
+        <v>-164</v>
       </c>
       <c r="M59">
         <v>-0</v>
@@ -7719,64 +7788,64 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>0.544</v>
+        <v>5.24</v>
       </c>
       <c r="V59">
-        <v>0.04857142857142858</v>
+        <v>0.2201680672268908</v>
       </c>
       <c r="W59">
-        <v>1.051671732522796</v>
+        <v>-0.5273311897106109</v>
       </c>
       <c r="X59">
-        <v>0.07617721702208283</v>
+        <v>0.06232154778597848</v>
       </c>
       <c r="Y59">
-        <v>0.9754945155007134</v>
+        <v>-0.5896527374965894</v>
       </c>
       <c r="AB59">
-        <v>0.07139846034289342</v>
+        <v>0.06230019526885139</v>
       </c>
       <c r="AD59">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>0.01903212146299918</v>
       </c>
       <c r="AF59">
-        <v>1.77</v>
+        <v>0.01903212146299918</v>
       </c>
       <c r="AG59">
-        <v>1.226</v>
+        <v>-5.220967878537001</v>
       </c>
       <c r="AH59">
-        <v>0.1364687740940632</v>
+        <v>0.0007990300095296314</v>
       </c>
       <c r="AI59">
-        <v>3.6875</v>
+        <v>0.003584857094018586</v>
       </c>
       <c r="AJ59">
-        <v>0.0986640914212136</v>
+        <v>-0.2810139863263166</v>
       </c>
       <c r="AK59">
-        <v>-19.15624999999998</v>
+        <v>-75.63099275944232</v>
       </c>
       <c r="AL59">
-        <v>0.037</v>
+        <v>0.001</v>
       </c>
       <c r="AM59">
-        <v>0.037</v>
+        <v>-0.074</v>
       </c>
       <c r="AN59">
-        <v>-3.177737881508079</v>
+        <v>-0</v>
       </c>
       <c r="AO59">
-        <v>-15.35135135135135</v>
+        <v>-1570</v>
       </c>
       <c r="AP59">
-        <v>-2.201077199281867</v>
+        <v>3.412397306233334</v>
       </c>
       <c r="AQ59">
-        <v>-15.35135135135135</v>
+        <v>21.21621621621622</v>
       </c>
     </row>
     <row r="60">
@@ -7787,7 +7856,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WAM Strategic Value Limited (ASX:WAR)</t>
+          <t>Fatfish Group Limited (ASX:FFG)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7795,68 +7864,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D60">
+        <v>-0.133</v>
+      </c>
+      <c r="G60">
+        <v>-2.238193018480493</v>
+      </c>
+      <c r="H60">
+        <v>-2.238193018480493</v>
+      </c>
+      <c r="I60">
+        <v>-1.550308008213552</v>
+      </c>
+      <c r="J60">
+        <v>-1.550308008213552</v>
+      </c>
       <c r="K60">
-        <v>-7.99</v>
+        <v>-4.18</v>
+      </c>
+      <c r="L60">
+        <v>-4.291581108829568</v>
       </c>
       <c r="M60">
-        <v>0.911</v>
+        <v>0.108</v>
       </c>
       <c r="N60">
-        <v>0.007329042638777153</v>
+        <v>0.007826086956521738</v>
       </c>
       <c r="O60">
-        <v>-0.114017521902378</v>
+        <v>-0.02583732057416268</v>
       </c>
       <c r="P60">
-        <v>0.911</v>
+        <v>-0</v>
       </c>
       <c r="Q60">
-        <v>0.007329042638777153</v>
+        <v>-0</v>
       </c>
       <c r="R60">
-        <v>-0.114017521902378</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>0.747</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>0.05413043478260869</v>
+      </c>
+      <c r="W60">
+        <v>0.6593059936908517</v>
       </c>
       <c r="X60">
-        <v>0.07245421904070486</v>
+        <v>0.06743594284687141</v>
+      </c>
+      <c r="Y60">
+        <v>0.5918700508439804</v>
       </c>
       <c r="AB60">
-        <v>0.07245421904070486</v>
+        <v>0.06031620172855389</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE60">
         <v>0</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>3.553</v>
       </c>
       <c r="AH60">
-        <v>0</v>
+        <v>0.2375690607734806</v>
+      </c>
+      <c r="AI60">
+        <v>0.8344653599844751</v>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>0.2047484584798017</v>
+      </c>
+      <c r="AK60">
+        <v>0.8064003631411711</v>
       </c>
       <c r="AL60">
-        <v>0</v>
+        <v>0.249</v>
       </c>
       <c r="AM60">
-        <v>0</v>
+        <v>0.249</v>
+      </c>
+      <c r="AN60">
+        <v>-3.64406779661017</v>
+      </c>
+      <c r="AO60">
+        <v>-6.06425702811245</v>
+      </c>
+      <c r="AP60">
+        <v>-3.011016949152542</v>
+      </c>
+      <c r="AQ60">
+        <v>-6.06425702811245</v>
       </c>
     </row>
     <row r="61">
@@ -7867,7 +7978,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Salter Brothers Emerging Companies Limited (ASX:SB2)</t>
+          <t>InvestSMART Group Limited (ASX:INV)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7875,8 +7986,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D61">
+        <v>-0.0542</v>
+      </c>
+      <c r="G61">
+        <v>-0.05324483775811209</v>
+      </c>
+      <c r="H61">
+        <v>-0.05324483775811209</v>
+      </c>
+      <c r="I61">
+        <v>-0.1122418879056047</v>
+      </c>
+      <c r="J61">
+        <v>-0.1122418879056047</v>
+      </c>
       <c r="K61">
-        <v>-5.64</v>
+        <v>-0.649</v>
+      </c>
+      <c r="L61">
+        <v>-0.09572271386430678</v>
       </c>
       <c r="M61">
         <v>-0</v>
@@ -7900,40 +8029,58 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>0.335483870967742</v>
+      </c>
+      <c r="W61">
+        <v>-0.1552631578947369</v>
       </c>
       <c r="X61">
-        <v>0.07245421904070486</v>
+        <v>0.0627606595978259</v>
+      </c>
+      <c r="Y61">
+        <v>-0.2180238174925627</v>
       </c>
       <c r="AB61">
-        <v>0.07245421904070486</v>
+        <v>0.06203410679180594</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="AE61">
         <v>0</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>0.426</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>-4.774</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>0.02674871279668467</v>
+      </c>
+      <c r="AI61">
+        <v>0.1093429158110883</v>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>-0.4450867052023122</v>
+      </c>
+      <c r="AK61">
+        <v>3.661042944785276</v>
       </c>
       <c r="AL61">
         <v>0</v>
       </c>
       <c r="AM61">
         <v>0</v>
+      </c>
+      <c r="AN61">
+        <v>-1.18005540166205</v>
+      </c>
+      <c r="AP61">
+        <v>13.22437673130194</v>
       </c>
     </row>
     <row r="62">
@@ -7944,7 +8091,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ARC Funds Limited (ASX:ARC)</t>
+          <t>K2 Asset Management Holdings Ltd (ASX:KAM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7953,25 +8100,25 @@
         </is>
       </c>
       <c r="D62">
-        <v>-0.5770000000000001</v>
+        <v>-0.325</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>-0.9090909090909091</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>-0.9393939393939393</v>
       </c>
       <c r="I62">
-        <v>-127.3333333333333</v>
+        <v>-0.962121212121212</v>
       </c>
       <c r="J62">
-        <v>-127.3333333333333</v>
+        <v>-0.962121212121212</v>
       </c>
       <c r="K62">
-        <v>-0.422</v>
+        <v>-1.29</v>
       </c>
       <c r="L62">
-        <v>-140.6666666666667</v>
+        <v>-0.9772727272727273</v>
       </c>
       <c r="M62">
         <v>-0</v>
@@ -7995,52 +8142,64 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>1.66</v>
+        <v>6.02</v>
       </c>
       <c r="V62">
-        <v>0.2459259259259259</v>
+        <v>0.5423423423423424</v>
       </c>
       <c r="W62">
-        <v>-0.1688</v>
+        <v>-0.1755102040816327</v>
       </c>
       <c r="X62">
-        <v>0.07245421904070486</v>
+        <v>0.06230987104679038</v>
       </c>
       <c r="Y62">
-        <v>-0.2412542190407049</v>
+        <v>-0.2378200751284231</v>
       </c>
       <c r="AB62">
-        <v>0.07245421904070486</v>
+        <v>0.06230763313389543</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG62">
-        <v>-1.66</v>
+        <v>-6.018999999999999</v>
       </c>
       <c r="AH62">
-        <v>0</v>
+        <v>9.008197459688317e-05</v>
       </c>
       <c r="AI62">
-        <v>0</v>
+        <v>0.0001720874204095681</v>
       </c>
       <c r="AJ62">
-        <v>-0.3261296660117878</v>
+        <v>-1.184609328872269</v>
       </c>
       <c r="AK62">
-        <v>-4.882352941176469</v>
+        <v>28.799043062201</v>
       </c>
       <c r="AL62">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AM62">
-        <v>0</v>
+        <v>0.017</v>
+      </c>
+      <c r="AN62">
+        <v>-0.0008064516129032258</v>
+      </c>
+      <c r="AO62">
+        <v>-74.70588235294117</v>
+      </c>
+      <c r="AP62">
+        <v>4.854032258064516</v>
+      </c>
+      <c r="AQ62">
+        <v>-74.70588235294117</v>
       </c>
     </row>
   </sheetData>
